--- a/PA-PL_occupancy_pace_150day.xlsx
+++ b/PA-PL_occupancy_pace_150day.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D155"/>
+  <dimension ref="A1:D125"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -415,637 +415,637 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>06/29</v>
+        <v>07/06</v>
       </c>
       <c r="B2">
-        <v>241.59375</v>
+        <v>228.15</v>
       </c>
       <c r="C2">
         <v>8</v>
       </c>
       <c r="D2">
-        <v>1932.75</v>
+        <v>1825.2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>06/30</v>
+        <v>07/07</v>
       </c>
       <c r="B3">
-        <v>276.6775</v>
+        <v>215.20555555555558</v>
       </c>
       <c r="C3">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D3">
-        <v>1106.71</v>
+        <v>1936.8500000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>07/01</v>
+        <v>07/08</v>
       </c>
       <c r="B4">
-        <v>359.75</v>
+        <v>213.252</v>
       </c>
       <c r="C4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D4">
-        <v>1439</v>
+        <v>1066.26</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>07/02</v>
+        <v>07/09</v>
       </c>
       <c r="B5">
-        <v>338.5</v>
+        <v>245.2444444444444</v>
       </c>
       <c r="C5">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D5">
-        <v>1354</v>
+        <v>2207.2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>07/03</v>
+        <v>07/10</v>
       </c>
       <c r="B6">
-        <v>426.4319047619048</v>
+        <v>336.2</v>
       </c>
       <c r="C6">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="D6">
-        <v>8955.07</v>
+        <v>3698.2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>07/04</v>
+        <v>07/11</v>
       </c>
       <c r="B7">
-        <v>408.6536842105263</v>
+        <v>324.82</v>
       </c>
       <c r="C7">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="D7">
-        <v>7764.42</v>
+        <v>3248.2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>07/05</v>
+        <v>07/12</v>
       </c>
       <c r="B8">
-        <v>197.054</v>
+        <v>243.8</v>
       </c>
       <c r="C8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D8">
-        <v>985.27</v>
+        <v>975.2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>07/06</v>
+        <v>07/13</v>
       </c>
       <c r="B9">
-        <v>230.70000000000002</v>
+        <v>212.86499999999998</v>
       </c>
       <c r="C9">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D9">
-        <v>1384.2</v>
+        <v>425.72999999999996</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>07/07</v>
+        <v>07/14</v>
       </c>
       <c r="B10">
-        <v>220.72500000000002</v>
+        <v>201.1</v>
       </c>
       <c r="C10">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D10">
-        <v>1324.3500000000001</v>
+        <v>402.2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>07/08</v>
+        <v>07/15</v>
       </c>
       <c r="B11">
-        <v>200.315</v>
+        <v>275.19666666666666</v>
       </c>
       <c r="C11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D11">
-        <v>801.26</v>
+        <v>825.5899999999999</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>07/09</v>
+        <v>07/16</v>
       </c>
       <c r="B12">
-        <v>233.9</v>
+        <v>262.6</v>
       </c>
       <c r="C12">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D12">
-        <v>1871.2</v>
+        <v>525.2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>07/10</v>
+        <v>07/17</v>
       </c>
       <c r="B13">
-        <v>336.2</v>
+        <v>347.64</v>
       </c>
       <c r="C13">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D13">
-        <v>3698.2</v>
+        <v>2781.12</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>07/11</v>
+        <v>07/18</v>
       </c>
       <c r="B14">
-        <v>333.2444444444444</v>
+        <v>311.59</v>
       </c>
       <c r="C14">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D14">
-        <v>2999.2</v>
+        <v>4050.6699999999996</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>07/12</v>
+        <v>07/19</v>
       </c>
       <c r="B15">
-        <v>257.40000000000003</v>
+        <v>264.34375</v>
       </c>
       <c r="C15">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D15">
-        <v>772.2</v>
+        <v>2114.75</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>07/13</v>
+        <v>07/20</v>
       </c>
       <c r="B16">
-        <v>143.2</v>
+        <v>316.3333333333333</v>
       </c>
       <c r="C16">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D16">
-        <v>143.2</v>
+        <v>949</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>07/14</v>
+        <v>07/21</v>
       </c>
       <c r="B17">
-        <v>143.2</v>
+        <v>339.5</v>
       </c>
       <c r="C17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D17">
-        <v>143.2</v>
+        <v>679</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>07/15</v>
+        <v>07/22</v>
       </c>
       <c r="B18">
-        <v>275.19666666666666</v>
+        <v>0</v>
       </c>
       <c r="C18">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D18">
-        <v>825.5899999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>07/16</v>
+        <v>07/23</v>
       </c>
       <c r="B19">
-        <v>262.6</v>
+        <v>349</v>
       </c>
       <c r="C19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D19">
-        <v>525.2</v>
+        <v>349</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>07/17</v>
+        <v>07/24</v>
       </c>
       <c r="B20">
-        <v>347.64</v>
+        <v>362.4</v>
       </c>
       <c r="C20">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D20">
-        <v>2781.12</v>
+        <v>1812</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>07/18</v>
+        <v>07/25</v>
       </c>
       <c r="B21">
-        <v>311.59</v>
+        <v>360.3333333333333</v>
       </c>
       <c r="C21">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D21">
-        <v>4050.6699999999996</v>
+        <v>2162</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>07/19</v>
+        <v>07/26</v>
       </c>
       <c r="B22">
-        <v>264.34375</v>
+        <v>247</v>
       </c>
       <c r="C22">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D22">
-        <v>2114.75</v>
+        <v>247</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>07/20</v>
+        <v>07/27</v>
       </c>
       <c r="B23">
-        <v>333</v>
+        <v>327.5</v>
       </c>
       <c r="C23">
         <v>2</v>
       </c>
       <c r="D23">
-        <v>666</v>
+        <v>655</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>07/21</v>
+        <v>07/28</v>
       </c>
       <c r="B24">
-        <v>394</v>
+        <v>326.5</v>
       </c>
       <c r="C24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D24">
-        <v>394</v>
+        <v>653</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>07/22</v>
+        <v>07/29</v>
       </c>
       <c r="B25">
-        <v>0</v>
+        <v>386</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>772</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>07/23</v>
+        <v>07/30</v>
       </c>
       <c r="B26">
-        <v>0</v>
+        <v>464</v>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>464</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>07/24</v>
+        <v>07/31</v>
       </c>
       <c r="B27">
-        <v>333</v>
+        <v>434.61538461538464</v>
       </c>
       <c r="C27">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="D27">
-        <v>1332</v>
+        <v>5650</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>07/25</v>
+        <v>08/01</v>
       </c>
       <c r="B28">
-        <v>337</v>
+        <v>432.875</v>
       </c>
       <c r="C28">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="D28">
-        <v>1348</v>
+        <v>6926</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>07/26</v>
+        <v>08/02</v>
       </c>
       <c r="B29">
-        <v>0</v>
+        <v>360.4</v>
       </c>
       <c r="C29">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D29">
-        <v>0</v>
+        <v>1802</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>07/27</v>
+        <v>08/03</v>
       </c>
       <c r="B30">
-        <v>375</v>
+        <v>363.75</v>
       </c>
       <c r="C30">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D30">
-        <v>375</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>07/28</v>
+        <v>08/04</v>
       </c>
       <c r="B31">
-        <v>390</v>
+        <v>336</v>
       </c>
       <c r="C31">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D31">
-        <v>390</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>07/29</v>
+        <v>08/05</v>
       </c>
       <c r="B32">
-        <v>386</v>
+        <v>289</v>
       </c>
       <c r="C32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D32">
-        <v>772</v>
+        <v>289</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>07/30</v>
+        <v>08/06</v>
       </c>
       <c r="B33">
-        <v>464</v>
+        <v>289</v>
       </c>
       <c r="C33">
         <v>1</v>
       </c>
       <c r="D33">
-        <v>464</v>
+        <v>289</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>07/31</v>
+        <v>08/07</v>
       </c>
       <c r="B34">
-        <v>432.4</v>
+        <v>462.7</v>
       </c>
       <c r="C34">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D34">
-        <v>4324</v>
+        <v>1850.8</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>08/01</v>
+        <v>08/08</v>
       </c>
       <c r="B35">
-        <v>431.7692307692308</v>
+        <v>484.21000000000004</v>
       </c>
       <c r="C35">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D35">
-        <v>5613</v>
+        <v>2905.26</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>08/02</v>
+        <v>08/09</v>
       </c>
       <c r="B36">
-        <v>364.25</v>
+        <v>239.80000000000004</v>
       </c>
       <c r="C36">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D36">
-        <v>1457</v>
+        <v>719.4000000000001</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>08/03</v>
+        <v>08/10</v>
       </c>
       <c r="B37">
-        <v>363.75</v>
+        <v>215.2</v>
       </c>
       <c r="C37">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D37">
-        <v>1455</v>
+        <v>430.4</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>08/04</v>
+        <v>08/11</v>
       </c>
       <c r="B38">
-        <v>336</v>
+        <v>371</v>
       </c>
       <c r="C38">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D38">
-        <v>1344</v>
+        <v>371</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>08/05</v>
+        <v>08/12</v>
       </c>
       <c r="B39">
-        <v>289</v>
+        <v>358</v>
       </c>
       <c r="C39">
         <v>1</v>
       </c>
       <c r="D39">
-        <v>289</v>
+        <v>358</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>08/06</v>
+        <v>08/13</v>
       </c>
       <c r="B40">
-        <v>289</v>
+        <v>0</v>
       </c>
       <c r="C40">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D40">
-        <v>289</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>08/07</v>
+        <v>08/14</v>
       </c>
       <c r="B41">
-        <v>462.7</v>
+        <v>0</v>
       </c>
       <c r="C41">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D41">
-        <v>1850.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>08/08</v>
+        <v>08/15</v>
       </c>
       <c r="B42">
-        <v>484.21000000000004</v>
+        <v>433.8</v>
       </c>
       <c r="C42">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D42">
-        <v>2905.26</v>
+        <v>433.8</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>08/09</v>
+        <v>08/16</v>
       </c>
       <c r="B43">
-        <v>239.79999999999998</v>
+        <v>328.49</v>
       </c>
       <c r="C43">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D43">
-        <v>719.4</v>
+        <v>328.49</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>08/10</v>
+        <v>08/17</v>
       </c>
       <c r="B44">
-        <v>215.2</v>
+        <v>487</v>
       </c>
       <c r="C44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D44">
-        <v>430.4</v>
+        <v>487</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>08/11</v>
+        <v>08/18</v>
       </c>
       <c r="B45">
-        <v>371</v>
+        <v>380.6</v>
       </c>
       <c r="C45">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D45">
-        <v>371</v>
+        <v>761.2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>08/12</v>
+        <v>08/19</v>
       </c>
       <c r="B46">
-        <v>358</v>
+        <v>330.3</v>
       </c>
       <c r="C46">
         <v>1</v>
       </c>
       <c r="D46">
-        <v>358</v>
+        <v>330.3</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>08/13</v>
+        <v>08/20</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -1059,77 +1059,77 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>08/14</v>
+        <v>08/21</v>
       </c>
       <c r="B48">
-        <v>0</v>
+        <v>417.3</v>
       </c>
       <c r="C48">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D48">
-        <v>0</v>
+        <v>834.6</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>08/15</v>
+        <v>08/22</v>
       </c>
       <c r="B49">
-        <v>433.8</v>
+        <v>417.3</v>
       </c>
       <c r="C49">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D49">
-        <v>433.8</v>
+        <v>834.6</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>08/16</v>
+        <v>08/23</v>
       </c>
       <c r="B50">
-        <v>328.49</v>
+        <v>368.05</v>
       </c>
       <c r="C50">
         <v>1</v>
       </c>
       <c r="D50">
-        <v>328.49</v>
+        <v>368.05</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>08/17</v>
+        <v>08/24</v>
       </c>
       <c r="B51">
-        <v>487</v>
+        <v>342.54999999999995</v>
       </c>
       <c r="C51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D51">
-        <v>487</v>
+        <v>685.0999999999999</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>08/18</v>
+        <v>08/25</v>
       </c>
       <c r="B52">
-        <v>430</v>
+        <v>309.48333333333335</v>
       </c>
       <c r="C52">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D52">
-        <v>430</v>
+        <v>928.45</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>08/19</v>
+        <v>08/26</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -1143,7 +1143,7 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>08/20</v>
+        <v>08/27</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -1157,77 +1157,77 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>08/21</v>
+        <v>08/28</v>
       </c>
       <c r="B55">
-        <v>417.3</v>
+        <v>0</v>
       </c>
       <c r="C55">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D55">
-        <v>834.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>08/22</v>
+        <v>08/29</v>
       </c>
       <c r="B56">
-        <v>417.3</v>
+        <v>0</v>
       </c>
       <c r="C56">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D56">
-        <v>834.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>08/23</v>
+        <v>08/30</v>
       </c>
       <c r="B57">
-        <v>368.05</v>
+        <v>0</v>
       </c>
       <c r="C57">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D57">
-        <v>368.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>08/24</v>
+        <v>08/31</v>
       </c>
       <c r="B58">
-        <v>342.54999999999995</v>
+        <v>294</v>
       </c>
       <c r="C58">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D58">
-        <v>685.0999999999999</v>
+        <v>294</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>08/25</v>
+        <v>09/01</v>
       </c>
       <c r="B59">
-        <v>309.48333333333335</v>
+        <v>266</v>
       </c>
       <c r="C59">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D59">
-        <v>928.45</v>
+        <v>266</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>08/26</v>
+        <v>09/02</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -1241,7 +1241,7 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>08/27</v>
+        <v>09/03</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -1255,77 +1255,77 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>08/28</v>
+        <v>09/04</v>
       </c>
       <c r="B62">
-        <v>399</v>
+        <v>0</v>
       </c>
       <c r="C62">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D62">
-        <v>399</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>08/29</v>
+        <v>09/05</v>
       </c>
       <c r="B63">
-        <v>399</v>
+        <v>385</v>
       </c>
       <c r="C63">
         <v>1</v>
       </c>
       <c r="D63">
-        <v>399</v>
+        <v>385</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>08/30</v>
+        <v>09/06</v>
       </c>
       <c r="B64">
-        <v>0</v>
+        <v>398</v>
       </c>
       <c r="C64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D64">
-        <v>0</v>
+        <v>398</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>08/31</v>
+        <v>09/07</v>
       </c>
       <c r="B65">
-        <v>294</v>
+        <v>206</v>
       </c>
       <c r="C65">
         <v>1</v>
       </c>
       <c r="D65">
-        <v>294</v>
+        <v>206</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>09/01</v>
+        <v>09/08</v>
       </c>
       <c r="B66">
-        <v>266</v>
+        <v>181</v>
       </c>
       <c r="C66">
         <v>1</v>
       </c>
       <c r="D66">
-        <v>266</v>
+        <v>181</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>09/02</v>
+        <v>09/09</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -1339,175 +1339,175 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>09/03</v>
+        <v>09/10</v>
       </c>
       <c r="B68">
-        <v>0</v>
+        <v>219</v>
       </c>
       <c r="C68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D68">
-        <v>0</v>
+        <v>219</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>09/04</v>
+        <v>09/11</v>
       </c>
       <c r="B69">
-        <v>0</v>
+        <v>301</v>
       </c>
       <c r="C69">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D69">
-        <v>0</v>
+        <v>602</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>09/05</v>
+        <v>09/12</v>
       </c>
       <c r="B70">
-        <v>385</v>
+        <v>311</v>
       </c>
       <c r="C70">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D70">
-        <v>385</v>
+        <v>933</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>09/06</v>
+        <v>09/13</v>
       </c>
       <c r="B71">
-        <v>398</v>
+        <v>210.33333333333334</v>
       </c>
       <c r="C71">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D71">
-        <v>398</v>
+        <v>631</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>09/07</v>
+        <v>09/14</v>
       </c>
       <c r="B72">
-        <v>206</v>
+        <v>188</v>
       </c>
       <c r="C72">
         <v>1</v>
       </c>
       <c r="D72">
-        <v>206</v>
+        <v>188</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>09/08</v>
+        <v>09/15</v>
       </c>
       <c r="B73">
-        <v>181</v>
+        <v>0</v>
       </c>
       <c r="C73">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D73">
-        <v>181</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>09/09</v>
+        <v>09/16</v>
       </c>
       <c r="B74">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="C74">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D74">
-        <v>0</v>
+        <v>210</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>09/10</v>
+        <v>09/17</v>
       </c>
       <c r="B75">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="C75">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D75">
-        <v>0</v>
+        <v>210</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>09/11</v>
+        <v>09/18</v>
       </c>
       <c r="B76">
-        <v>0</v>
+        <v>310.29555555555555</v>
       </c>
       <c r="C76">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="D76">
-        <v>0</v>
+        <v>5585.32</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>09/12</v>
+        <v>09/19</v>
       </c>
       <c r="B77">
-        <v>0</v>
+        <v>305.17272727272723</v>
       </c>
       <c r="C77">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="D77">
-        <v>0</v>
+        <v>6713.799999999999</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>09/13</v>
+        <v>09/20</v>
       </c>
       <c r="B78">
-        <v>197</v>
+        <v>214</v>
       </c>
       <c r="C78">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D78">
-        <v>197</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>09/14</v>
+        <v>09/21</v>
       </c>
       <c r="B79">
-        <v>188</v>
+        <v>160</v>
       </c>
       <c r="C79">
         <v>1</v>
       </c>
       <c r="D79">
-        <v>188</v>
+        <v>160</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>09/15</v>
+        <v>09/22</v>
       </c>
       <c r="B80">
         <v>0</v>
@@ -1521,77 +1521,77 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>09/16</v>
+        <v>09/23</v>
       </c>
       <c r="B81">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="C81">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D81">
-        <v>210</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>09/17</v>
+        <v>09/24</v>
       </c>
       <c r="B82">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="C82">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D82">
-        <v>210</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>09/18</v>
+        <v>09/25</v>
       </c>
       <c r="B83">
-        <v>304.895</v>
+        <v>395</v>
       </c>
       <c r="C83">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D83">
-        <v>4878.32</v>
+        <v>2370</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>09/19</v>
+        <v>09/26</v>
       </c>
       <c r="B84">
-        <v>303.7263157894737</v>
+        <v>391.3333333333333</v>
       </c>
       <c r="C84">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D84">
-        <v>5770.8</v>
+        <v>3522</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>09/20</v>
+        <v>09/27</v>
       </c>
       <c r="B85">
-        <v>239</v>
+        <v>274.2857142857143</v>
       </c>
       <c r="C85">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D85">
-        <v>717</v>
+        <v>1920</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>09/21</v>
+        <v>09/28</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -1605,7 +1605,7 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>09/22</v>
+        <v>09/29</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -1619,7 +1619,7 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>09/23</v>
+        <v>09/30</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -1633,77 +1633,77 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>09/24</v>
+        <v>10/01</v>
       </c>
       <c r="B89">
-        <v>0</v>
+        <v>194</v>
       </c>
       <c r="C89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D89">
-        <v>0</v>
+        <v>194</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>09/25</v>
+        <v>10/02</v>
       </c>
       <c r="B90">
-        <v>395</v>
+        <v>322.16</v>
       </c>
       <c r="C90">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D90">
-        <v>2370</v>
+        <v>3221.6000000000004</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>09/26</v>
+        <v>10/03</v>
       </c>
       <c r="B91">
-        <v>391.3333333333333</v>
+        <v>319.64</v>
       </c>
       <c r="C91">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D91">
-        <v>3522</v>
+        <v>3196.4</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>09/27</v>
+        <v>10/04</v>
       </c>
       <c r="B92">
-        <v>274.2857142857143</v>
+        <v>203</v>
       </c>
       <c r="C92">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D92">
-        <v>1920</v>
+        <v>203</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>09/28</v>
+        <v>10/05</v>
       </c>
       <c r="B93">
-        <v>0</v>
+        <v>193.5</v>
       </c>
       <c r="C93">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D93">
-        <v>0</v>
+        <v>387</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>09/29</v>
+        <v>10/06</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -1717,7 +1717,7 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>09/30</v>
+        <v>10/07</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -1731,77 +1731,77 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>10/01</v>
+        <v>10/08</v>
       </c>
       <c r="B96">
-        <v>194</v>
+        <v>0</v>
       </c>
       <c r="C96">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D96">
-        <v>194</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>10/02</v>
+        <v>10/09</v>
       </c>
       <c r="B97">
-        <v>322.15999999999997</v>
+        <v>406.29999999999995</v>
       </c>
       <c r="C97">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D97">
-        <v>3221.6</v>
+        <v>1218.8999999999999</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>10/03</v>
+        <v>10/10</v>
       </c>
       <c r="B98">
-        <v>319.64</v>
+        <v>396.3833333333334</v>
       </c>
       <c r="C98">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D98">
-        <v>3196.4</v>
+        <v>1189.15</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>10/04</v>
+        <v>10/11</v>
       </c>
       <c r="B99">
-        <v>203</v>
+        <v>0</v>
       </c>
       <c r="C99">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D99">
-        <v>203</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>10/05</v>
+        <v>10/12</v>
       </c>
       <c r="B100">
-        <v>193.5</v>
+        <v>0</v>
       </c>
       <c r="C100">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D100">
-        <v>387</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>10/06</v>
+        <v>10/13</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -1815,7 +1815,7 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>10/07</v>
+        <v>10/14</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -1829,7 +1829,7 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>10/08</v>
+        <v>10/15</v>
       </c>
       <c r="B103">
         <v>0</v>
@@ -1843,7 +1843,7 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>10/09</v>
+        <v>10/16</v>
       </c>
       <c r="B104">
         <v>0</v>
@@ -1857,7 +1857,7 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>10/10</v>
+        <v>10/17</v>
       </c>
       <c r="B105">
         <v>0</v>
@@ -1871,7 +1871,7 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>10/11</v>
+        <v>10/18</v>
       </c>
       <c r="B106">
         <v>0</v>
@@ -1885,7 +1885,7 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>10/12</v>
+        <v>10/19</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -1899,7 +1899,7 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>10/13</v>
+        <v>10/20</v>
       </c>
       <c r="B108">
         <v>0</v>
@@ -1913,7 +1913,7 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>10/14</v>
+        <v>10/21</v>
       </c>
       <c r="B109">
         <v>0</v>
@@ -1927,49 +1927,49 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>10/15</v>
+        <v>10/22</v>
       </c>
       <c r="B110">
-        <v>0</v>
+        <v>239.115</v>
       </c>
       <c r="C110">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D110">
-        <v>0</v>
+        <v>478.23</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>10/16</v>
+        <v>10/23</v>
       </c>
       <c r="B111">
-        <v>0</v>
+        <v>308.5</v>
       </c>
       <c r="C111">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D111">
-        <v>0</v>
+        <v>1851</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>10/17</v>
+        <v>10/24</v>
       </c>
       <c r="B112">
-        <v>0</v>
+        <v>313.6666666666667</v>
       </c>
       <c r="C112">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D112">
-        <v>0</v>
+        <v>1882</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>10/18</v>
+        <v>10/25</v>
       </c>
       <c r="B113">
         <v>0</v>
@@ -1983,7 +1983,7 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>10/19</v>
+        <v>10/26</v>
       </c>
       <c r="B114">
         <v>0</v>
@@ -1997,7 +1997,7 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>10/20</v>
+        <v>10/27</v>
       </c>
       <c r="B115">
         <v>0</v>
@@ -2011,77 +2011,77 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>10/21</v>
+        <v>10/28</v>
       </c>
       <c r="B116">
-        <v>0</v>
+        <v>135.15</v>
       </c>
       <c r="C116">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D116">
-        <v>0</v>
+        <v>135.15</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>10/22</v>
+        <v>10/29</v>
       </c>
       <c r="B117">
-        <v>239.115</v>
+        <v>144.5</v>
       </c>
       <c r="C117">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D117">
-        <v>478.23</v>
+        <v>144.5</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>10/23</v>
+        <v>10/30</v>
       </c>
       <c r="B118">
-        <v>308.6</v>
+        <v>289</v>
       </c>
       <c r="C118">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D118">
-        <v>1543</v>
+        <v>867</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>10/24</v>
+        <v>10/31</v>
       </c>
       <c r="B119">
-        <v>314.2</v>
+        <v>291</v>
       </c>
       <c r="C119">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D119">
-        <v>1571</v>
+        <v>873</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>10/25</v>
+        <v>11/01</v>
       </c>
       <c r="B120">
-        <v>0</v>
+        <v>219</v>
       </c>
       <c r="C120">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D120">
-        <v>0</v>
+        <v>219</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>10/26</v>
+        <v>11/02</v>
       </c>
       <c r="B121">
         <v>0</v>
@@ -2095,7 +2095,7 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>10/27</v>
+        <v>11/03</v>
       </c>
       <c r="B122">
         <v>0</v>
@@ -2109,469 +2109,49 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>10/28</v>
+        <v>11/04</v>
       </c>
       <c r="B123">
-        <v>135.15</v>
+        <v>0</v>
       </c>
       <c r="C123">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D123">
-        <v>135.15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>10/29</v>
+        <v>11/05</v>
       </c>
       <c r="B124">
-        <v>144.5</v>
+        <v>0</v>
       </c>
       <c r="C124">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D124">
-        <v>144.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>10/30</v>
+        <v>11/06</v>
       </c>
       <c r="B125">
-        <v>289</v>
+        <v>327.5</v>
       </c>
       <c r="C125">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D125">
-        <v>867</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="str">
-        <v>10/31</v>
-      </c>
-      <c r="B126">
-        <v>291</v>
-      </c>
-      <c r="C126">
-        <v>3</v>
-      </c>
-      <c r="D126">
-        <v>873</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="str">
-        <v>11/01</v>
-      </c>
-      <c r="B127">
-        <v>219</v>
-      </c>
-      <c r="C127">
-        <v>1</v>
-      </c>
-      <c r="D127">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="str">
-        <v>11/02</v>
-      </c>
-      <c r="B128">
-        <v>0</v>
-      </c>
-      <c r="C128">
-        <v>0</v>
-      </c>
-      <c r="D128">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="str">
-        <v>11/03</v>
-      </c>
-      <c r="B129">
-        <v>0</v>
-      </c>
-      <c r="C129">
-        <v>0</v>
-      </c>
-      <c r="D129">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="str">
-        <v>11/04</v>
-      </c>
-      <c r="B130">
-        <v>0</v>
-      </c>
-      <c r="C130">
-        <v>0</v>
-      </c>
-      <c r="D130">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="str">
-        <v>11/05</v>
-      </c>
-      <c r="B131">
-        <v>0</v>
-      </c>
-      <c r="C131">
-        <v>0</v>
-      </c>
-      <c r="D131">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="str">
-        <v>11/06</v>
-      </c>
-      <c r="B132">
-        <v>0</v>
-      </c>
-      <c r="C132">
-        <v>0</v>
-      </c>
-      <c r="D132">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="str">
-        <v>11/07</v>
-      </c>
-      <c r="B133">
-        <v>0</v>
-      </c>
-      <c r="C133">
-        <v>0</v>
-      </c>
-      <c r="D133">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="str">
-        <v>11/08</v>
-      </c>
-      <c r="B134">
-        <v>0</v>
-      </c>
-      <c r="C134">
-        <v>0</v>
-      </c>
-      <c r="D134">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="str">
-        <v>11/09</v>
-      </c>
-      <c r="B135">
-        <v>0</v>
-      </c>
-      <c r="C135">
-        <v>0</v>
-      </c>
-      <c r="D135">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="str">
-        <v>11/10</v>
-      </c>
-      <c r="B136">
-        <v>0</v>
-      </c>
-      <c r="C136">
-        <v>0</v>
-      </c>
-      <c r="D136">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="str">
-        <v>11/11</v>
-      </c>
-      <c r="B137">
-        <v>0</v>
-      </c>
-      <c r="C137">
-        <v>0</v>
-      </c>
-      <c r="D137">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="str">
-        <v>11/12</v>
-      </c>
-      <c r="B138">
-        <v>0</v>
-      </c>
-      <c r="C138">
-        <v>0</v>
-      </c>
-      <c r="D138">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="str">
-        <v>11/13</v>
-      </c>
-      <c r="B139">
-        <v>0</v>
-      </c>
-      <c r="C139">
-        <v>0</v>
-      </c>
-      <c r="D139">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="str">
-        <v>11/14</v>
-      </c>
-      <c r="B140">
-        <v>0</v>
-      </c>
-      <c r="C140">
-        <v>0</v>
-      </c>
-      <c r="D140">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="str">
-        <v>11/15</v>
-      </c>
-      <c r="B141">
-        <v>0</v>
-      </c>
-      <c r="C141">
-        <v>0</v>
-      </c>
-      <c r="D141">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="str">
-        <v>11/16</v>
-      </c>
-      <c r="B142">
-        <v>0</v>
-      </c>
-      <c r="C142">
-        <v>0</v>
-      </c>
-      <c r="D142">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="str">
-        <v>11/17</v>
-      </c>
-      <c r="B143">
-        <v>0</v>
-      </c>
-      <c r="C143">
-        <v>0</v>
-      </c>
-      <c r="D143">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="str">
-        <v>11/18</v>
-      </c>
-      <c r="B144">
-        <v>0</v>
-      </c>
-      <c r="C144">
-        <v>0</v>
-      </c>
-      <c r="D144">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="str">
-        <v>11/19</v>
-      </c>
-      <c r="B145">
-        <v>0</v>
-      </c>
-      <c r="C145">
-        <v>0</v>
-      </c>
-      <c r="D145">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="str">
-        <v>11/20</v>
-      </c>
-      <c r="B146">
-        <v>0</v>
-      </c>
-      <c r="C146">
-        <v>0</v>
-      </c>
-      <c r="D146">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="str">
-        <v>11/21</v>
-      </c>
-      <c r="B147">
-        <v>0</v>
-      </c>
-      <c r="C147">
-        <v>0</v>
-      </c>
-      <c r="D147">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="str">
-        <v>11/22</v>
-      </c>
-      <c r="B148">
-        <v>0</v>
-      </c>
-      <c r="C148">
-        <v>0</v>
-      </c>
-      <c r="D148">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="str">
-        <v>11/23</v>
-      </c>
-      <c r="B149">
-        <v>0</v>
-      </c>
-      <c r="C149">
-        <v>0</v>
-      </c>
-      <c r="D149">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="str">
-        <v>11/24</v>
-      </c>
-      <c r="B150">
-        <v>0</v>
-      </c>
-      <c r="C150">
-        <v>0</v>
-      </c>
-      <c r="D150">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="str">
-        <v>11/25</v>
-      </c>
-      <c r="B151">
-        <v>0</v>
-      </c>
-      <c r="C151">
-        <v>0</v>
-      </c>
-      <c r="D151">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="str">
-        <v>11/26</v>
-      </c>
-      <c r="B152">
-        <v>0</v>
-      </c>
-      <c r="C152">
-        <v>0</v>
-      </c>
-      <c r="D152">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="str">
-        <v>11/27</v>
-      </c>
-      <c r="B153">
-        <v>0</v>
-      </c>
-      <c r="C153">
-        <v>0</v>
-      </c>
-      <c r="D153">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="str">
-        <v>11/28</v>
-      </c>
-      <c r="B154">
-        <v>0</v>
-      </c>
-      <c r="C154">
-        <v>0</v>
-      </c>
-      <c r="D154">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="str">
-        <v>11/29</v>
-      </c>
-      <c r="B155">
-        <v>0</v>
-      </c>
-      <c r="C155">
-        <v>0</v>
-      </c>
-      <c r="D155">
-        <v>0</v>
+        <v>655</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D155"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D125"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/PA-PL_occupancy_pace_150day.xlsx
+++ b/PA-PL_occupancy_pace_150day.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D125"/>
+  <dimension ref="A1:D154"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -415,539 +415,539 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>07/06</v>
+        <v>07/13</v>
       </c>
       <c r="B2">
-        <v>228.15</v>
+        <v>242.96599999999998</v>
       </c>
       <c r="C2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D2">
-        <v>1825.2</v>
+        <v>1214.83</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>07/07</v>
+        <v>07/14</v>
       </c>
       <c r="B3">
-        <v>215.20555555555558</v>
+        <v>190.66750000000002</v>
       </c>
       <c r="C3">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D3">
-        <v>1936.8500000000001</v>
+        <v>762.6700000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>07/08</v>
+        <v>07/15</v>
       </c>
       <c r="B4">
-        <v>213.252</v>
+        <v>275.19666666666666</v>
       </c>
       <c r="C4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D4">
-        <v>1066.26</v>
+        <v>825.5899999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>07/09</v>
+        <v>07/16</v>
       </c>
       <c r="B5">
-        <v>245.2444444444444</v>
+        <v>286.97249999999997</v>
       </c>
       <c r="C5">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D5">
-        <v>2207.2</v>
+        <v>1147.8899999999999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>07/10</v>
+        <v>07/17</v>
       </c>
       <c r="B6">
-        <v>336.2</v>
+        <v>336.07666666666665</v>
       </c>
       <c r="C6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D6">
-        <v>3698.2</v>
+        <v>4032.9199999999996</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>07/11</v>
+        <v>07/18</v>
       </c>
       <c r="B7">
-        <v>324.82</v>
+        <v>300.97470588235296</v>
       </c>
       <c r="C7">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D7">
-        <v>3248.2</v>
+        <v>5116.570000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>07/12</v>
+        <v>07/19</v>
       </c>
       <c r="B8">
-        <v>243.8</v>
+        <v>269.775</v>
       </c>
       <c r="C8">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D8">
-        <v>975.2</v>
+        <v>2697.75</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>07/13</v>
+        <v>07/20</v>
       </c>
       <c r="B9">
-        <v>212.86499999999998</v>
+        <v>330.75</v>
       </c>
       <c r="C9">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D9">
-        <v>425.72999999999996</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>07/14</v>
+        <v>07/21</v>
       </c>
       <c r="B10">
-        <v>201.1</v>
+        <v>348.6666666666667</v>
       </c>
       <c r="C10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10">
-        <v>402.2</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>07/15</v>
+        <v>07/22</v>
       </c>
       <c r="B11">
-        <v>275.19666666666666</v>
+        <v>309</v>
       </c>
       <c r="C11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D11">
-        <v>825.5899999999999</v>
+        <v>309</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>07/16</v>
+        <v>07/23</v>
       </c>
       <c r="B12">
-        <v>262.6</v>
+        <v>349</v>
       </c>
       <c r="C12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D12">
-        <v>525.2</v>
+        <v>349</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>07/17</v>
+        <v>07/24</v>
       </c>
       <c r="B13">
-        <v>347.64</v>
+        <v>362.4</v>
       </c>
       <c r="C13">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D13">
-        <v>2781.12</v>
+        <v>1812</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>07/18</v>
+        <v>07/25</v>
       </c>
       <c r="B14">
-        <v>311.59</v>
+        <v>358</v>
       </c>
       <c r="C14">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D14">
-        <v>4050.6699999999996</v>
+        <v>2506</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>07/19</v>
+        <v>07/26</v>
       </c>
       <c r="B15">
-        <v>264.34375</v>
+        <v>254</v>
       </c>
       <c r="C15">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D15">
-        <v>2114.75</v>
+        <v>508</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>07/20</v>
+        <v>07/27</v>
       </c>
       <c r="B16">
-        <v>316.3333333333333</v>
+        <v>327.5</v>
       </c>
       <c r="C16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D16">
-        <v>949</v>
+        <v>655</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>07/21</v>
+        <v>07/28</v>
       </c>
       <c r="B17">
-        <v>339.5</v>
+        <v>326.5</v>
       </c>
       <c r="C17">
         <v>2</v>
       </c>
       <c r="D17">
-        <v>679</v>
+        <v>653</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>07/22</v>
+        <v>07/29</v>
       </c>
       <c r="B18">
-        <v>0</v>
+        <v>392.6666666666667</v>
       </c>
       <c r="C18">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>07/23</v>
+        <v>07/30</v>
       </c>
       <c r="B19">
-        <v>349</v>
+        <v>436</v>
       </c>
       <c r="C19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D19">
-        <v>349</v>
+        <v>872</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>07/24</v>
+        <v>07/31</v>
       </c>
       <c r="B20">
-        <v>362.4</v>
+        <v>431.1666666666667</v>
       </c>
       <c r="C20">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D20">
-        <v>1812</v>
+        <v>5174</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>07/25</v>
+        <v>08/01</v>
       </c>
       <c r="B21">
-        <v>360.3333333333333</v>
+        <v>430</v>
       </c>
       <c r="C21">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="D21">
-        <v>2162</v>
+        <v>6450</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>07/26</v>
+        <v>08/02</v>
       </c>
       <c r="B22">
-        <v>247</v>
+        <v>360.4</v>
       </c>
       <c r="C22">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D22">
-        <v>247</v>
+        <v>1802</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>07/27</v>
+        <v>08/03</v>
       </c>
       <c r="B23">
-        <v>327.5</v>
+        <v>363.75</v>
       </c>
       <c r="C23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D23">
-        <v>655</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>07/28</v>
+        <v>08/04</v>
       </c>
       <c r="B24">
-        <v>326.5</v>
+        <v>336</v>
       </c>
       <c r="C24">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D24">
-        <v>653</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>07/29</v>
+        <v>08/05</v>
       </c>
       <c r="B25">
-        <v>386</v>
+        <v>289</v>
       </c>
       <c r="C25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D25">
-        <v>772</v>
+        <v>289</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>07/30</v>
+        <v>08/06</v>
       </c>
       <c r="B26">
-        <v>464</v>
+        <v>289</v>
       </c>
       <c r="C26">
         <v>1</v>
       </c>
       <c r="D26">
-        <v>464</v>
+        <v>289</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>07/31</v>
+        <v>08/07</v>
       </c>
       <c r="B27">
-        <v>434.61538461538464</v>
+        <v>485.7</v>
       </c>
       <c r="C27">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D27">
-        <v>5650</v>
+        <v>2914.2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>08/01</v>
+        <v>08/08</v>
       </c>
       <c r="B28">
-        <v>432.875</v>
+        <v>474.5057142857143</v>
       </c>
       <c r="C28">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D28">
-        <v>6926</v>
+        <v>3321.54</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>08/02</v>
+        <v>08/09</v>
       </c>
       <c r="B29">
-        <v>360.4</v>
+        <v>297.546</v>
       </c>
       <c r="C29">
         <v>5</v>
       </c>
       <c r="D29">
-        <v>1802</v>
+        <v>1487.73</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>08/03</v>
+        <v>08/10</v>
       </c>
       <c r="B30">
-        <v>363.75</v>
+        <v>281.486</v>
       </c>
       <c r="C30">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D30">
-        <v>1455</v>
+        <v>1407.43</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>08/04</v>
+        <v>08/11</v>
       </c>
       <c r="B31">
-        <v>336</v>
+        <v>296.2</v>
       </c>
       <c r="C31">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D31">
-        <v>1344</v>
+        <v>592.4</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>08/05</v>
+        <v>08/12</v>
       </c>
       <c r="B32">
-        <v>289</v>
+        <v>358</v>
       </c>
       <c r="C32">
         <v>1</v>
       </c>
       <c r="D32">
-        <v>289</v>
+        <v>358</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>08/06</v>
+        <v>08/13</v>
       </c>
       <c r="B33">
-        <v>289</v>
+        <v>0</v>
       </c>
       <c r="C33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D33">
-        <v>289</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>08/07</v>
+        <v>08/14</v>
       </c>
       <c r="B34">
-        <v>462.7</v>
+        <v>391</v>
       </c>
       <c r="C34">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D34">
-        <v>1850.8</v>
+        <v>391</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>08/08</v>
+        <v>08/15</v>
       </c>
       <c r="B35">
-        <v>484.21000000000004</v>
+        <v>411.4</v>
       </c>
       <c r="C35">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D35">
-        <v>2905.26</v>
+        <v>822.8</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>08/09</v>
+        <v>08/16</v>
       </c>
       <c r="B36">
-        <v>239.80000000000004</v>
+        <v>328.49</v>
       </c>
       <c r="C36">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D36">
-        <v>719.4000000000001</v>
+        <v>328.49</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>08/10</v>
+        <v>08/17</v>
       </c>
       <c r="B37">
-        <v>215.2</v>
+        <v>487</v>
       </c>
       <c r="C37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D37">
-        <v>430.4</v>
+        <v>487</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>08/11</v>
+        <v>08/18</v>
       </c>
       <c r="B38">
-        <v>371</v>
+        <v>310.148</v>
       </c>
       <c r="C38">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D38">
-        <v>371</v>
+        <v>1550.74</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>08/12</v>
+        <v>08/19</v>
       </c>
       <c r="B39">
-        <v>358</v>
+        <v>311.43333333333334</v>
       </c>
       <c r="C39">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D39">
-        <v>358</v>
+        <v>934.3</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>08/13</v>
+        <v>08/20</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -961,91 +961,91 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>08/14</v>
+        <v>08/21</v>
       </c>
       <c r="B41">
-        <v>0</v>
+        <v>417.3</v>
       </c>
       <c r="C41">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D41">
-        <v>0</v>
+        <v>834.6</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>08/15</v>
+        <v>08/22</v>
       </c>
       <c r="B42">
-        <v>433.8</v>
+        <v>417.3</v>
       </c>
       <c r="C42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D42">
-        <v>433.8</v>
+        <v>834.6</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>08/16</v>
+        <v>08/23</v>
       </c>
       <c r="B43">
-        <v>328.49</v>
+        <v>399.525</v>
       </c>
       <c r="C43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D43">
-        <v>328.49</v>
+        <v>799.05</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>08/17</v>
+        <v>08/24</v>
       </c>
       <c r="B44">
-        <v>487</v>
+        <v>360.3666666666666</v>
       </c>
       <c r="C44">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D44">
-        <v>487</v>
+        <v>1081.1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>08/18</v>
+        <v>08/25</v>
       </c>
       <c r="B45">
-        <v>380.6</v>
+        <v>325.3625</v>
       </c>
       <c r="C45">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D45">
-        <v>761.2</v>
+        <v>1301.45</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>08/19</v>
+        <v>08/26</v>
       </c>
       <c r="B46">
-        <v>330.3</v>
+        <v>0</v>
       </c>
       <c r="C46">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D46">
-        <v>330.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>08/20</v>
+        <v>08/27</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -1059,77 +1059,77 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>08/21</v>
+        <v>08/28</v>
       </c>
       <c r="B48">
-        <v>417.3</v>
+        <v>289.85</v>
       </c>
       <c r="C48">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D48">
-        <v>834.6</v>
+        <v>289.85</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>08/22</v>
+        <v>08/29</v>
       </c>
       <c r="B49">
-        <v>417.3</v>
+        <v>279.70000000000005</v>
       </c>
       <c r="C49">
         <v>2</v>
       </c>
       <c r="D49">
-        <v>834.6</v>
+        <v>559.4000000000001</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>08/23</v>
+        <v>08/30</v>
       </c>
       <c r="B50">
-        <v>368.05</v>
+        <v>195.16</v>
       </c>
       <c r="C50">
         <v>1</v>
       </c>
       <c r="D50">
-        <v>368.05</v>
+        <v>195.16</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>08/24</v>
+        <v>08/31</v>
       </c>
       <c r="B51">
-        <v>342.54999999999995</v>
+        <v>294</v>
       </c>
       <c r="C51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D51">
-        <v>685.0999999999999</v>
+        <v>294</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>08/25</v>
+        <v>09/01</v>
       </c>
       <c r="B52">
-        <v>309.48333333333335</v>
+        <v>266</v>
       </c>
       <c r="C52">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D52">
-        <v>928.45</v>
+        <v>266</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>08/26</v>
+        <v>09/02</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -1143,7 +1143,7 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>08/27</v>
+        <v>09/03</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -1157,7 +1157,7 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>08/28</v>
+        <v>09/04</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -1171,343 +1171,343 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>08/29</v>
+        <v>09/05</v>
       </c>
       <c r="B56">
-        <v>0</v>
+        <v>385</v>
       </c>
       <c r="C56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D56">
-        <v>0</v>
+        <v>385</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>08/30</v>
+        <v>09/06</v>
       </c>
       <c r="B57">
-        <v>0</v>
+        <v>398</v>
       </c>
       <c r="C57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D57">
-        <v>0</v>
+        <v>398</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>08/31</v>
+        <v>09/07</v>
       </c>
       <c r="B58">
-        <v>294</v>
+        <v>230.75</v>
       </c>
       <c r="C58">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D58">
-        <v>294</v>
+        <v>923</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>09/01</v>
+        <v>09/08</v>
       </c>
       <c r="B59">
-        <v>266</v>
+        <v>215.2</v>
       </c>
       <c r="C59">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D59">
-        <v>266</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>09/02</v>
+        <v>09/09</v>
       </c>
       <c r="B60">
-        <v>0</v>
+        <v>219</v>
       </c>
       <c r="C60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D60">
-        <v>0</v>
+        <v>219</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>09/03</v>
+        <v>09/10</v>
       </c>
       <c r="B61">
-        <v>0</v>
+        <v>219</v>
       </c>
       <c r="C61">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D61">
-        <v>0</v>
+        <v>219</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>09/04</v>
+        <v>09/11</v>
       </c>
       <c r="B62">
-        <v>0</v>
+        <v>301</v>
       </c>
       <c r="C62">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D62">
-        <v>0</v>
+        <v>602</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>09/05</v>
+        <v>09/12</v>
       </c>
       <c r="B63">
-        <v>385</v>
+        <v>311</v>
       </c>
       <c r="C63">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D63">
-        <v>385</v>
+        <v>933</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>09/06</v>
+        <v>09/13</v>
       </c>
       <c r="B64">
-        <v>398</v>
+        <v>210.33333333333334</v>
       </c>
       <c r="C64">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D64">
-        <v>398</v>
+        <v>631</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>09/07</v>
+        <v>09/14</v>
       </c>
       <c r="B65">
-        <v>206</v>
+        <v>188</v>
       </c>
       <c r="C65">
         <v>1</v>
       </c>
       <c r="D65">
-        <v>206</v>
+        <v>188</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>09/08</v>
+        <v>09/15</v>
       </c>
       <c r="B66">
-        <v>181</v>
+        <v>0</v>
       </c>
       <c r="C66">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D66">
-        <v>181</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>09/09</v>
+        <v>09/16</v>
       </c>
       <c r="B67">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="C67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D67">
-        <v>0</v>
+        <v>210</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>09/10</v>
+        <v>09/17</v>
       </c>
       <c r="B68">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="C68">
         <v>1</v>
       </c>
       <c r="D68">
-        <v>219</v>
+        <v>210</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>09/11</v>
+        <v>09/18</v>
       </c>
       <c r="B69">
-        <v>301</v>
+        <v>310.29555555555555</v>
       </c>
       <c r="C69">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="D69">
-        <v>602</v>
+        <v>5585.32</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>09/12</v>
+        <v>09/19</v>
       </c>
       <c r="B70">
-        <v>311</v>
+        <v>305.17272727272723</v>
       </c>
       <c r="C70">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="D70">
-        <v>933</v>
+        <v>6713.799999999999</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>09/13</v>
+        <v>09/20</v>
       </c>
       <c r="B71">
-        <v>210.33333333333334</v>
+        <v>230.6</v>
       </c>
       <c r="C71">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D71">
-        <v>631</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>09/14</v>
+        <v>09/21</v>
       </c>
       <c r="B72">
-        <v>188</v>
+        <v>242</v>
       </c>
       <c r="C72">
         <v>1</v>
       </c>
       <c r="D72">
-        <v>188</v>
+        <v>242</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>09/15</v>
+        <v>09/22</v>
       </c>
       <c r="B73">
-        <v>0</v>
+        <v>251</v>
       </c>
       <c r="C73">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D73">
-        <v>0</v>
+        <v>251</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>09/16</v>
+        <v>09/23</v>
       </c>
       <c r="B74">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="C74">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D74">
-        <v>210</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>09/17</v>
+        <v>09/24</v>
       </c>
       <c r="B75">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="C75">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D75">
-        <v>210</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>09/18</v>
+        <v>09/25</v>
       </c>
       <c r="B76">
-        <v>310.29555555555555</v>
+        <v>395</v>
       </c>
       <c r="C76">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="D76">
-        <v>5585.32</v>
+        <v>2370</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>09/19</v>
+        <v>09/26</v>
       </c>
       <c r="B77">
-        <v>305.17272727272723</v>
+        <v>391.3333333333333</v>
       </c>
       <c r="C77">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="D77">
-        <v>6713.799999999999</v>
+        <v>3522</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>09/20</v>
+        <v>09/27</v>
       </c>
       <c r="B78">
-        <v>214</v>
+        <v>274.2857142857143</v>
       </c>
       <c r="C78">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D78">
-        <v>1070</v>
+        <v>1920</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>09/21</v>
+        <v>09/28</v>
       </c>
       <c r="B79">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="C79">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D79">
-        <v>160</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>09/22</v>
+        <v>09/29</v>
       </c>
       <c r="B80">
         <v>0</v>
@@ -1521,7 +1521,7 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>09/23</v>
+        <v>09/30</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -1535,77 +1535,77 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>09/24</v>
+        <v>10/01</v>
       </c>
       <c r="B82">
-        <v>0</v>
+        <v>195</v>
       </c>
       <c r="C82">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D82">
-        <v>0</v>
+        <v>390</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>09/25</v>
+        <v>10/02</v>
       </c>
       <c r="B83">
-        <v>395</v>
+        <v>322.15999999999997</v>
       </c>
       <c r="C83">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D83">
-        <v>2370</v>
+        <v>3221.6</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>09/26</v>
+        <v>10/03</v>
       </c>
       <c r="B84">
-        <v>391.3333333333333</v>
+        <v>314.40000000000003</v>
       </c>
       <c r="C84">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D84">
-        <v>3522</v>
+        <v>3458.4</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>09/27</v>
+        <v>10/04</v>
       </c>
       <c r="B85">
-        <v>274.2857142857143</v>
+        <v>199.5</v>
       </c>
       <c r="C85">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D85">
-        <v>1920</v>
+        <v>399</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>09/28</v>
+        <v>10/05</v>
       </c>
       <c r="B86">
-        <v>0</v>
+        <v>193.5</v>
       </c>
       <c r="C86">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D86">
-        <v>0</v>
+        <v>387</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>09/29</v>
+        <v>10/06</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -1619,7 +1619,7 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>09/30</v>
+        <v>10/07</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -1633,77 +1633,77 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>10/01</v>
+        <v>10/08</v>
       </c>
       <c r="B89">
-        <v>194</v>
+        <v>222.21</v>
       </c>
       <c r="C89">
         <v>1</v>
       </c>
       <c r="D89">
-        <v>194</v>
+        <v>222.21</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>10/02</v>
+        <v>10/09</v>
       </c>
       <c r="B90">
-        <v>322.16</v>
+        <v>387.23400000000004</v>
       </c>
       <c r="C90">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D90">
-        <v>3221.6000000000004</v>
+        <v>1936.17</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>10/03</v>
+        <v>10/10</v>
       </c>
       <c r="B91">
-        <v>319.64</v>
+        <v>384.5375</v>
       </c>
       <c r="C91">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D91">
-        <v>3196.4</v>
+        <v>1538.15</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>10/04</v>
+        <v>10/11</v>
       </c>
       <c r="B92">
-        <v>203</v>
+        <v>360</v>
       </c>
       <c r="C92">
         <v>1</v>
       </c>
       <c r="D92">
-        <v>203</v>
+        <v>360</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>10/05</v>
+        <v>10/12</v>
       </c>
       <c r="B93">
-        <v>193.5</v>
+        <v>0</v>
       </c>
       <c r="C93">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D93">
-        <v>387</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>10/06</v>
+        <v>10/13</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -1717,7 +1717,7 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>10/07</v>
+        <v>10/14</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -1731,7 +1731,7 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>10/08</v>
+        <v>10/15</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -1745,35 +1745,35 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>10/09</v>
+        <v>10/16</v>
       </c>
       <c r="B97">
-        <v>406.29999999999995</v>
+        <v>0</v>
       </c>
       <c r="C97">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D97">
-        <v>1218.8999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>10/10</v>
+        <v>10/17</v>
       </c>
       <c r="B98">
-        <v>396.3833333333334</v>
+        <v>0</v>
       </c>
       <c r="C98">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D98">
-        <v>1189.15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>10/11</v>
+        <v>10/18</v>
       </c>
       <c r="B99">
         <v>0</v>
@@ -1787,7 +1787,7 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>10/12</v>
+        <v>10/19</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>10/13</v>
+        <v>10/20</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -1815,7 +1815,7 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>10/14</v>
+        <v>10/21</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -1829,49 +1829,49 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>10/15</v>
+        <v>10/22</v>
       </c>
       <c r="B103">
-        <v>0</v>
+        <v>239.115</v>
       </c>
       <c r="C103">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D103">
-        <v>0</v>
+        <v>478.23</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>10/16</v>
+        <v>10/23</v>
       </c>
       <c r="B104">
-        <v>0</v>
+        <v>308.5</v>
       </c>
       <c r="C104">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D104">
-        <v>0</v>
+        <v>1851</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>10/17</v>
+        <v>10/24</v>
       </c>
       <c r="B105">
-        <v>0</v>
+        <v>313.6666666666667</v>
       </c>
       <c r="C105">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D105">
-        <v>0</v>
+        <v>1882</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>10/18</v>
+        <v>10/25</v>
       </c>
       <c r="B106">
         <v>0</v>
@@ -1885,7 +1885,7 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>10/19</v>
+        <v>10/26</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -1899,7 +1899,7 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>10/20</v>
+        <v>10/27</v>
       </c>
       <c r="B108">
         <v>0</v>
@@ -1913,77 +1913,77 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>10/21</v>
+        <v>10/28</v>
       </c>
       <c r="B109">
-        <v>0</v>
+        <v>135.15</v>
       </c>
       <c r="C109">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D109">
-        <v>0</v>
+        <v>135.15</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>10/22</v>
+        <v>10/29</v>
       </c>
       <c r="B110">
-        <v>239.115</v>
+        <v>144.5</v>
       </c>
       <c r="C110">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D110">
-        <v>478.23</v>
+        <v>144.5</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>10/23</v>
+        <v>10/30</v>
       </c>
       <c r="B111">
-        <v>308.5</v>
+        <v>289</v>
       </c>
       <c r="C111">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D111">
-        <v>1851</v>
+        <v>867</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>10/24</v>
+        <v>10/31</v>
       </c>
       <c r="B112">
-        <v>313.6666666666667</v>
+        <v>291</v>
       </c>
       <c r="C112">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D112">
-        <v>1882</v>
+        <v>873</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>10/25</v>
+        <v>11/01</v>
       </c>
       <c r="B113">
-        <v>0</v>
+        <v>219</v>
       </c>
       <c r="C113">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D113">
-        <v>0</v>
+        <v>219</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>10/26</v>
+        <v>11/02</v>
       </c>
       <c r="B114">
         <v>0</v>
@@ -1997,7 +1997,7 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>10/27</v>
+        <v>11/03</v>
       </c>
       <c r="B115">
         <v>0</v>
@@ -2011,77 +2011,77 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>10/28</v>
+        <v>11/04</v>
       </c>
       <c r="B116">
-        <v>135.15</v>
+        <v>0</v>
       </c>
       <c r="C116">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D116">
-        <v>135.15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>10/29</v>
+        <v>11/05</v>
       </c>
       <c r="B117">
-        <v>144.5</v>
+        <v>0</v>
       </c>
       <c r="C117">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D117">
-        <v>144.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>10/30</v>
+        <v>11/06</v>
       </c>
       <c r="B118">
-        <v>289</v>
+        <v>278.375</v>
       </c>
       <c r="C118">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D118">
-        <v>867</v>
+        <v>556.75</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>10/31</v>
+        <v>11/07</v>
       </c>
       <c r="B119">
-        <v>291</v>
+        <v>280.925</v>
       </c>
       <c r="C119">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D119">
-        <v>873</v>
+        <v>561.85</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>11/01</v>
+        <v>11/08</v>
       </c>
       <c r="B120">
-        <v>219</v>
+        <v>0</v>
       </c>
       <c r="C120">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D120">
-        <v>219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>11/02</v>
+        <v>11/09</v>
       </c>
       <c r="B121">
         <v>0</v>
@@ -2095,7 +2095,7 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>11/03</v>
+        <v>11/10</v>
       </c>
       <c r="B122">
         <v>0</v>
@@ -2109,7 +2109,7 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>11/04</v>
+        <v>11/11</v>
       </c>
       <c r="B123">
         <v>0</v>
@@ -2123,7 +2123,7 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>11/05</v>
+        <v>11/12</v>
       </c>
       <c r="B124">
         <v>0</v>
@@ -2137,21 +2137,427 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>11/06</v>
+        <v>11/13</v>
       </c>
       <c r="B125">
-        <v>327.5</v>
+        <v>0</v>
       </c>
       <c r="C125">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D125">
-        <v>655</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>11/14</v>
+      </c>
+      <c r="B126">
+        <v>0</v>
+      </c>
+      <c r="C126">
+        <v>0</v>
+      </c>
+      <c r="D126">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>11/15</v>
+      </c>
+      <c r="B127">
+        <v>0</v>
+      </c>
+      <c r="C127">
+        <v>0</v>
+      </c>
+      <c r="D127">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>11/16</v>
+      </c>
+      <c r="B128">
+        <v>0</v>
+      </c>
+      <c r="C128">
+        <v>0</v>
+      </c>
+      <c r="D128">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>11/17</v>
+      </c>
+      <c r="B129">
+        <v>0</v>
+      </c>
+      <c r="C129">
+        <v>0</v>
+      </c>
+      <c r="D129">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="str">
+        <v>11/18</v>
+      </c>
+      <c r="B130">
+        <v>0</v>
+      </c>
+      <c r="C130">
+        <v>0</v>
+      </c>
+      <c r="D130">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="str">
+        <v>11/19</v>
+      </c>
+      <c r="B131">
+        <v>0</v>
+      </c>
+      <c r="C131">
+        <v>0</v>
+      </c>
+      <c r="D131">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="str">
+        <v>11/20</v>
+      </c>
+      <c r="B132">
+        <v>0</v>
+      </c>
+      <c r="C132">
+        <v>0</v>
+      </c>
+      <c r="D132">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="str">
+        <v>11/21</v>
+      </c>
+      <c r="B133">
+        <v>0</v>
+      </c>
+      <c r="C133">
+        <v>0</v>
+      </c>
+      <c r="D133">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="str">
+        <v>11/22</v>
+      </c>
+      <c r="B134">
+        <v>0</v>
+      </c>
+      <c r="C134">
+        <v>0</v>
+      </c>
+      <c r="D134">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="str">
+        <v>11/23</v>
+      </c>
+      <c r="B135">
+        <v>0</v>
+      </c>
+      <c r="C135">
+        <v>0</v>
+      </c>
+      <c r="D135">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="str">
+        <v>11/24</v>
+      </c>
+      <c r="B136">
+        <v>0</v>
+      </c>
+      <c r="C136">
+        <v>0</v>
+      </c>
+      <c r="D136">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="str">
+        <v>11/25</v>
+      </c>
+      <c r="B137">
+        <v>0</v>
+      </c>
+      <c r="C137">
+        <v>0</v>
+      </c>
+      <c r="D137">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="str">
+        <v>11/26</v>
+      </c>
+      <c r="B138">
+        <v>0</v>
+      </c>
+      <c r="C138">
+        <v>0</v>
+      </c>
+      <c r="D138">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="str">
+        <v>11/27</v>
+      </c>
+      <c r="B139">
+        <v>0</v>
+      </c>
+      <c r="C139">
+        <v>0</v>
+      </c>
+      <c r="D139">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="str">
+        <v>11/28</v>
+      </c>
+      <c r="B140">
+        <v>0</v>
+      </c>
+      <c r="C140">
+        <v>0</v>
+      </c>
+      <c r="D140">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="str">
+        <v>11/29</v>
+      </c>
+      <c r="B141">
+        <v>0</v>
+      </c>
+      <c r="C141">
+        <v>0</v>
+      </c>
+      <c r="D141">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="str">
+        <v>11/30</v>
+      </c>
+      <c r="B142">
+        <v>0</v>
+      </c>
+      <c r="C142">
+        <v>0</v>
+      </c>
+      <c r="D142">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="str">
+        <v>12/01</v>
+      </c>
+      <c r="B143">
+        <v>0</v>
+      </c>
+      <c r="C143">
+        <v>0</v>
+      </c>
+      <c r="D143">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="str">
+        <v>12/02</v>
+      </c>
+      <c r="B144">
+        <v>0</v>
+      </c>
+      <c r="C144">
+        <v>0</v>
+      </c>
+      <c r="D144">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="str">
+        <v>12/03</v>
+      </c>
+      <c r="B145">
+        <v>0</v>
+      </c>
+      <c r="C145">
+        <v>0</v>
+      </c>
+      <c r="D145">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="str">
+        <v>12/04</v>
+      </c>
+      <c r="B146">
+        <v>0</v>
+      </c>
+      <c r="C146">
+        <v>0</v>
+      </c>
+      <c r="D146">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="str">
+        <v>12/05</v>
+      </c>
+      <c r="B147">
+        <v>0</v>
+      </c>
+      <c r="C147">
+        <v>0</v>
+      </c>
+      <c r="D147">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="str">
+        <v>12/06</v>
+      </c>
+      <c r="B148">
+        <v>0</v>
+      </c>
+      <c r="C148">
+        <v>0</v>
+      </c>
+      <c r="D148">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="str">
+        <v>12/07</v>
+      </c>
+      <c r="B149">
+        <v>0</v>
+      </c>
+      <c r="C149">
+        <v>0</v>
+      </c>
+      <c r="D149">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="str">
+        <v>12/08</v>
+      </c>
+      <c r="B150">
+        <v>0</v>
+      </c>
+      <c r="C150">
+        <v>0</v>
+      </c>
+      <c r="D150">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="str">
+        <v>12/09</v>
+      </c>
+      <c r="B151">
+        <v>0</v>
+      </c>
+      <c r="C151">
+        <v>0</v>
+      </c>
+      <c r="D151">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="str">
+        <v>12/10</v>
+      </c>
+      <c r="B152">
+        <v>0</v>
+      </c>
+      <c r="C152">
+        <v>0</v>
+      </c>
+      <c r="D152">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="str">
+        <v>12/11</v>
+      </c>
+      <c r="B153">
+        <v>0</v>
+      </c>
+      <c r="C153">
+        <v>0</v>
+      </c>
+      <c r="D153">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="str">
+        <v>12/12</v>
+      </c>
+      <c r="B154">
+        <v>0</v>
+      </c>
+      <c r="C154">
+        <v>0</v>
+      </c>
+      <c r="D154">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D125"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D154"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/PA-PL_occupancy_pace_150day.xlsx
+++ b/PA-PL_occupancy_pace_150day.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D154"/>
+  <dimension ref="A1:D155"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -415,903 +415,903 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>07/13</v>
+        <v>07/27</v>
       </c>
       <c r="B2">
-        <v>242.96599999999998</v>
+        <v>262.392</v>
       </c>
       <c r="C2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D2">
-        <v>1214.83</v>
+        <v>2623.92</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>07/14</v>
+        <v>07/28</v>
       </c>
       <c r="B3">
-        <v>190.66750000000002</v>
+        <v>290</v>
       </c>
       <c r="C3">
         <v>4</v>
       </c>
       <c r="D3">
-        <v>762.6700000000001</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>07/15</v>
+        <v>07/29</v>
       </c>
       <c r="B4">
-        <v>275.19666666666666</v>
+        <v>274.43142857142857</v>
       </c>
       <c r="C4">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D4">
-        <v>825.5899999999999</v>
+        <v>1921.02</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>07/16</v>
+        <v>07/30</v>
       </c>
       <c r="B5">
-        <v>286.97249999999997</v>
+        <v>334.546</v>
       </c>
       <c r="C5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D5">
-        <v>1147.8899999999999</v>
+        <v>1672.73</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>07/17</v>
+        <v>07/31</v>
       </c>
       <c r="B6">
-        <v>336.07666666666665</v>
+        <v>393.46666666666664</v>
       </c>
       <c r="C6">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D6">
-        <v>4032.9199999999996</v>
+        <v>5902</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>07/18</v>
+        <v>08/01</v>
       </c>
       <c r="B7">
-        <v>300.97470588235296</v>
+        <v>402.2352941176471</v>
       </c>
       <c r="C7">
         <v>17</v>
       </c>
       <c r="D7">
-        <v>5116.570000000001</v>
+        <v>6838</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>07/19</v>
+        <v>08/02</v>
       </c>
       <c r="B8">
-        <v>269.775</v>
+        <v>349.57142857142856</v>
       </c>
       <c r="C8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D8">
-        <v>2697.75</v>
+        <v>2447</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>07/20</v>
+        <v>08/03</v>
       </c>
       <c r="B9">
-        <v>330.75</v>
+        <v>332.4166666666667</v>
       </c>
       <c r="C9">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D9">
-        <v>1323</v>
+        <v>1994.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>07/21</v>
+        <v>08/04</v>
       </c>
       <c r="B10">
-        <v>348.6666666666667</v>
+        <v>320.33000000000004</v>
       </c>
       <c r="C10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D10">
-        <v>1046</v>
+        <v>1601.65</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>07/22</v>
+        <v>08/05</v>
       </c>
       <c r="B11">
-        <v>309</v>
+        <v>288.55</v>
       </c>
       <c r="C11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D11">
-        <v>309</v>
+        <v>865.65</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>07/23</v>
+        <v>08/06</v>
       </c>
       <c r="B12">
-        <v>349</v>
+        <v>275.5</v>
       </c>
       <c r="C12">
         <v>1</v>
       </c>
       <c r="D12">
-        <v>349</v>
+        <v>275.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>07/24</v>
+        <v>08/07</v>
       </c>
       <c r="B13">
-        <v>362.4</v>
+        <v>445.404</v>
       </c>
       <c r="C13">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D13">
-        <v>1812</v>
+        <v>4454.04</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>07/25</v>
+        <v>08/08</v>
       </c>
       <c r="B14">
-        <v>358</v>
+        <v>445.1983333333333</v>
       </c>
       <c r="C14">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D14">
-        <v>2506</v>
+        <v>5342.38</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>07/26</v>
+        <v>08/09</v>
       </c>
       <c r="B15">
-        <v>254</v>
+        <v>308.9614285714286</v>
       </c>
       <c r="C15">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D15">
-        <v>508</v>
+        <v>2162.73</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>07/27</v>
+        <v>08/10</v>
       </c>
       <c r="B16">
-        <v>327.5</v>
+        <v>257.8128571428571</v>
       </c>
       <c r="C16">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D16">
-        <v>655</v>
+        <v>1804.69</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>07/28</v>
+        <v>08/11</v>
       </c>
       <c r="B17">
-        <v>326.5</v>
+        <v>284.4</v>
       </c>
       <c r="C17">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D17">
-        <v>653</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>07/29</v>
+        <v>08/12</v>
       </c>
       <c r="B18">
-        <v>392.6666666666667</v>
+        <v>358</v>
       </c>
       <c r="C18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D18">
-        <v>1178</v>
+        <v>358</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>07/30</v>
+        <v>08/13</v>
       </c>
       <c r="B19">
-        <v>436</v>
+        <v>0</v>
       </c>
       <c r="C19">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D19">
-        <v>872</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>07/31</v>
+        <v>08/14</v>
       </c>
       <c r="B20">
-        <v>431.1666666666667</v>
+        <v>357</v>
       </c>
       <c r="C20">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D20">
-        <v>5174</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>08/01</v>
+        <v>08/15</v>
       </c>
       <c r="B21">
-        <v>430</v>
+        <v>366.76</v>
       </c>
       <c r="C21">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="D21">
-        <v>6450</v>
+        <v>1833.8</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>08/02</v>
+        <v>08/16</v>
       </c>
       <c r="B22">
-        <v>360.4</v>
+        <v>329.745</v>
       </c>
       <c r="C22">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D22">
-        <v>1802</v>
+        <v>659.49</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>08/03</v>
+        <v>08/17</v>
       </c>
       <c r="B23">
-        <v>363.75</v>
+        <v>367.3333333333333</v>
       </c>
       <c r="C23">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D23">
-        <v>1455</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>08/04</v>
+        <v>08/18</v>
       </c>
       <c r="B24">
-        <v>336</v>
+        <v>296.3914285714286</v>
       </c>
       <c r="C24">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D24">
-        <v>1344</v>
+        <v>2074.7400000000002</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>08/05</v>
+        <v>08/19</v>
       </c>
       <c r="B25">
-        <v>289</v>
+        <v>295.86</v>
       </c>
       <c r="C25">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D25">
-        <v>289</v>
+        <v>1479.3</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>08/06</v>
+        <v>08/20</v>
       </c>
       <c r="B26">
-        <v>289</v>
+        <v>353.55</v>
       </c>
       <c r="C26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D26">
-        <v>289</v>
+        <v>707.1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>08/07</v>
+        <v>08/21</v>
       </c>
       <c r="B27">
-        <v>485.7</v>
+        <v>432.025</v>
       </c>
       <c r="C27">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D27">
-        <v>2914.2</v>
+        <v>1728.1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>08/08</v>
+        <v>08/22</v>
       </c>
       <c r="B28">
-        <v>474.5057142857143</v>
+        <v>417.3</v>
       </c>
       <c r="C28">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D28">
-        <v>3321.54</v>
+        <v>834.6</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>08/09</v>
+        <v>08/23</v>
       </c>
       <c r="B29">
-        <v>297.546</v>
+        <v>367.15999999999997</v>
       </c>
       <c r="C29">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D29">
-        <v>1487.73</v>
+        <v>1468.6399999999999</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>08/10</v>
+        <v>08/24</v>
       </c>
       <c r="B30">
-        <v>281.486</v>
+        <v>338.21999999999997</v>
       </c>
       <c r="C30">
         <v>5</v>
       </c>
       <c r="D30">
-        <v>1407.43</v>
+        <v>1691.1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>08/11</v>
+        <v>08/25</v>
       </c>
       <c r="B31">
-        <v>296.2</v>
+        <v>307.21000000000004</v>
       </c>
       <c r="C31">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D31">
-        <v>592.4</v>
+        <v>1536.0500000000002</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>08/12</v>
+        <v>08/26</v>
       </c>
       <c r="B32">
-        <v>358</v>
+        <v>217.175</v>
       </c>
       <c r="C32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D32">
-        <v>358</v>
+        <v>434.35</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>08/13</v>
+        <v>08/27</v>
       </c>
       <c r="B33">
-        <v>0</v>
+        <v>239</v>
       </c>
       <c r="C33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D33">
-        <v>0</v>
+        <v>239</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>08/14</v>
+        <v>08/28</v>
       </c>
       <c r="B34">
-        <v>391</v>
+        <v>312.925</v>
       </c>
       <c r="C34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D34">
-        <v>391</v>
+        <v>625.85</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>08/15</v>
+        <v>08/29</v>
       </c>
       <c r="B35">
-        <v>411.4</v>
+        <v>358.61</v>
       </c>
       <c r="C35">
         <v>2</v>
       </c>
       <c r="D35">
-        <v>822.8</v>
+        <v>717.22</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>08/16</v>
+        <v>08/30</v>
       </c>
       <c r="B36">
-        <v>328.49</v>
+        <v>335</v>
       </c>
       <c r="C36">
         <v>1</v>
       </c>
       <c r="D36">
-        <v>328.49</v>
+        <v>335</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>08/17</v>
+        <v>08/31</v>
       </c>
       <c r="B37">
-        <v>487</v>
+        <v>294</v>
       </c>
       <c r="C37">
         <v>1</v>
       </c>
       <c r="D37">
-        <v>487</v>
+        <v>294</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>08/18</v>
+        <v>09/01</v>
       </c>
       <c r="B38">
-        <v>310.148</v>
+        <v>266</v>
       </c>
       <c r="C38">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D38">
-        <v>1550.74</v>
+        <v>266</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>08/19</v>
+        <v>09/02</v>
       </c>
       <c r="B39">
-        <v>311.43333333333334</v>
+        <v>184</v>
       </c>
       <c r="C39">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D39">
-        <v>934.3</v>
+        <v>368</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>08/20</v>
+        <v>09/03</v>
       </c>
       <c r="B40">
-        <v>0</v>
+        <v>230.4</v>
       </c>
       <c r="C40">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D40">
-        <v>0</v>
+        <v>691.2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>08/21</v>
+        <v>09/04</v>
       </c>
       <c r="B41">
-        <v>417.3</v>
+        <v>409</v>
       </c>
       <c r="C41">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D41">
-        <v>834.6</v>
+        <v>409</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>08/22</v>
+        <v>09/05</v>
       </c>
       <c r="B42">
-        <v>417.3</v>
+        <v>398</v>
       </c>
       <c r="C42">
         <v>2</v>
       </c>
       <c r="D42">
-        <v>834.6</v>
+        <v>796</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>08/23</v>
+        <v>09/06</v>
       </c>
       <c r="B43">
-        <v>399.525</v>
+        <v>398</v>
       </c>
       <c r="C43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D43">
-        <v>799.05</v>
+        <v>398</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>08/24</v>
+        <v>09/07</v>
       </c>
       <c r="B44">
-        <v>360.3666666666666</v>
+        <v>221.4</v>
       </c>
       <c r="C44">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D44">
-        <v>1081.1</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>08/25</v>
+        <v>09/08</v>
       </c>
       <c r="B45">
-        <v>325.3625</v>
+        <v>210</v>
       </c>
       <c r="C45">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D45">
-        <v>1301.45</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>08/26</v>
+        <v>09/09</v>
       </c>
       <c r="B46">
-        <v>0</v>
+        <v>219</v>
       </c>
       <c r="C46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D46">
-        <v>0</v>
+        <v>219</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>08/27</v>
+        <v>09/10</v>
       </c>
       <c r="B47">
-        <v>0</v>
+        <v>219</v>
       </c>
       <c r="C47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D47">
-        <v>0</v>
+        <v>219</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>08/28</v>
+        <v>09/11</v>
       </c>
       <c r="B48">
-        <v>289.85</v>
+        <v>250</v>
       </c>
       <c r="C48">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D48">
-        <v>289.85</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>08/29</v>
+        <v>09/12</v>
       </c>
       <c r="B49">
-        <v>279.70000000000005</v>
+        <v>266.8333333333333</v>
       </c>
       <c r="C49">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D49">
-        <v>559.4000000000001</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>08/30</v>
+        <v>09/13</v>
       </c>
       <c r="B50">
-        <v>195.16</v>
+        <v>210.33333333333334</v>
       </c>
       <c r="C50">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D50">
-        <v>195.16</v>
+        <v>631</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>08/31</v>
+        <v>09/14</v>
       </c>
       <c r="B51">
-        <v>294</v>
+        <v>188</v>
       </c>
       <c r="C51">
         <v>1</v>
       </c>
       <c r="D51">
-        <v>294</v>
+        <v>188</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>09/01</v>
+        <v>09/15</v>
       </c>
       <c r="B52">
-        <v>266</v>
+        <v>0</v>
       </c>
       <c r="C52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D52">
-        <v>266</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>09/02</v>
+        <v>09/16</v>
       </c>
       <c r="B53">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="C53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D53">
-        <v>0</v>
+        <v>210</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>09/03</v>
+        <v>09/17</v>
       </c>
       <c r="B54">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="C54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D54">
-        <v>0</v>
+        <v>210</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>09/04</v>
+        <v>09/18</v>
       </c>
       <c r="B55">
-        <v>0</v>
+        <v>309.8063157894737</v>
       </c>
       <c r="C55">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="D55">
-        <v>0</v>
+        <v>5886.32</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>09/05</v>
+        <v>09/19</v>
       </c>
       <c r="B56">
-        <v>385</v>
+        <v>304.59999999999997</v>
       </c>
       <c r="C56">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="D56">
-        <v>385</v>
+        <v>7005.799999999999</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>09/06</v>
+        <v>09/20</v>
       </c>
       <c r="B57">
-        <v>398</v>
+        <v>229.99857142857144</v>
       </c>
       <c r="C57">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D57">
-        <v>398</v>
+        <v>1609.99</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>09/07</v>
+        <v>09/21</v>
       </c>
       <c r="B58">
-        <v>230.75</v>
+        <v>242</v>
       </c>
       <c r="C58">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D58">
-        <v>923</v>
+        <v>242</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>09/08</v>
+        <v>09/22</v>
       </c>
       <c r="B59">
-        <v>215.2</v>
+        <v>251</v>
       </c>
       <c r="C59">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D59">
-        <v>1076</v>
+        <v>251</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>09/09</v>
+        <v>09/23</v>
       </c>
       <c r="B60">
-        <v>219</v>
+        <v>0</v>
       </c>
       <c r="C60">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D60">
-        <v>219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>09/10</v>
+        <v>09/24</v>
       </c>
       <c r="B61">
-        <v>219</v>
+        <v>0</v>
       </c>
       <c r="C61">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D61">
-        <v>219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>09/11</v>
+        <v>09/25</v>
       </c>
       <c r="B62">
-        <v>301</v>
+        <v>387.14285714285717</v>
       </c>
       <c r="C62">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D62">
-        <v>602</v>
+        <v>2710</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>09/12</v>
+        <v>09/26</v>
       </c>
       <c r="B63">
-        <v>311</v>
+        <v>384.3</v>
       </c>
       <c r="C63">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D63">
-        <v>933</v>
+        <v>3843</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>09/13</v>
+        <v>09/27</v>
       </c>
       <c r="B64">
-        <v>210.33333333333334</v>
+        <v>274.2857142857143</v>
       </c>
       <c r="C64">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D64">
-        <v>631</v>
+        <v>1920</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>09/14</v>
+        <v>09/28</v>
       </c>
       <c r="B65">
-        <v>188</v>
+        <v>0</v>
       </c>
       <c r="C65">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D65">
-        <v>188</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>09/15</v>
+        <v>09/29</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -1325,105 +1325,105 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>09/16</v>
+        <v>09/30</v>
       </c>
       <c r="B67">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="C67">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D67">
-        <v>210</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>09/17</v>
+        <v>10/01</v>
       </c>
       <c r="B68">
-        <v>210</v>
+        <v>194</v>
       </c>
       <c r="C68">
         <v>1</v>
       </c>
       <c r="D68">
-        <v>210</v>
+        <v>194</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>09/18</v>
+        <v>10/02</v>
       </c>
       <c r="B69">
-        <v>310.29555555555555</v>
+        <v>322.16</v>
       </c>
       <c r="C69">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D69">
-        <v>5585.32</v>
+        <v>3221.6000000000004</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>09/19</v>
+        <v>10/03</v>
       </c>
       <c r="B70">
-        <v>305.17272727272723</v>
+        <v>314.40000000000003</v>
       </c>
       <c r="C70">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="D70">
-        <v>6713.799999999999</v>
+        <v>3458.4</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>09/20</v>
+        <v>10/04</v>
       </c>
       <c r="B71">
-        <v>230.6</v>
+        <v>199.5</v>
       </c>
       <c r="C71">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D71">
-        <v>1153</v>
+        <v>399</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>09/21</v>
+        <v>10/05</v>
       </c>
       <c r="B72">
-        <v>242</v>
+        <v>193.5</v>
       </c>
       <c r="C72">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D72">
-        <v>242</v>
+        <v>387</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>09/22</v>
+        <v>10/06</v>
       </c>
       <c r="B73">
-        <v>251</v>
+        <v>0</v>
       </c>
       <c r="C73">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D73">
-        <v>251</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>09/23</v>
+        <v>10/07</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -1437,63 +1437,63 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>09/24</v>
+        <v>10/08</v>
       </c>
       <c r="B75">
-        <v>0</v>
+        <v>222.21</v>
       </c>
       <c r="C75">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D75">
-        <v>0</v>
+        <v>222.21</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>09/25</v>
+        <v>10/09</v>
       </c>
       <c r="B76">
-        <v>395</v>
+        <v>366.52833333333336</v>
       </c>
       <c r="C76">
         <v>6</v>
       </c>
       <c r="D76">
-        <v>2370</v>
+        <v>2199.17</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>09/26</v>
+        <v>10/10</v>
       </c>
       <c r="B77">
-        <v>391.3333333333333</v>
+        <v>358.03000000000003</v>
       </c>
       <c r="C77">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D77">
-        <v>3522</v>
+        <v>1790.15</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>09/27</v>
+        <v>10/11</v>
       </c>
       <c r="B78">
-        <v>274.2857142857143</v>
+        <v>336</v>
       </c>
       <c r="C78">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D78">
-        <v>1920</v>
+        <v>672</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>09/28</v>
+        <v>10/12</v>
       </c>
       <c r="B79">
         <v>0</v>
@@ -1507,7 +1507,7 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>09/29</v>
+        <v>10/13</v>
       </c>
       <c r="B80">
         <v>0</v>
@@ -1521,7 +1521,7 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>09/30</v>
+        <v>10/14</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -1535,77 +1535,77 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>10/01</v>
+        <v>10/15</v>
       </c>
       <c r="B82">
-        <v>195</v>
+        <v>250.5</v>
       </c>
       <c r="C82">
         <v>2</v>
       </c>
       <c r="D82">
-        <v>390</v>
+        <v>501</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>10/02</v>
+        <v>10/16</v>
       </c>
       <c r="B83">
-        <v>322.15999999999997</v>
+        <v>358.1666666666667</v>
       </c>
       <c r="C83">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D83">
-        <v>3221.6</v>
+        <v>2149</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>10/03</v>
+        <v>10/17</v>
       </c>
       <c r="B84">
-        <v>314.40000000000003</v>
+        <v>363</v>
       </c>
       <c r="C84">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D84">
-        <v>3458.4</v>
+        <v>1815</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>10/04</v>
+        <v>10/18</v>
       </c>
       <c r="B85">
-        <v>199.5</v>
+        <v>261</v>
       </c>
       <c r="C85">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D85">
-        <v>399</v>
+        <v>261</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>10/05</v>
+        <v>10/19</v>
       </c>
       <c r="B86">
-        <v>193.5</v>
+        <v>0</v>
       </c>
       <c r="C86">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D86">
-        <v>387</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>10/06</v>
+        <v>10/20</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -1619,77 +1619,77 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>10/07</v>
+        <v>10/21</v>
       </c>
       <c r="B88">
-        <v>0</v>
+        <v>149</v>
       </c>
       <c r="C88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D88">
-        <v>0</v>
+        <v>149</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>10/08</v>
+        <v>10/22</v>
       </c>
       <c r="B89">
-        <v>222.21</v>
+        <v>211.74333333333334</v>
       </c>
       <c r="C89">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D89">
-        <v>222.21</v>
+        <v>635.23</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>10/09</v>
+        <v>10/23</v>
       </c>
       <c r="B90">
-        <v>387.23400000000004</v>
+        <v>292.1111111111111</v>
       </c>
       <c r="C90">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D90">
-        <v>1936.17</v>
+        <v>2629</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>10/10</v>
+        <v>10/24</v>
       </c>
       <c r="B91">
-        <v>384.5375</v>
+        <v>296.44444444444446</v>
       </c>
       <c r="C91">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D91">
-        <v>1538.15</v>
+        <v>2668</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>10/11</v>
+        <v>10/25</v>
       </c>
       <c r="B92">
-        <v>360</v>
+        <v>0</v>
       </c>
       <c r="C92">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D92">
-        <v>360</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>10/12</v>
+        <v>10/26</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -1703,7 +1703,7 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>10/13</v>
+        <v>10/27</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -1717,91 +1717,91 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>10/14</v>
+        <v>10/28</v>
       </c>
       <c r="B95">
-        <v>0</v>
+        <v>135.15</v>
       </c>
       <c r="C95">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D95">
-        <v>0</v>
+        <v>135.15</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>10/15</v>
+        <v>10/29</v>
       </c>
       <c r="B96">
-        <v>0</v>
+        <v>144.5</v>
       </c>
       <c r="C96">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D96">
-        <v>0</v>
+        <v>144.5</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>10/16</v>
+        <v>10/30</v>
       </c>
       <c r="B97">
-        <v>0</v>
+        <v>289</v>
       </c>
       <c r="C97">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D97">
-        <v>0</v>
+        <v>867</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>10/17</v>
+        <v>10/31</v>
       </c>
       <c r="B98">
-        <v>0</v>
+        <v>291</v>
       </c>
       <c r="C98">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D98">
-        <v>0</v>
+        <v>873</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>10/18</v>
+        <v>11/01</v>
       </c>
       <c r="B99">
-        <v>0</v>
+        <v>224</v>
       </c>
       <c r="C99">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D99">
-        <v>0</v>
+        <v>448</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>10/19</v>
+        <v>11/02</v>
       </c>
       <c r="B100">
-        <v>0</v>
+        <v>229</v>
       </c>
       <c r="C100">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D100">
-        <v>0</v>
+        <v>229</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>10/20</v>
+        <v>11/03</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -1815,7 +1815,7 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>10/21</v>
+        <v>11/04</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -1829,49 +1829,49 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>10/22</v>
+        <v>11/05</v>
       </c>
       <c r="B103">
-        <v>239.115</v>
+        <v>0</v>
       </c>
       <c r="C103">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D103">
-        <v>478.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>10/23</v>
+        <v>11/06</v>
       </c>
       <c r="B104">
-        <v>308.5</v>
+        <v>278.375</v>
       </c>
       <c r="C104">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D104">
-        <v>1851</v>
+        <v>556.75</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>10/24</v>
+        <v>11/07</v>
       </c>
       <c r="B105">
-        <v>313.6666666666667</v>
+        <v>280.925</v>
       </c>
       <c r="C105">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D105">
-        <v>1882</v>
+        <v>561.85</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>10/25</v>
+        <v>11/08</v>
       </c>
       <c r="B106">
         <v>0</v>
@@ -1885,7 +1885,7 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>10/26</v>
+        <v>11/09</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -1899,7 +1899,7 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>10/27</v>
+        <v>11/10</v>
       </c>
       <c r="B108">
         <v>0</v>
@@ -1913,77 +1913,77 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>10/28</v>
+        <v>11/11</v>
       </c>
       <c r="B109">
-        <v>135.15</v>
+        <v>0</v>
       </c>
       <c r="C109">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D109">
-        <v>135.15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>10/29</v>
+        <v>11/12</v>
       </c>
       <c r="B110">
-        <v>144.5</v>
+        <v>0</v>
       </c>
       <c r="C110">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D110">
-        <v>144.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>10/30</v>
+        <v>11/13</v>
       </c>
       <c r="B111">
-        <v>289</v>
+        <v>0</v>
       </c>
       <c r="C111">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D111">
-        <v>867</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>10/31</v>
+        <v>11/14</v>
       </c>
       <c r="B112">
-        <v>291</v>
+        <v>0</v>
       </c>
       <c r="C112">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D112">
-        <v>873</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>11/01</v>
+        <v>11/15</v>
       </c>
       <c r="B113">
-        <v>219</v>
+        <v>0</v>
       </c>
       <c r="C113">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D113">
-        <v>219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>11/02</v>
+        <v>11/16</v>
       </c>
       <c r="B114">
         <v>0</v>
@@ -1997,7 +1997,7 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>11/03</v>
+        <v>11/17</v>
       </c>
       <c r="B115">
         <v>0</v>
@@ -2011,7 +2011,7 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>11/04</v>
+        <v>11/18</v>
       </c>
       <c r="B116">
         <v>0</v>
@@ -2025,7 +2025,7 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>11/05</v>
+        <v>11/19</v>
       </c>
       <c r="B117">
         <v>0</v>
@@ -2039,35 +2039,35 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>11/06</v>
+        <v>11/20</v>
       </c>
       <c r="B118">
-        <v>278.375</v>
+        <v>0</v>
       </c>
       <c r="C118">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D118">
-        <v>556.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>11/07</v>
+        <v>11/21</v>
       </c>
       <c r="B119">
-        <v>280.925</v>
+        <v>0</v>
       </c>
       <c r="C119">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D119">
-        <v>561.85</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>11/08</v>
+        <v>11/22</v>
       </c>
       <c r="B120">
         <v>0</v>
@@ -2081,7 +2081,7 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>11/09</v>
+        <v>11/23</v>
       </c>
       <c r="B121">
         <v>0</v>
@@ -2095,7 +2095,7 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>11/10</v>
+        <v>11/24</v>
       </c>
       <c r="B122">
         <v>0</v>
@@ -2109,7 +2109,7 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>11/11</v>
+        <v>11/25</v>
       </c>
       <c r="B123">
         <v>0</v>
@@ -2123,7 +2123,7 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>11/12</v>
+        <v>11/26</v>
       </c>
       <c r="B124">
         <v>0</v>
@@ -2137,7 +2137,7 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>11/13</v>
+        <v>11/27</v>
       </c>
       <c r="B125">
         <v>0</v>
@@ -2151,7 +2151,7 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>11/14</v>
+        <v>11/28</v>
       </c>
       <c r="B126">
         <v>0</v>
@@ -2165,7 +2165,7 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>11/15</v>
+        <v>11/29</v>
       </c>
       <c r="B127">
         <v>0</v>
@@ -2179,7 +2179,7 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>11/16</v>
+        <v>11/30</v>
       </c>
       <c r="B128">
         <v>0</v>
@@ -2193,7 +2193,7 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>11/17</v>
+        <v>12/01</v>
       </c>
       <c r="B129">
         <v>0</v>
@@ -2207,7 +2207,7 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>11/18</v>
+        <v>12/02</v>
       </c>
       <c r="B130">
         <v>0</v>
@@ -2221,7 +2221,7 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>11/19</v>
+        <v>12/03</v>
       </c>
       <c r="B131">
         <v>0</v>
@@ -2235,7 +2235,7 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>11/20</v>
+        <v>12/04</v>
       </c>
       <c r="B132">
         <v>0</v>
@@ -2249,7 +2249,7 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>11/21</v>
+        <v>12/05</v>
       </c>
       <c r="B133">
         <v>0</v>
@@ -2263,7 +2263,7 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>11/22</v>
+        <v>12/06</v>
       </c>
       <c r="B134">
         <v>0</v>
@@ -2277,7 +2277,7 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>11/23</v>
+        <v>12/07</v>
       </c>
       <c r="B135">
         <v>0</v>
@@ -2291,7 +2291,7 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>11/24</v>
+        <v>12/08</v>
       </c>
       <c r="B136">
         <v>0</v>
@@ -2305,7 +2305,7 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>11/25</v>
+        <v>12/09</v>
       </c>
       <c r="B137">
         <v>0</v>
@@ -2319,7 +2319,7 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>11/26</v>
+        <v>12/10</v>
       </c>
       <c r="B138">
         <v>0</v>
@@ -2333,7 +2333,7 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>11/27</v>
+        <v>12/11</v>
       </c>
       <c r="B139">
         <v>0</v>
@@ -2347,7 +2347,7 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>11/28</v>
+        <v>12/12</v>
       </c>
       <c r="B140">
         <v>0</v>
@@ -2361,7 +2361,7 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>11/29</v>
+        <v>12/13</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -2375,7 +2375,7 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>11/30</v>
+        <v>12/14</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -2389,7 +2389,7 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>12/01</v>
+        <v>12/15</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -2403,7 +2403,7 @@
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>12/02</v>
+        <v>12/16</v>
       </c>
       <c r="B144">
         <v>0</v>
@@ -2417,7 +2417,7 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>12/03</v>
+        <v>12/17</v>
       </c>
       <c r="B145">
         <v>0</v>
@@ -2431,7 +2431,7 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>12/04</v>
+        <v>12/18</v>
       </c>
       <c r="B146">
         <v>0</v>
@@ -2445,7 +2445,7 @@
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>12/05</v>
+        <v>12/19</v>
       </c>
       <c r="B147">
         <v>0</v>
@@ -2459,7 +2459,7 @@
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>12/06</v>
+        <v>12/20</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -2473,7 +2473,7 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>12/07</v>
+        <v>12/21</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -2487,7 +2487,7 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>12/08</v>
+        <v>12/22</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -2501,7 +2501,7 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>12/09</v>
+        <v>12/23</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -2515,7 +2515,7 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>12/10</v>
+        <v>12/24</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -2529,7 +2529,7 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>12/11</v>
+        <v>12/25</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -2543,7 +2543,7 @@
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>12/12</v>
+        <v>12/26</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -2552,12 +2552,26 @@
         <v>0</v>
       </c>
       <c r="D154">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="str">
+        <v>12/27</v>
+      </c>
+      <c r="B155">
+        <v>0</v>
+      </c>
+      <c r="C155">
+        <v>0</v>
+      </c>
+      <c r="D155">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D154"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D155"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/PA-PL_occupancy_pace_150day.xlsx
+++ b/PA-PL_occupancy_pace_150day.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D155"/>
+  <dimension ref="A1:D124"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -415,819 +415,819 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>07/27</v>
+        <v>08/03</v>
       </c>
       <c r="B2">
-        <v>262.392</v>
+        <v>259.28499999999997</v>
       </c>
       <c r="C2">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D2">
-        <v>2623.92</v>
+        <v>3629.99</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>07/28</v>
+        <v>08/04</v>
       </c>
       <c r="B3">
-        <v>290</v>
+        <v>266.461</v>
       </c>
       <c r="C3">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D3">
-        <v>1160</v>
+        <v>2664.61</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>07/29</v>
+        <v>08/05</v>
       </c>
       <c r="B4">
-        <v>274.43142857142857</v>
+        <v>245.8714285714286</v>
       </c>
       <c r="C4">
         <v>7</v>
       </c>
       <c r="D4">
-        <v>1921.02</v>
+        <v>1721.1000000000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>07/30</v>
+        <v>08/06</v>
       </c>
       <c r="B5">
-        <v>334.546</v>
+        <v>235.83333333333334</v>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D5">
-        <v>1672.73</v>
+        <v>707.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>07/31</v>
+        <v>08/07</v>
       </c>
       <c r="B6">
-        <v>393.46666666666664</v>
+        <v>361.756875</v>
       </c>
       <c r="C6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D6">
-        <v>5902</v>
+        <v>5788.11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>08/01</v>
+        <v>08/08</v>
       </c>
       <c r="B7">
-        <v>402.2352941176471</v>
+        <v>349.18909090909096</v>
       </c>
       <c r="C7">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D7">
-        <v>6838</v>
+        <v>7682.160000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>08/02</v>
+        <v>08/09</v>
       </c>
       <c r="B8">
-        <v>349.57142857142856</v>
+        <v>261.44235294117647</v>
       </c>
       <c r="C8">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="D8">
-        <v>2447</v>
+        <v>4444.5199999999995</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>08/03</v>
+        <v>08/10</v>
       </c>
       <c r="B9">
-        <v>332.4166666666667</v>
+        <v>257.8128571428571</v>
       </c>
       <c r="C9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D9">
-        <v>1994.5</v>
+        <v>1804.69</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>08/04</v>
+        <v>08/11</v>
       </c>
       <c r="B10">
-        <v>320.33000000000004</v>
+        <v>284.4</v>
       </c>
       <c r="C10">
         <v>5</v>
       </c>
       <c r="D10">
-        <v>1601.65</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>08/05</v>
+        <v>08/12</v>
       </c>
       <c r="B11">
-        <v>288.55</v>
+        <v>310.5</v>
       </c>
       <c r="C11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D11">
-        <v>865.65</v>
+        <v>621</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>08/06</v>
+        <v>08/13</v>
       </c>
       <c r="B12">
-        <v>275.5</v>
+        <v>296</v>
       </c>
       <c r="C12">
         <v>1</v>
       </c>
       <c r="D12">
-        <v>275.5</v>
+        <v>296</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>08/07</v>
+        <v>08/14</v>
       </c>
       <c r="B13">
-        <v>445.404</v>
+        <v>342.25</v>
       </c>
       <c r="C13">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D13">
-        <v>4454.04</v>
+        <v>4107</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>08/08</v>
+        <v>08/15</v>
       </c>
       <c r="B14">
-        <v>445.1983333333333</v>
+        <v>341.6666666666667</v>
       </c>
       <c r="C14">
         <v>12</v>
       </c>
       <c r="D14">
-        <v>5342.38</v>
+        <v>4100</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>08/09</v>
+        <v>08/16</v>
       </c>
       <c r="B15">
-        <v>308.9614285714286</v>
+        <v>333.2</v>
       </c>
       <c r="C15">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D15">
-        <v>2162.73</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>08/10</v>
+        <v>08/17</v>
       </c>
       <c r="B16">
-        <v>257.8128571428571</v>
+        <v>330.14285714285717</v>
       </c>
       <c r="C16">
         <v>7</v>
       </c>
       <c r="D16">
-        <v>1804.69</v>
+        <v>2311</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>08/11</v>
+        <v>08/18</v>
       </c>
       <c r="B17">
-        <v>284.4</v>
+        <v>289.0925</v>
       </c>
       <c r="C17">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D17">
-        <v>1422</v>
+        <v>2312.74</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>08/12</v>
+        <v>08/19</v>
       </c>
       <c r="B18">
-        <v>358</v>
+        <v>295.86</v>
       </c>
       <c r="C18">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D18">
-        <v>358</v>
+        <v>1479.3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>08/13</v>
+        <v>08/20</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>353.55</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>707.1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>08/14</v>
+        <v>08/21</v>
       </c>
       <c r="B20">
-        <v>357</v>
+        <v>420.41999999999996</v>
       </c>
       <c r="C20">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D20">
-        <v>1428</v>
+        <v>2102.1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>08/15</v>
+        <v>08/22</v>
       </c>
       <c r="B21">
-        <v>366.76</v>
+        <v>390.875</v>
       </c>
       <c r="C21">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D21">
-        <v>1833.8</v>
+        <v>1563.5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>08/16</v>
+        <v>08/23</v>
       </c>
       <c r="B22">
-        <v>329.745</v>
+        <v>355.24</v>
       </c>
       <c r="C22">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D22">
-        <v>659.49</v>
+        <v>2131.44</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>08/17</v>
+        <v>08/24</v>
       </c>
       <c r="B23">
-        <v>367.3333333333333</v>
+        <v>324.01666666666665</v>
       </c>
       <c r="C23">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D23">
-        <v>1102</v>
+        <v>1944.1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>08/18</v>
+        <v>08/25</v>
       </c>
       <c r="B24">
-        <v>296.3914285714286</v>
+        <v>294.4357142857143</v>
       </c>
       <c r="C24">
         <v>7</v>
       </c>
       <c r="D24">
-        <v>2074.7400000000002</v>
+        <v>2061.05</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>08/19</v>
+        <v>08/26</v>
       </c>
       <c r="B25">
-        <v>295.86</v>
+        <v>244.2225</v>
       </c>
       <c r="C25">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D25">
-        <v>1479.3</v>
+        <v>976.89</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>08/20</v>
+        <v>08/27</v>
       </c>
       <c r="B26">
-        <v>353.55</v>
+        <v>274.5</v>
       </c>
       <c r="C26">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D26">
-        <v>707.1</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>08/21</v>
+        <v>08/28</v>
       </c>
       <c r="B27">
-        <v>432.025</v>
+        <v>323.2642857142857</v>
       </c>
       <c r="C27">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D27">
-        <v>1728.1</v>
+        <v>2262.85</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>08/22</v>
+        <v>08/29</v>
       </c>
       <c r="B28">
-        <v>417.3</v>
+        <v>350.0314285714286</v>
       </c>
       <c r="C28">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D28">
-        <v>834.6</v>
+        <v>2450.2200000000003</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>08/23</v>
+        <v>08/30</v>
       </c>
       <c r="B29">
-        <v>367.15999999999997</v>
+        <v>292</v>
       </c>
       <c r="C29">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D29">
-        <v>1468.6399999999999</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>08/24</v>
+        <v>08/31</v>
       </c>
       <c r="B30">
-        <v>338.21999999999997</v>
+        <v>261.3333333333333</v>
       </c>
       <c r="C30">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D30">
-        <v>1691.1</v>
+        <v>784</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>08/25</v>
+        <v>09/01</v>
       </c>
       <c r="B31">
-        <v>307.21000000000004</v>
+        <v>257.5</v>
       </c>
       <c r="C31">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D31">
-        <v>1536.0500000000002</v>
+        <v>515</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>08/26</v>
+        <v>09/02</v>
       </c>
       <c r="B32">
-        <v>217.175</v>
+        <v>211.5</v>
       </c>
       <c r="C32">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D32">
-        <v>434.35</v>
+        <v>846</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>08/27</v>
+        <v>09/03</v>
       </c>
       <c r="B33">
-        <v>239</v>
+        <v>238.3</v>
       </c>
       <c r="C33">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D33">
-        <v>239</v>
+        <v>953.2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>08/28</v>
+        <v>09/04</v>
       </c>
       <c r="B34">
-        <v>312.925</v>
+        <v>354</v>
       </c>
       <c r="C34">
         <v>2</v>
       </c>
       <c r="D34">
-        <v>625.85</v>
+        <v>708</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>08/29</v>
+        <v>09/05</v>
       </c>
       <c r="B35">
-        <v>358.61</v>
+        <v>380.6225</v>
       </c>
       <c r="C35">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D35">
-        <v>717.22</v>
+        <v>1522.49</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>08/30</v>
+        <v>09/06</v>
       </c>
       <c r="B36">
-        <v>335</v>
+        <v>418.3</v>
       </c>
       <c r="C36">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D36">
-        <v>335</v>
+        <v>2091.5</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>08/31</v>
+        <v>09/07</v>
       </c>
       <c r="B37">
-        <v>294</v>
+        <v>221.4</v>
       </c>
       <c r="C37">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D37">
-        <v>294</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>09/01</v>
+        <v>09/08</v>
       </c>
       <c r="B38">
-        <v>266</v>
+        <v>215.57142857142858</v>
       </c>
       <c r="C38">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D38">
-        <v>266</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>09/02</v>
+        <v>09/09</v>
       </c>
       <c r="B39">
-        <v>184</v>
+        <v>234</v>
       </c>
       <c r="C39">
         <v>2</v>
       </c>
       <c r="D39">
-        <v>368</v>
+        <v>468</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>09/03</v>
+        <v>09/10</v>
       </c>
       <c r="B40">
-        <v>230.4</v>
+        <v>219</v>
       </c>
       <c r="C40">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D40">
-        <v>691.2</v>
+        <v>219</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>09/04</v>
+        <v>09/11</v>
       </c>
       <c r="B41">
-        <v>409</v>
+        <v>266.1666666666667</v>
       </c>
       <c r="C41">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D41">
-        <v>409</v>
+        <v>1597</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>09/05</v>
+        <v>09/12</v>
       </c>
       <c r="B42">
-        <v>398</v>
+        <v>275.5</v>
       </c>
       <c r="C42">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D42">
-        <v>796</v>
+        <v>2204</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>09/06</v>
+        <v>09/13</v>
       </c>
       <c r="B43">
-        <v>398</v>
+        <v>209.75</v>
       </c>
       <c r="C43">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D43">
-        <v>398</v>
+        <v>839</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>09/07</v>
+        <v>09/14</v>
       </c>
       <c r="B44">
-        <v>221.4</v>
+        <v>188</v>
       </c>
       <c r="C44">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D44">
-        <v>1107</v>
+        <v>188</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>09/08</v>
+        <v>09/15</v>
       </c>
       <c r="B45">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="C45">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D45">
-        <v>1260</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>09/09</v>
+        <v>09/16</v>
       </c>
       <c r="B46">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="C46">
         <v>1</v>
       </c>
       <c r="D46">
-        <v>219</v>
+        <v>210</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>09/10</v>
+        <v>09/17</v>
       </c>
       <c r="B47">
-        <v>219</v>
+        <v>222.385</v>
       </c>
       <c r="C47">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D47">
-        <v>219</v>
+        <v>444.77</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>09/11</v>
+        <v>09/18</v>
       </c>
       <c r="B48">
-        <v>250</v>
+        <v>309.08380952380946</v>
       </c>
       <c r="C48">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="D48">
-        <v>1250</v>
+        <v>6490.759999999999</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>09/12</v>
+        <v>09/19</v>
       </c>
       <c r="B49">
-        <v>266.8333333333333</v>
+        <v>304.075</v>
       </c>
       <c r="C49">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="D49">
-        <v>1601</v>
+        <v>7297.799999999999</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>09/13</v>
+        <v>09/20</v>
       </c>
       <c r="B50">
-        <v>210.33333333333334</v>
+        <v>225.37375</v>
       </c>
       <c r="C50">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D50">
-        <v>631</v>
+        <v>1802.99</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>09/14</v>
+        <v>09/21</v>
       </c>
       <c r="B51">
-        <v>188</v>
+        <v>242</v>
       </c>
       <c r="C51">
         <v>1</v>
       </c>
       <c r="D51">
-        <v>188</v>
+        <v>242</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>09/15</v>
+        <v>09/22</v>
       </c>
       <c r="B52">
-        <v>0</v>
+        <v>251</v>
       </c>
       <c r="C52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D52">
-        <v>0</v>
+        <v>251</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>09/16</v>
+        <v>09/23</v>
       </c>
       <c r="B53">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="C53">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D53">
-        <v>210</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>09/17</v>
+        <v>09/24</v>
       </c>
       <c r="B54">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="C54">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D54">
-        <v>210</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>09/18</v>
+        <v>09/25</v>
       </c>
       <c r="B55">
-        <v>309.8063157894737</v>
+        <v>328.1818181818182</v>
       </c>
       <c r="C55">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D55">
-        <v>5886.32</v>
+        <v>3610</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>09/19</v>
+        <v>09/26</v>
       </c>
       <c r="B56">
-        <v>304.59999999999997</v>
+        <v>336.9714285714286</v>
       </c>
       <c r="C56">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="D56">
-        <v>7005.799999999999</v>
+        <v>4717.6</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>09/20</v>
+        <v>09/27</v>
       </c>
       <c r="B57">
-        <v>229.99857142857144</v>
+        <v>274.2857142857143</v>
       </c>
       <c r="C57">
         <v>7</v>
       </c>
       <c r="D57">
-        <v>1609.99</v>
+        <v>1920</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>09/21</v>
+        <v>09/28</v>
       </c>
       <c r="B58">
-        <v>242</v>
+        <v>0</v>
       </c>
       <c r="C58">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D58">
-        <v>242</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>09/22</v>
+        <v>09/29</v>
       </c>
       <c r="B59">
-        <v>251</v>
+        <v>0</v>
       </c>
       <c r="C59">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D59">
-        <v>251</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>09/23</v>
+        <v>09/30</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -1241,77 +1241,77 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>09/24</v>
+        <v>10/01</v>
       </c>
       <c r="B61">
-        <v>0</v>
+        <v>194</v>
       </c>
       <c r="C61">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D61">
-        <v>0</v>
+        <v>194</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>09/25</v>
+        <v>10/02</v>
       </c>
       <c r="B62">
-        <v>387.14285714285717</v>
+        <v>322.16</v>
       </c>
       <c r="C62">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D62">
-        <v>2710</v>
+        <v>3221.6000000000004</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>09/26</v>
+        <v>10/03</v>
       </c>
       <c r="B63">
-        <v>384.3</v>
+        <v>314.40000000000003</v>
       </c>
       <c r="C63">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D63">
-        <v>3843</v>
+        <v>3458.4</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>09/27</v>
+        <v>10/04</v>
       </c>
       <c r="B64">
-        <v>274.2857142857143</v>
+        <v>199.5</v>
       </c>
       <c r="C64">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D64">
-        <v>1920</v>
+        <v>399</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>09/28</v>
+        <v>10/05</v>
       </c>
       <c r="B65">
-        <v>0</v>
+        <v>193.5</v>
       </c>
       <c r="C65">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D65">
-        <v>0</v>
+        <v>387</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>09/29</v>
+        <v>10/06</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -1325,7 +1325,7 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>09/30</v>
+        <v>10/07</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -1339,175 +1339,175 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>10/01</v>
+        <v>10/08</v>
       </c>
       <c r="B68">
-        <v>194</v>
+        <v>222.21</v>
       </c>
       <c r="C68">
         <v>1</v>
       </c>
       <c r="D68">
-        <v>194</v>
+        <v>222.21</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>10/02</v>
+        <v>10/09</v>
       </c>
       <c r="B69">
-        <v>322.16</v>
+        <v>366.52833333333336</v>
       </c>
       <c r="C69">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D69">
-        <v>3221.6000000000004</v>
+        <v>2199.17</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>10/03</v>
+        <v>10/10</v>
       </c>
       <c r="B70">
-        <v>314.40000000000003</v>
+        <v>358.03000000000003</v>
       </c>
       <c r="C70">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D70">
-        <v>3458.4</v>
+        <v>1790.15</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>10/04</v>
+        <v>10/11</v>
       </c>
       <c r="B71">
-        <v>199.5</v>
+        <v>336</v>
       </c>
       <c r="C71">
         <v>2</v>
       </c>
       <c r="D71">
-        <v>399</v>
+        <v>672</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>10/05</v>
+        <v>10/12</v>
       </c>
       <c r="B72">
-        <v>193.5</v>
+        <v>192</v>
       </c>
       <c r="C72">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D72">
-        <v>387</v>
+        <v>192</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>10/06</v>
+        <v>10/13</v>
       </c>
       <c r="B73">
-        <v>0</v>
+        <v>184</v>
       </c>
       <c r="C73">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D73">
-        <v>0</v>
+        <v>184</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>10/07</v>
+        <v>10/14</v>
       </c>
       <c r="B74">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="C74">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D74">
-        <v>0</v>
+        <v>190</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>10/08</v>
+        <v>10/15</v>
       </c>
       <c r="B75">
-        <v>222.21</v>
+        <v>0</v>
       </c>
       <c r="C75">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D75">
-        <v>222.21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>10/09</v>
+        <v>10/16</v>
       </c>
       <c r="B76">
-        <v>366.52833333333336</v>
+        <v>352.25</v>
       </c>
       <c r="C76">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D76">
-        <v>2199.17</v>
+        <v>2818</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>10/10</v>
+        <v>10/17</v>
       </c>
       <c r="B77">
-        <v>358.03000000000003</v>
+        <v>352.9</v>
       </c>
       <c r="C77">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D77">
-        <v>1790.15</v>
+        <v>3529</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>10/11</v>
+        <v>10/18</v>
       </c>
       <c r="B78">
-        <v>336</v>
+        <v>263</v>
       </c>
       <c r="C78">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D78">
-        <v>672</v>
+        <v>789</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>10/12</v>
+        <v>10/19</v>
       </c>
       <c r="B79">
-        <v>0</v>
+        <v>229</v>
       </c>
       <c r="C79">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D79">
-        <v>0</v>
+        <v>229</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>10/13</v>
+        <v>10/20</v>
       </c>
       <c r="B80">
         <v>0</v>
@@ -1521,91 +1521,91 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>10/14</v>
+        <v>10/21</v>
       </c>
       <c r="B81">
-        <v>0</v>
+        <v>149</v>
       </c>
       <c r="C81">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D81">
-        <v>0</v>
+        <v>149</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>10/15</v>
+        <v>10/22</v>
       </c>
       <c r="B82">
-        <v>250.5</v>
+        <v>220.846</v>
       </c>
       <c r="C82">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D82">
-        <v>501</v>
+        <v>1104.23</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>10/16</v>
+        <v>10/23</v>
       </c>
       <c r="B83">
-        <v>358.1666666666667</v>
+        <v>296.46153846153845</v>
       </c>
       <c r="C83">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D83">
-        <v>2149</v>
+        <v>3854</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>10/17</v>
+        <v>10/24</v>
       </c>
       <c r="B84">
-        <v>363</v>
+        <v>301.3636363636364</v>
       </c>
       <c r="C84">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D84">
-        <v>1815</v>
+        <v>3315</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>10/18</v>
+        <v>10/25</v>
       </c>
       <c r="B85">
-        <v>261</v>
+        <v>232</v>
       </c>
       <c r="C85">
         <v>1</v>
       </c>
       <c r="D85">
-        <v>261</v>
+        <v>232</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>10/19</v>
+        <v>10/26</v>
       </c>
       <c r="B86">
-        <v>0</v>
+        <v>229</v>
       </c>
       <c r="C86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D86">
-        <v>0</v>
+        <v>229</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>10/20</v>
+        <v>10/27</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -1619,91 +1619,91 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>10/21</v>
+        <v>10/28</v>
       </c>
       <c r="B88">
-        <v>149</v>
+        <v>135.15</v>
       </c>
       <c r="C88">
         <v>1</v>
       </c>
       <c r="D88">
-        <v>149</v>
+        <v>135.15</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>10/22</v>
+        <v>10/29</v>
       </c>
       <c r="B89">
-        <v>211.74333333333334</v>
+        <v>164.25</v>
       </c>
       <c r="C89">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D89">
-        <v>635.23</v>
+        <v>328.5</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>10/23</v>
+        <v>10/30</v>
       </c>
       <c r="B90">
-        <v>292.1111111111111</v>
+        <v>273.5</v>
       </c>
       <c r="C90">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D90">
-        <v>2629</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>10/24</v>
+        <v>10/31</v>
       </c>
       <c r="B91">
-        <v>296.44444444444446</v>
+        <v>291</v>
       </c>
       <c r="C91">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D91">
-        <v>2668</v>
+        <v>873</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>10/25</v>
+        <v>11/01</v>
       </c>
       <c r="B92">
-        <v>0</v>
+        <v>224</v>
       </c>
       <c r="C92">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D92">
-        <v>0</v>
+        <v>448</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>10/26</v>
+        <v>11/02</v>
       </c>
       <c r="B93">
-        <v>0</v>
+        <v>229</v>
       </c>
       <c r="C93">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D93">
-        <v>0</v>
+        <v>229</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>10/27</v>
+        <v>11/03</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -1717,91 +1717,91 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>10/28</v>
+        <v>11/04</v>
       </c>
       <c r="B95">
-        <v>135.15</v>
+        <v>0</v>
       </c>
       <c r="C95">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D95">
-        <v>135.15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>10/29</v>
+        <v>11/05</v>
       </c>
       <c r="B96">
-        <v>144.5</v>
+        <v>0</v>
       </c>
       <c r="C96">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D96">
-        <v>144.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>10/30</v>
+        <v>11/06</v>
       </c>
       <c r="B97">
-        <v>289</v>
+        <v>278.375</v>
       </c>
       <c r="C97">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D97">
-        <v>867</v>
+        <v>556.75</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>10/31</v>
+        <v>11/07</v>
       </c>
       <c r="B98">
-        <v>291</v>
+        <v>280.925</v>
       </c>
       <c r="C98">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D98">
-        <v>873</v>
+        <v>561.85</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>11/01</v>
+        <v>11/08</v>
       </c>
       <c r="B99">
-        <v>224</v>
+        <v>0</v>
       </c>
       <c r="C99">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D99">
-        <v>448</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>11/02</v>
+        <v>11/09</v>
       </c>
       <c r="B100">
-        <v>229</v>
+        <v>0</v>
       </c>
       <c r="C100">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D100">
-        <v>229</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>11/03</v>
+        <v>11/10</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -1815,7 +1815,7 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>11/04</v>
+        <v>11/11</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -1829,7 +1829,7 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>11/05</v>
+        <v>11/12</v>
       </c>
       <c r="B103">
         <v>0</v>
@@ -1843,35 +1843,35 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>11/06</v>
+        <v>11/13</v>
       </c>
       <c r="B104">
-        <v>278.375</v>
+        <v>0</v>
       </c>
       <c r="C104">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D104">
-        <v>556.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>11/07</v>
+        <v>11/14</v>
       </c>
       <c r="B105">
-        <v>280.925</v>
+        <v>0</v>
       </c>
       <c r="C105">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D105">
-        <v>561.85</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>11/08</v>
+        <v>11/15</v>
       </c>
       <c r="B106">
         <v>0</v>
@@ -1885,7 +1885,7 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>11/09</v>
+        <v>11/16</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -1899,7 +1899,7 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>11/10</v>
+        <v>11/17</v>
       </c>
       <c r="B108">
         <v>0</v>
@@ -1913,7 +1913,7 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>11/11</v>
+        <v>11/18</v>
       </c>
       <c r="B109">
         <v>0</v>
@@ -1927,7 +1927,7 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>11/12</v>
+        <v>11/19</v>
       </c>
       <c r="B110">
         <v>0</v>
@@ -1941,7 +1941,7 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>11/13</v>
+        <v>11/20</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -1955,7 +1955,7 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>11/14</v>
+        <v>11/21</v>
       </c>
       <c r="B112">
         <v>0</v>
@@ -1969,7 +1969,7 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>11/15</v>
+        <v>11/22</v>
       </c>
       <c r="B113">
         <v>0</v>
@@ -1983,7 +1983,7 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>11/16</v>
+        <v>11/23</v>
       </c>
       <c r="B114">
         <v>0</v>
@@ -1997,7 +1997,7 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>11/17</v>
+        <v>11/24</v>
       </c>
       <c r="B115">
         <v>0</v>
@@ -2011,7 +2011,7 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>11/18</v>
+        <v>11/25</v>
       </c>
       <c r="B116">
         <v>0</v>
@@ -2025,7 +2025,7 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>11/19</v>
+        <v>11/26</v>
       </c>
       <c r="B117">
         <v>0</v>
@@ -2039,7 +2039,7 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>11/20</v>
+        <v>11/27</v>
       </c>
       <c r="B118">
         <v>0</v>
@@ -2053,7 +2053,7 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>11/21</v>
+        <v>11/28</v>
       </c>
       <c r="B119">
         <v>0</v>
@@ -2067,7 +2067,7 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>11/22</v>
+        <v>11/29</v>
       </c>
       <c r="B120">
         <v>0</v>
@@ -2081,7 +2081,7 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>11/23</v>
+        <v>11/30</v>
       </c>
       <c r="B121">
         <v>0</v>
@@ -2095,7 +2095,7 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>11/24</v>
+        <v>12/01</v>
       </c>
       <c r="B122">
         <v>0</v>
@@ -2109,7 +2109,7 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>11/25</v>
+        <v>12/02</v>
       </c>
       <c r="B123">
         <v>0</v>
@@ -2123,7 +2123,7 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>11/26</v>
+        <v>12/03</v>
       </c>
       <c r="B124">
         <v>0</v>
@@ -2132,446 +2132,12 @@
         <v>0</v>
       </c>
       <c r="D124">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="str">
-        <v>11/27</v>
-      </c>
-      <c r="B125">
-        <v>0</v>
-      </c>
-      <c r="C125">
-        <v>0</v>
-      </c>
-      <c r="D125">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="str">
-        <v>11/28</v>
-      </c>
-      <c r="B126">
-        <v>0</v>
-      </c>
-      <c r="C126">
-        <v>0</v>
-      </c>
-      <c r="D126">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="str">
-        <v>11/29</v>
-      </c>
-      <c r="B127">
-        <v>0</v>
-      </c>
-      <c r="C127">
-        <v>0</v>
-      </c>
-      <c r="D127">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="str">
-        <v>11/30</v>
-      </c>
-      <c r="B128">
-        <v>0</v>
-      </c>
-      <c r="C128">
-        <v>0</v>
-      </c>
-      <c r="D128">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="str">
-        <v>12/01</v>
-      </c>
-      <c r="B129">
-        <v>0</v>
-      </c>
-      <c r="C129">
-        <v>0</v>
-      </c>
-      <c r="D129">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="str">
-        <v>12/02</v>
-      </c>
-      <c r="B130">
-        <v>0</v>
-      </c>
-      <c r="C130">
-        <v>0</v>
-      </c>
-      <c r="D130">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="str">
-        <v>12/03</v>
-      </c>
-      <c r="B131">
-        <v>0</v>
-      </c>
-      <c r="C131">
-        <v>0</v>
-      </c>
-      <c r="D131">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="str">
-        <v>12/04</v>
-      </c>
-      <c r="B132">
-        <v>0</v>
-      </c>
-      <c r="C132">
-        <v>0</v>
-      </c>
-      <c r="D132">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="str">
-        <v>12/05</v>
-      </c>
-      <c r="B133">
-        <v>0</v>
-      </c>
-      <c r="C133">
-        <v>0</v>
-      </c>
-      <c r="D133">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="str">
-        <v>12/06</v>
-      </c>
-      <c r="B134">
-        <v>0</v>
-      </c>
-      <c r="C134">
-        <v>0</v>
-      </c>
-      <c r="D134">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="str">
-        <v>12/07</v>
-      </c>
-      <c r="B135">
-        <v>0</v>
-      </c>
-      <c r="C135">
-        <v>0</v>
-      </c>
-      <c r="D135">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="str">
-        <v>12/08</v>
-      </c>
-      <c r="B136">
-        <v>0</v>
-      </c>
-      <c r="C136">
-        <v>0</v>
-      </c>
-      <c r="D136">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="str">
-        <v>12/09</v>
-      </c>
-      <c r="B137">
-        <v>0</v>
-      </c>
-      <c r="C137">
-        <v>0</v>
-      </c>
-      <c r="D137">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="str">
-        <v>12/10</v>
-      </c>
-      <c r="B138">
-        <v>0</v>
-      </c>
-      <c r="C138">
-        <v>0</v>
-      </c>
-      <c r="D138">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="str">
-        <v>12/11</v>
-      </c>
-      <c r="B139">
-        <v>0</v>
-      </c>
-      <c r="C139">
-        <v>0</v>
-      </c>
-      <c r="D139">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="str">
-        <v>12/12</v>
-      </c>
-      <c r="B140">
-        <v>0</v>
-      </c>
-      <c r="C140">
-        <v>0</v>
-      </c>
-      <c r="D140">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="str">
-        <v>12/13</v>
-      </c>
-      <c r="B141">
-        <v>0</v>
-      </c>
-      <c r="C141">
-        <v>0</v>
-      </c>
-      <c r="D141">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="str">
-        <v>12/14</v>
-      </c>
-      <c r="B142">
-        <v>0</v>
-      </c>
-      <c r="C142">
-        <v>0</v>
-      </c>
-      <c r="D142">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="str">
-        <v>12/15</v>
-      </c>
-      <c r="B143">
-        <v>0</v>
-      </c>
-      <c r="C143">
-        <v>0</v>
-      </c>
-      <c r="D143">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="str">
-        <v>12/16</v>
-      </c>
-      <c r="B144">
-        <v>0</v>
-      </c>
-      <c r="C144">
-        <v>0</v>
-      </c>
-      <c r="D144">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="str">
-        <v>12/17</v>
-      </c>
-      <c r="B145">
-        <v>0</v>
-      </c>
-      <c r="C145">
-        <v>0</v>
-      </c>
-      <c r="D145">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="str">
-        <v>12/18</v>
-      </c>
-      <c r="B146">
-        <v>0</v>
-      </c>
-      <c r="C146">
-        <v>0</v>
-      </c>
-      <c r="D146">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="str">
-        <v>12/19</v>
-      </c>
-      <c r="B147">
-        <v>0</v>
-      </c>
-      <c r="C147">
-        <v>0</v>
-      </c>
-      <c r="D147">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="str">
-        <v>12/20</v>
-      </c>
-      <c r="B148">
-        <v>0</v>
-      </c>
-      <c r="C148">
-        <v>0</v>
-      </c>
-      <c r="D148">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="str">
-        <v>12/21</v>
-      </c>
-      <c r="B149">
-        <v>0</v>
-      </c>
-      <c r="C149">
-        <v>0</v>
-      </c>
-      <c r="D149">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="str">
-        <v>12/22</v>
-      </c>
-      <c r="B150">
-        <v>0</v>
-      </c>
-      <c r="C150">
-        <v>0</v>
-      </c>
-      <c r="D150">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="str">
-        <v>12/23</v>
-      </c>
-      <c r="B151">
-        <v>0</v>
-      </c>
-      <c r="C151">
-        <v>0</v>
-      </c>
-      <c r="D151">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="str">
-        <v>12/24</v>
-      </c>
-      <c r="B152">
-        <v>0</v>
-      </c>
-      <c r="C152">
-        <v>0</v>
-      </c>
-      <c r="D152">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="str">
-        <v>12/25</v>
-      </c>
-      <c r="B153">
-        <v>0</v>
-      </c>
-      <c r="C153">
-        <v>0</v>
-      </c>
-      <c r="D153">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="str">
-        <v>12/26</v>
-      </c>
-      <c r="B154">
-        <v>0</v>
-      </c>
-      <c r="C154">
-        <v>0</v>
-      </c>
-      <c r="D154">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="str">
-        <v>12/27</v>
-      </c>
-      <c r="B155">
-        <v>0</v>
-      </c>
-      <c r="C155">
-        <v>0</v>
-      </c>
-      <c r="D155">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D155"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D124"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/PA-PL_occupancy_pace_150day.xlsx
+++ b/PA-PL_occupancy_pace_150day.xlsx
@@ -415,805 +415,805 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>08/03</v>
+        <v>08/10</v>
       </c>
       <c r="B2">
-        <v>259.28499999999997</v>
+        <v>271.505</v>
       </c>
       <c r="C2">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D2">
-        <v>3629.99</v>
+        <v>2715.0499999999997</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>08/04</v>
+        <v>08/11</v>
       </c>
       <c r="B3">
-        <v>266.461</v>
+        <v>333.6355555555556</v>
       </c>
       <c r="C3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D3">
-        <v>2664.61</v>
+        <v>3002.7200000000003</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>08/05</v>
+        <v>08/12</v>
       </c>
       <c r="B4">
-        <v>245.8714285714286</v>
+        <v>307.74857142857144</v>
       </c>
       <c r="C4">
         <v>7</v>
       </c>
       <c r="D4">
-        <v>1721.1000000000001</v>
+        <v>2154.2400000000002</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>08/06</v>
+        <v>08/13</v>
       </c>
       <c r="B5">
-        <v>235.83333333333334</v>
+        <v>416.62857142857143</v>
       </c>
       <c r="C5">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D5">
-        <v>707.5</v>
+        <v>2916.4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>08/07</v>
+        <v>08/14</v>
       </c>
       <c r="B6">
-        <v>361.756875</v>
+        <v>395.2395652173913</v>
       </c>
       <c r="C6">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="D6">
-        <v>5788.11</v>
+        <v>9090.51</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>08/08</v>
+        <v>08/15</v>
       </c>
       <c r="B7">
-        <v>349.18909090909096</v>
+        <v>412.84125</v>
       </c>
       <c r="C7">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D7">
-        <v>7682.160000000001</v>
+        <v>9908.19</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>08/09</v>
+        <v>08/16</v>
       </c>
       <c r="B8">
-        <v>261.44235294117647</v>
+        <v>351.5571428571428</v>
       </c>
       <c r="C8">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="D8">
-        <v>4444.5199999999995</v>
+        <v>2460.8999999999996</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>08/10</v>
+        <v>08/17</v>
       </c>
       <c r="B9">
-        <v>257.8128571428571</v>
+        <v>313.89090909090913</v>
       </c>
       <c r="C9">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D9">
-        <v>1804.69</v>
+        <v>3452.8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>08/11</v>
+        <v>08/18</v>
       </c>
       <c r="B10">
-        <v>284.4</v>
+        <v>302.2283333333333</v>
       </c>
       <c r="C10">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D10">
-        <v>1422</v>
+        <v>3626.74</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>08/12</v>
+        <v>08/19</v>
       </c>
       <c r="B11">
-        <v>310.5</v>
+        <v>351.39000000000004</v>
       </c>
       <c r="C11">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D11">
-        <v>621</v>
+        <v>3513.9000000000005</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>08/13</v>
+        <v>08/20</v>
       </c>
       <c r="B12">
-        <v>296</v>
+        <v>431.51666666666665</v>
       </c>
       <c r="C12">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D12">
-        <v>296</v>
+        <v>2589.1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>08/14</v>
+        <v>08/21</v>
       </c>
       <c r="B13">
-        <v>342.25</v>
+        <v>493.08714285714285</v>
       </c>
       <c r="C13">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D13">
-        <v>4107</v>
+        <v>6903.22</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>08/15</v>
+        <v>08/22</v>
       </c>
       <c r="B14">
-        <v>341.6666666666667</v>
+        <v>465.14666666666676</v>
       </c>
       <c r="C14">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D14">
-        <v>4100</v>
+        <v>6977.200000000002</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>08/16</v>
+        <v>08/23</v>
       </c>
       <c r="B15">
-        <v>333.2</v>
+        <v>349.7528571428572</v>
       </c>
       <c r="C15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D15">
-        <v>1666</v>
+        <v>2448.2700000000004</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>08/17</v>
+        <v>08/24</v>
       </c>
       <c r="B16">
-        <v>330.14285714285717</v>
+        <v>356.13700000000006</v>
       </c>
       <c r="C16">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D16">
-        <v>2311</v>
+        <v>3561.3700000000003</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>08/18</v>
+        <v>08/25</v>
       </c>
       <c r="B17">
-        <v>289.0925</v>
+        <v>331.61499999999995</v>
       </c>
       <c r="C17">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D17">
-        <v>2312.74</v>
+        <v>3316.1499999999996</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>08/19</v>
+        <v>08/26</v>
       </c>
       <c r="B18">
-        <v>295.86</v>
+        <v>347.86125</v>
       </c>
       <c r="C18">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D18">
-        <v>1479.3</v>
+        <v>2782.89</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>08/20</v>
+        <v>08/27</v>
       </c>
       <c r="B19">
-        <v>353.55</v>
+        <v>277</v>
       </c>
       <c r="C19">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D19">
-        <v>707.1</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>08/21</v>
+        <v>08/28</v>
       </c>
       <c r="B20">
-        <v>420.41999999999996</v>
+        <v>312.8722222222222</v>
       </c>
       <c r="C20">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D20">
-        <v>2102.1</v>
+        <v>2815.85</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>08/22</v>
+        <v>08/29</v>
       </c>
       <c r="B21">
-        <v>390.875</v>
+        <v>321.52200000000005</v>
       </c>
       <c r="C21">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D21">
-        <v>1563.5</v>
+        <v>3215.2200000000003</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>08/23</v>
+        <v>08/30</v>
       </c>
       <c r="B22">
-        <v>355.24</v>
+        <v>275.3333333333333</v>
       </c>
       <c r="C22">
         <v>6</v>
       </c>
       <c r="D22">
-        <v>2131.44</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>08/24</v>
+        <v>08/31</v>
       </c>
       <c r="B23">
-        <v>324.01666666666665</v>
+        <v>265.75</v>
       </c>
       <c r="C23">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D23">
-        <v>1944.1</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>08/25</v>
+        <v>09/01</v>
       </c>
       <c r="B24">
-        <v>294.4357142857143</v>
+        <v>268.25</v>
       </c>
       <c r="C24">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D24">
-        <v>2061.05</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>08/26</v>
+        <v>09/02</v>
       </c>
       <c r="B25">
-        <v>244.2225</v>
+        <v>225</v>
       </c>
       <c r="C25">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D25">
-        <v>976.89</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>08/27</v>
+        <v>09/03</v>
       </c>
       <c r="B26">
-        <v>274.5</v>
+        <v>325.6</v>
       </c>
       <c r="C26">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D26">
-        <v>1098</v>
+        <v>1953.6000000000001</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>08/28</v>
+        <v>09/04</v>
       </c>
       <c r="B27">
-        <v>323.2642857142857</v>
+        <v>739.9333333333334</v>
       </c>
       <c r="C27">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D27">
-        <v>2262.85</v>
+        <v>4439.6</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>08/29</v>
+        <v>09/05</v>
       </c>
       <c r="B28">
-        <v>350.0314285714286</v>
+        <v>571.7355555555555</v>
       </c>
       <c r="C28">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D28">
-        <v>2450.2200000000003</v>
+        <v>5145.62</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>08/30</v>
+        <v>09/06</v>
       </c>
       <c r="B29">
-        <v>292</v>
+        <v>435.7875000000001</v>
       </c>
       <c r="C29">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D29">
-        <v>1460</v>
+        <v>3486.3000000000006</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>08/31</v>
+        <v>09/07</v>
       </c>
       <c r="B30">
-        <v>261.3333333333333</v>
+        <v>259.8</v>
       </c>
       <c r="C30">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D30">
-        <v>784</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>09/01</v>
+        <v>09/08</v>
       </c>
       <c r="B31">
-        <v>257.5</v>
+        <v>246.57142857142858</v>
       </c>
       <c r="C31">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D31">
-        <v>515</v>
+        <v>1726</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>09/02</v>
+        <v>09/09</v>
       </c>
       <c r="B32">
-        <v>211.5</v>
+        <v>234</v>
       </c>
       <c r="C32">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D32">
-        <v>846</v>
+        <v>468</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>09/03</v>
+        <v>09/10</v>
       </c>
       <c r="B33">
-        <v>238.3</v>
+        <v>226.57</v>
       </c>
       <c r="C33">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D33">
-        <v>953.2</v>
+        <v>453.14</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>09/04</v>
+        <v>09/11</v>
       </c>
       <c r="B34">
-        <v>354</v>
+        <v>315.43083333333334</v>
       </c>
       <c r="C34">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D34">
-        <v>708</v>
+        <v>3785.17</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>09/05</v>
+        <v>09/12</v>
       </c>
       <c r="B35">
-        <v>380.6225</v>
+        <v>315.5571428571428</v>
       </c>
       <c r="C35">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D35">
-        <v>1522.49</v>
+        <v>4417.799999999999</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>09/06</v>
+        <v>09/13</v>
       </c>
       <c r="B36">
-        <v>418.3</v>
+        <v>209.75</v>
       </c>
       <c r="C36">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D36">
-        <v>2091.5</v>
+        <v>839</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>09/07</v>
+        <v>09/14</v>
       </c>
       <c r="B37">
-        <v>221.4</v>
+        <v>188</v>
       </c>
       <c r="C37">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D37">
-        <v>1107</v>
+        <v>188</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>09/08</v>
+        <v>09/15</v>
       </c>
       <c r="B38">
-        <v>215.57142857142858</v>
+        <v>267</v>
       </c>
       <c r="C38">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D38">
-        <v>1509</v>
+        <v>267</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>09/09</v>
+        <v>09/16</v>
       </c>
       <c r="B39">
-        <v>234</v>
+        <v>242.5</v>
       </c>
       <c r="C39">
         <v>2</v>
       </c>
       <c r="D39">
-        <v>468</v>
+        <v>485</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>09/10</v>
+        <v>09/17</v>
       </c>
       <c r="B40">
-        <v>219</v>
+        <v>241.25666666666666</v>
       </c>
       <c r="C40">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D40">
-        <v>219</v>
+        <v>723.77</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>09/11</v>
+        <v>09/18</v>
       </c>
       <c r="B41">
-        <v>266.1666666666667</v>
+        <v>309.08380952380946</v>
       </c>
       <c r="C41">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D41">
-        <v>1597</v>
+        <v>6490.759999999999</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>09/12</v>
+        <v>09/19</v>
       </c>
       <c r="B42">
-        <v>275.5</v>
+        <v>304.075</v>
       </c>
       <c r="C42">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="D42">
-        <v>2204</v>
+        <v>7297.8</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>09/13</v>
+        <v>09/20</v>
       </c>
       <c r="B43">
-        <v>209.75</v>
+        <v>225.37375</v>
       </c>
       <c r="C43">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D43">
-        <v>839</v>
+        <v>1802.99</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>09/14</v>
+        <v>09/21</v>
       </c>
       <c r="B44">
-        <v>188</v>
+        <v>242</v>
       </c>
       <c r="C44">
         <v>1</v>
       </c>
       <c r="D44">
-        <v>188</v>
+        <v>242</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>09/15</v>
+        <v>09/22</v>
       </c>
       <c r="B45">
-        <v>0</v>
+        <v>251</v>
       </c>
       <c r="C45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D45">
-        <v>0</v>
+        <v>251</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>09/16</v>
+        <v>09/23</v>
       </c>
       <c r="B46">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="C46">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D46">
-        <v>210</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>09/17</v>
+        <v>09/24</v>
       </c>
       <c r="B47">
-        <v>222.385</v>
+        <v>0</v>
       </c>
       <c r="C47">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D47">
-        <v>444.77</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>09/18</v>
+        <v>09/25</v>
       </c>
       <c r="B48">
-        <v>309.08380952380946</v>
+        <v>328.1818181818182</v>
       </c>
       <c r="C48">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="D48">
-        <v>6490.759999999999</v>
+        <v>3610</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>09/19</v>
+        <v>09/26</v>
       </c>
       <c r="B49">
-        <v>304.075</v>
+        <v>336.9714285714286</v>
       </c>
       <c r="C49">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D49">
-        <v>7297.799999999999</v>
+        <v>4717.6</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>09/20</v>
+        <v>09/27</v>
       </c>
       <c r="B50">
-        <v>225.37375</v>
+        <v>274.2857142857143</v>
       </c>
       <c r="C50">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D50">
-        <v>1802.99</v>
+        <v>1920</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>09/21</v>
+        <v>09/28</v>
       </c>
       <c r="B51">
-        <v>242</v>
+        <v>266</v>
       </c>
       <c r="C51">
         <v>1</v>
       </c>
       <c r="D51">
-        <v>242</v>
+        <v>266</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>09/22</v>
+        <v>09/29</v>
       </c>
       <c r="B52">
-        <v>251</v>
+        <v>265</v>
       </c>
       <c r="C52">
         <v>1</v>
       </c>
       <c r="D52">
-        <v>251</v>
+        <v>265</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>09/23</v>
+        <v>09/30</v>
       </c>
       <c r="B53">
-        <v>0</v>
+        <v>266</v>
       </c>
       <c r="C53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D53">
-        <v>0</v>
+        <v>266</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>09/24</v>
+        <v>10/01</v>
       </c>
       <c r="B54">
-        <v>0</v>
+        <v>194</v>
       </c>
       <c r="C54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D54">
-        <v>0</v>
+        <v>194</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>09/25</v>
+        <v>10/02</v>
       </c>
       <c r="B55">
-        <v>328.1818181818182</v>
+        <v>322.15999999999997</v>
       </c>
       <c r="C55">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D55">
-        <v>3610</v>
+        <v>3221.6</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>09/26</v>
+        <v>10/03</v>
       </c>
       <c r="B56">
-        <v>336.9714285714286</v>
+        <v>314.40000000000003</v>
       </c>
       <c r="C56">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D56">
-        <v>4717.6</v>
+        <v>3458.4</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>09/27</v>
+        <v>10/04</v>
       </c>
       <c r="B57">
-        <v>274.2857142857143</v>
+        <v>199.5</v>
       </c>
       <c r="C57">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D57">
-        <v>1920</v>
+        <v>399</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>09/28</v>
+        <v>10/05</v>
       </c>
       <c r="B58">
-        <v>0</v>
+        <v>193.5</v>
       </c>
       <c r="C58">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D58">
-        <v>0</v>
+        <v>387</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>09/29</v>
+        <v>10/06</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -1227,7 +1227,7 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>09/30</v>
+        <v>10/07</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -1241,273 +1241,273 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>10/01</v>
+        <v>10/08</v>
       </c>
       <c r="B61">
-        <v>194</v>
+        <v>222.21</v>
       </c>
       <c r="C61">
         <v>1</v>
       </c>
       <c r="D61">
-        <v>194</v>
+        <v>222.21</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>10/02</v>
+        <v>10/09</v>
       </c>
       <c r="B62">
-        <v>322.16</v>
+        <v>446.45285714285717</v>
       </c>
       <c r="C62">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D62">
-        <v>3221.6000000000004</v>
+        <v>3125.17</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>10/03</v>
+        <v>10/10</v>
       </c>
       <c r="B63">
-        <v>314.40000000000003</v>
+        <v>445.02500000000003</v>
       </c>
       <c r="C63">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D63">
-        <v>3458.4</v>
+        <v>2670.15</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>10/04</v>
+        <v>10/11</v>
       </c>
       <c r="B64">
-        <v>199.5</v>
+        <v>336</v>
       </c>
       <c r="C64">
         <v>2</v>
       </c>
       <c r="D64">
-        <v>399</v>
+        <v>672</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>10/05</v>
+        <v>10/12</v>
       </c>
       <c r="B65">
-        <v>193.5</v>
+        <v>192</v>
       </c>
       <c r="C65">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D65">
-        <v>387</v>
+        <v>192</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>10/06</v>
+        <v>10/13</v>
       </c>
       <c r="B66">
-        <v>0</v>
+        <v>184</v>
       </c>
       <c r="C66">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D66">
-        <v>0</v>
+        <v>184</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>10/07</v>
+        <v>10/14</v>
       </c>
       <c r="B67">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="C67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D67">
-        <v>0</v>
+        <v>190</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>10/08</v>
+        <v>10/15</v>
       </c>
       <c r="B68">
-        <v>222.21</v>
+        <v>0</v>
       </c>
       <c r="C68">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D68">
-        <v>222.21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>10/09</v>
+        <v>10/16</v>
       </c>
       <c r="B69">
-        <v>366.52833333333336</v>
+        <v>352.25</v>
       </c>
       <c r="C69">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D69">
-        <v>2199.17</v>
+        <v>2818</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>10/10</v>
+        <v>10/17</v>
       </c>
       <c r="B70">
-        <v>358.03000000000003</v>
+        <v>344.45454545454544</v>
       </c>
       <c r="C70">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D70">
-        <v>1790.15</v>
+        <v>3789</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>10/11</v>
+        <v>10/18</v>
       </c>
       <c r="B71">
-        <v>336</v>
+        <v>250.5</v>
       </c>
       <c r="C71">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D71">
-        <v>672</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>10/12</v>
+        <v>10/19</v>
       </c>
       <c r="B72">
-        <v>192</v>
+        <v>230.5</v>
       </c>
       <c r="C72">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D72">
-        <v>192</v>
+        <v>461</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>10/13</v>
+        <v>10/20</v>
       </c>
       <c r="B73">
-        <v>184</v>
+        <v>0</v>
       </c>
       <c r="C73">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D73">
-        <v>184</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>10/14</v>
+        <v>10/21</v>
       </c>
       <c r="B74">
-        <v>190</v>
+        <v>149</v>
       </c>
       <c r="C74">
         <v>1</v>
       </c>
       <c r="D74">
-        <v>190</v>
+        <v>149</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>10/15</v>
+        <v>10/22</v>
       </c>
       <c r="B75">
-        <v>0</v>
+        <v>220.846</v>
       </c>
       <c r="C75">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D75">
-        <v>0</v>
+        <v>1104.23</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>10/16</v>
+        <v>10/23</v>
       </c>
       <c r="B76">
-        <v>352.25</v>
+        <v>296.46153846153845</v>
       </c>
       <c r="C76">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D76">
-        <v>2818</v>
+        <v>3854</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>10/17</v>
+        <v>10/24</v>
       </c>
       <c r="B77">
-        <v>352.9</v>
+        <v>296.75</v>
       </c>
       <c r="C77">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D77">
-        <v>3529</v>
+        <v>3561</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>10/18</v>
+        <v>10/25</v>
       </c>
       <c r="B78">
-        <v>263</v>
+        <v>217</v>
       </c>
       <c r="C78">
         <v>3</v>
       </c>
       <c r="D78">
-        <v>789</v>
+        <v>651</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>10/19</v>
+        <v>10/26</v>
       </c>
       <c r="B79">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="C79">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D79">
-        <v>229</v>
+        <v>660</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>10/20</v>
+        <v>10/27</v>
       </c>
       <c r="B80">
         <v>0</v>
@@ -1521,77 +1521,77 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>10/21</v>
+        <v>10/28</v>
       </c>
       <c r="B81">
-        <v>149</v>
+        <v>135.15</v>
       </c>
       <c r="C81">
         <v>1</v>
       </c>
       <c r="D81">
-        <v>149</v>
+        <v>135.15</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>10/22</v>
+        <v>10/29</v>
       </c>
       <c r="B82">
-        <v>220.846</v>
+        <v>164.25</v>
       </c>
       <c r="C82">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D82">
-        <v>1104.23</v>
+        <v>328.5</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>10/23</v>
+        <v>10/30</v>
       </c>
       <c r="B83">
-        <v>296.46153846153845</v>
+        <v>273.5</v>
       </c>
       <c r="C83">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D83">
-        <v>3854</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>10/24</v>
+        <v>10/31</v>
       </c>
       <c r="B84">
-        <v>301.3636363636364</v>
+        <v>291</v>
       </c>
       <c r="C84">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D84">
-        <v>3315</v>
+        <v>873</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>10/25</v>
+        <v>11/01</v>
       </c>
       <c r="B85">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="C85">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D85">
-        <v>232</v>
+        <v>448</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>10/26</v>
+        <v>11/02</v>
       </c>
       <c r="B86">
         <v>229</v>
@@ -1605,7 +1605,7 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>10/27</v>
+        <v>11/03</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -1619,91 +1619,91 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>10/28</v>
+        <v>11/04</v>
       </c>
       <c r="B88">
-        <v>135.15</v>
+        <v>0</v>
       </c>
       <c r="C88">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D88">
-        <v>135.15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>10/29</v>
+        <v>11/05</v>
       </c>
       <c r="B89">
-        <v>164.25</v>
+        <v>0</v>
       </c>
       <c r="C89">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D89">
-        <v>328.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>10/30</v>
+        <v>11/06</v>
       </c>
       <c r="B90">
-        <v>273.5</v>
+        <v>278.375</v>
       </c>
       <c r="C90">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D90">
-        <v>1094</v>
+        <v>556.75</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>10/31</v>
+        <v>11/07</v>
       </c>
       <c r="B91">
-        <v>291</v>
+        <v>280.925</v>
       </c>
       <c r="C91">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D91">
-        <v>873</v>
+        <v>561.85</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>11/01</v>
+        <v>11/08</v>
       </c>
       <c r="B92">
-        <v>224</v>
+        <v>0</v>
       </c>
       <c r="C92">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D92">
-        <v>448</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>11/02</v>
+        <v>11/09</v>
       </c>
       <c r="B93">
-        <v>229</v>
+        <v>0</v>
       </c>
       <c r="C93">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D93">
-        <v>229</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>11/03</v>
+        <v>11/10</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -1717,7 +1717,7 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>11/04</v>
+        <v>11/11</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -1731,7 +1731,7 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>11/05</v>
+        <v>11/12</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -1745,35 +1745,35 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>11/06</v>
+        <v>11/13</v>
       </c>
       <c r="B97">
-        <v>278.375</v>
+        <v>0</v>
       </c>
       <c r="C97">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D97">
-        <v>556.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>11/07</v>
+        <v>11/14</v>
       </c>
       <c r="B98">
-        <v>280.925</v>
+        <v>0</v>
       </c>
       <c r="C98">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D98">
-        <v>561.85</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>11/08</v>
+        <v>11/15</v>
       </c>
       <c r="B99">
         <v>0</v>
@@ -1787,7 +1787,7 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>11/09</v>
+        <v>11/16</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>11/10</v>
+        <v>11/17</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -1815,7 +1815,7 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>11/11</v>
+        <v>11/18</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -1829,7 +1829,7 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>11/12</v>
+        <v>11/19</v>
       </c>
       <c r="B103">
         <v>0</v>
@@ -1843,7 +1843,7 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>11/13</v>
+        <v>11/20</v>
       </c>
       <c r="B104">
         <v>0</v>
@@ -1857,7 +1857,7 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>11/14</v>
+        <v>11/21</v>
       </c>
       <c r="B105">
         <v>0</v>
@@ -1871,7 +1871,7 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>11/15</v>
+        <v>11/22</v>
       </c>
       <c r="B106">
         <v>0</v>
@@ -1885,7 +1885,7 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>11/16</v>
+        <v>11/23</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -1899,7 +1899,7 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>11/17</v>
+        <v>11/24</v>
       </c>
       <c r="B108">
         <v>0</v>
@@ -1913,7 +1913,7 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>11/18</v>
+        <v>11/25</v>
       </c>
       <c r="B109">
         <v>0</v>
@@ -1927,7 +1927,7 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>11/19</v>
+        <v>11/26</v>
       </c>
       <c r="B110">
         <v>0</v>
@@ -1941,7 +1941,7 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>11/20</v>
+        <v>11/27</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -1955,7 +1955,7 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>11/21</v>
+        <v>11/28</v>
       </c>
       <c r="B112">
         <v>0</v>
@@ -1969,7 +1969,7 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>11/22</v>
+        <v>11/29</v>
       </c>
       <c r="B113">
         <v>0</v>
@@ -1983,7 +1983,7 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>11/23</v>
+        <v>11/30</v>
       </c>
       <c r="B114">
         <v>0</v>
@@ -1997,7 +1997,7 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>11/24</v>
+        <v>12/01</v>
       </c>
       <c r="B115">
         <v>0</v>
@@ -2011,7 +2011,7 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>11/25</v>
+        <v>12/02</v>
       </c>
       <c r="B116">
         <v>0</v>
@@ -2025,7 +2025,7 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>11/26</v>
+        <v>12/03</v>
       </c>
       <c r="B117">
         <v>0</v>
@@ -2039,7 +2039,7 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>11/27</v>
+        <v>12/04</v>
       </c>
       <c r="B118">
         <v>0</v>
@@ -2053,7 +2053,7 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>11/28</v>
+        <v>12/05</v>
       </c>
       <c r="B119">
         <v>0</v>
@@ -2067,7 +2067,7 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>11/29</v>
+        <v>12/06</v>
       </c>
       <c r="B120">
         <v>0</v>
@@ -2081,7 +2081,7 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>11/30</v>
+        <v>12/07</v>
       </c>
       <c r="B121">
         <v>0</v>
@@ -2095,7 +2095,7 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>12/01</v>
+        <v>12/08</v>
       </c>
       <c r="B122">
         <v>0</v>
@@ -2109,7 +2109,7 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>12/02</v>
+        <v>12/09</v>
       </c>
       <c r="B123">
         <v>0</v>
@@ -2123,7 +2123,7 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>12/03</v>
+        <v>12/10</v>
       </c>
       <c r="B124">
         <v>0</v>

--- a/PA-PL_occupancy_pace_150day.xlsx
+++ b/PA-PL_occupancy_pace_150day.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D124"/>
+  <dimension ref="A1:D138"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -415,1001 +415,1001 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>08/10</v>
+        <v>08/17</v>
       </c>
       <c r="B2">
-        <v>271.505</v>
+        <v>273.8828571428572</v>
       </c>
       <c r="C2">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D2">
-        <v>2715.0499999999997</v>
+        <v>3834.36</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>08/11</v>
+        <v>08/18</v>
       </c>
       <c r="B3">
-        <v>333.6355555555556</v>
+        <v>265.61249999999995</v>
       </c>
       <c r="C3">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D3">
-        <v>3002.7200000000003</v>
+        <v>4249.799999999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>08/12</v>
+        <v>08/19</v>
       </c>
       <c r="B4">
-        <v>307.74857142857144</v>
+        <v>240.57142857142858</v>
       </c>
       <c r="C4">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D4">
-        <v>2154.2400000000002</v>
+        <v>3368</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>08/13</v>
+        <v>08/20</v>
       </c>
       <c r="B5">
-        <v>416.62857142857143</v>
+        <v>247.20999999999998</v>
       </c>
       <c r="C5">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D5">
-        <v>2916.4</v>
+        <v>2472.1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>08/14</v>
+        <v>08/21</v>
       </c>
       <c r="B6">
-        <v>395.2395652173913</v>
+        <v>307.502</v>
       </c>
       <c r="C6">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D6">
-        <v>9090.51</v>
+        <v>6150.04</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>08/15</v>
+        <v>08/22</v>
       </c>
       <c r="B7">
-        <v>412.84125</v>
+        <v>289.71695652173906</v>
       </c>
       <c r="C7">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D7">
-        <v>9908.19</v>
+        <v>6663.489999999998</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>08/16</v>
+        <v>08/23</v>
       </c>
       <c r="B8">
-        <v>351.5571428571428</v>
+        <v>275.8961538461539</v>
       </c>
       <c r="C8">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D8">
-        <v>2460.8999999999996</v>
+        <v>3586.65</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>08/17</v>
+        <v>08/24</v>
       </c>
       <c r="B9">
-        <v>313.89090909090913</v>
+        <v>254.6475</v>
       </c>
       <c r="C9">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D9">
-        <v>3452.8</v>
+        <v>4074.36</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>08/18</v>
+        <v>08/25</v>
       </c>
       <c r="B10">
-        <v>302.2283333333333</v>
+        <v>247.37624999999997</v>
       </c>
       <c r="C10">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D10">
-        <v>3626.74</v>
+        <v>3958.0199999999995</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>08/19</v>
+        <v>08/26</v>
       </c>
       <c r="B11">
-        <v>351.39000000000004</v>
+        <v>235.92153846153843</v>
       </c>
       <c r="C11">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D11">
-        <v>3513.9000000000005</v>
+        <v>3066.9799999999996</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>08/20</v>
+        <v>08/27</v>
       </c>
       <c r="B12">
-        <v>431.51666666666665</v>
+        <v>254.9125</v>
       </c>
       <c r="C12">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D12">
-        <v>2589.1</v>
+        <v>2039.3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>08/21</v>
+        <v>08/28</v>
       </c>
       <c r="B13">
-        <v>493.08714285714285</v>
+        <v>336.33666666666664</v>
       </c>
       <c r="C13">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D13">
-        <v>6903.22</v>
+        <v>4036.04</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>08/22</v>
+        <v>08/29</v>
       </c>
       <c r="B14">
-        <v>465.14666666666676</v>
+        <v>333.31000000000006</v>
       </c>
       <c r="C14">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D14">
-        <v>6977.200000000002</v>
+        <v>4333.030000000001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>08/23</v>
+        <v>08/30</v>
       </c>
       <c r="B15">
-        <v>349.7528571428572</v>
+        <v>275.3333333333333</v>
       </c>
       <c r="C15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D15">
-        <v>2448.2700000000004</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>08/24</v>
+        <v>08/31</v>
       </c>
       <c r="B16">
-        <v>356.13700000000006</v>
+        <v>254.908</v>
       </c>
       <c r="C16">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D16">
-        <v>3561.3700000000003</v>
+        <v>1274.54</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>08/25</v>
+        <v>09/01</v>
       </c>
       <c r="B17">
-        <v>331.61499999999995</v>
+        <v>268.25</v>
       </c>
       <c r="C17">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D17">
-        <v>3316.1499999999996</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>08/26</v>
+        <v>09/02</v>
       </c>
       <c r="B18">
-        <v>347.86125</v>
+        <v>225</v>
       </c>
       <c r="C18">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D18">
-        <v>2782.89</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>08/27</v>
+        <v>09/03</v>
       </c>
       <c r="B19">
-        <v>277</v>
+        <v>240.62857142857143</v>
       </c>
       <c r="C19">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D19">
-        <v>1385</v>
+        <v>1684.4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>08/28</v>
+        <v>09/04</v>
       </c>
       <c r="B20">
-        <v>312.8722222222222</v>
+        <v>413.06666666666666</v>
       </c>
       <c r="C20">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D20">
-        <v>2815.85</v>
+        <v>4956.8</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>08/29</v>
+        <v>09/05</v>
       </c>
       <c r="B21">
-        <v>321.52200000000005</v>
+        <v>404.3394444444445</v>
       </c>
       <c r="C21">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="D21">
-        <v>3215.2200000000003</v>
+        <v>7278.110000000001</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>08/30</v>
+        <v>09/06</v>
       </c>
       <c r="B22">
-        <v>275.3333333333333</v>
+        <v>367.75307692307695</v>
       </c>
       <c r="C22">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D22">
-        <v>1652</v>
+        <v>4780.79</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>08/31</v>
+        <v>09/07</v>
       </c>
       <c r="B23">
-        <v>265.75</v>
+        <v>220.08333333333334</v>
       </c>
       <c r="C23">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D23">
-        <v>1063</v>
+        <v>1320.5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>09/01</v>
+        <v>09/08</v>
       </c>
       <c r="B24">
-        <v>268.25</v>
+        <v>218.14285714285714</v>
       </c>
       <c r="C24">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D24">
-        <v>1073</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>09/02</v>
+        <v>09/09</v>
       </c>
       <c r="B25">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="C25">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D25">
-        <v>1125</v>
+        <v>468</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>09/03</v>
+        <v>09/10</v>
       </c>
       <c r="B26">
-        <v>325.6</v>
+        <v>226.57</v>
       </c>
       <c r="C26">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D26">
-        <v>1953.6000000000001</v>
+        <v>453.14</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>09/04</v>
+        <v>09/11</v>
       </c>
       <c r="B27">
-        <v>739.9333333333334</v>
+        <v>275.64214285714286</v>
       </c>
       <c r="C27">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D27">
-        <v>4439.6</v>
+        <v>3858.99</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>09/05</v>
+        <v>09/12</v>
       </c>
       <c r="B28">
-        <v>571.7355555555555</v>
+        <v>280.41999999999996</v>
       </c>
       <c r="C28">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D28">
-        <v>5145.62</v>
+        <v>4486.719999999999</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>09/06</v>
+        <v>09/13</v>
       </c>
       <c r="B29">
-        <v>435.7875000000001</v>
+        <v>209.75</v>
       </c>
       <c r="C29">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D29">
-        <v>3486.3000000000006</v>
+        <v>839</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>09/07</v>
+        <v>09/14</v>
       </c>
       <c r="B30">
-        <v>259.8</v>
+        <v>188</v>
       </c>
       <c r="C30">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D30">
-        <v>1299</v>
+        <v>188</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>09/08</v>
+        <v>09/15</v>
       </c>
       <c r="B31">
-        <v>246.57142857142858</v>
+        <v>267</v>
       </c>
       <c r="C31">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D31">
-        <v>1726</v>
+        <v>267</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>09/09</v>
+        <v>09/16</v>
       </c>
       <c r="B32">
-        <v>234</v>
+        <v>252.66666666666666</v>
       </c>
       <c r="C32">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D32">
-        <v>468</v>
+        <v>758</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>09/10</v>
+        <v>09/17</v>
       </c>
       <c r="B33">
-        <v>226.57</v>
+        <v>260.354</v>
       </c>
       <c r="C33">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D33">
-        <v>453.14</v>
+        <v>1301.77</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>09/11</v>
+        <v>09/18</v>
       </c>
       <c r="B34">
-        <v>315.43083333333334</v>
+        <v>314.05550000000005</v>
       </c>
       <c r="C34">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D34">
-        <v>3785.17</v>
+        <v>6281.110000000001</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>09/12</v>
+        <v>09/19</v>
       </c>
       <c r="B35">
-        <v>315.5571428571428</v>
+        <v>308.3904347826087</v>
       </c>
       <c r="C35">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="D35">
-        <v>4417.799999999999</v>
+        <v>7092.98</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>09/13</v>
+        <v>09/20</v>
       </c>
       <c r="B36">
-        <v>209.75</v>
+        <v>225.37375</v>
       </c>
       <c r="C36">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D36">
-        <v>839</v>
+        <v>1802.99</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>09/14</v>
+        <v>09/21</v>
       </c>
       <c r="B37">
-        <v>188</v>
+        <v>242</v>
       </c>
       <c r="C37">
         <v>1</v>
       </c>
       <c r="D37">
-        <v>188</v>
+        <v>242</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>09/15</v>
+        <v>09/22</v>
       </c>
       <c r="B38">
-        <v>267</v>
+        <v>217.5</v>
       </c>
       <c r="C38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D38">
-        <v>267</v>
+        <v>435</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>09/16</v>
+        <v>09/23</v>
       </c>
       <c r="B39">
-        <v>242.5</v>
+        <v>184</v>
       </c>
       <c r="C39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D39">
-        <v>485</v>
+        <v>184</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>09/17</v>
+        <v>09/24</v>
       </c>
       <c r="B40">
-        <v>241.25666666666666</v>
+        <v>196.5</v>
       </c>
       <c r="C40">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D40">
-        <v>723.77</v>
+        <v>393</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>09/18</v>
+        <v>09/25</v>
       </c>
       <c r="B41">
-        <v>309.08380952380946</v>
+        <v>305.7857142857143</v>
       </c>
       <c r="C41">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D41">
-        <v>6490.759999999999</v>
+        <v>4281</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>09/19</v>
+        <v>09/26</v>
       </c>
       <c r="B42">
-        <v>304.075</v>
+        <v>328.5733333333334</v>
       </c>
       <c r="C42">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D42">
-        <v>7297.8</v>
+        <v>4928.6</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>09/20</v>
+        <v>09/27</v>
       </c>
       <c r="B43">
-        <v>225.37375</v>
+        <v>272.72875</v>
       </c>
       <c r="C43">
         <v>8</v>
       </c>
       <c r="D43">
-        <v>1802.99</v>
+        <v>2181.83</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>09/21</v>
+        <v>09/28</v>
       </c>
       <c r="B44">
-        <v>242</v>
+        <v>266</v>
       </c>
       <c r="C44">
         <v>1</v>
       </c>
       <c r="D44">
-        <v>242</v>
+        <v>266</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>09/22</v>
+        <v>09/29</v>
       </c>
       <c r="B45">
-        <v>251</v>
+        <v>265</v>
       </c>
       <c r="C45">
         <v>1</v>
       </c>
       <c r="D45">
-        <v>251</v>
+        <v>265</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>09/23</v>
+        <v>09/30</v>
       </c>
       <c r="B46">
-        <v>0</v>
+        <v>266</v>
       </c>
       <c r="C46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D46">
-        <v>0</v>
+        <v>266</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>09/24</v>
+        <v>10/01</v>
       </c>
       <c r="B47">
-        <v>0</v>
+        <v>190.5</v>
       </c>
       <c r="C47">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D47">
-        <v>0</v>
+        <v>381</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>09/25</v>
+        <v>10/02</v>
       </c>
       <c r="B48">
-        <v>328.1818181818182</v>
+        <v>320.3066666666667</v>
       </c>
       <c r="C48">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D48">
-        <v>3610</v>
+        <v>4804.6</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>09/26</v>
+        <v>10/03</v>
       </c>
       <c r="B49">
-        <v>336.9714285714286</v>
+        <v>318.3375</v>
       </c>
       <c r="C49">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D49">
-        <v>4717.6</v>
+        <v>5093.4</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>09/27</v>
+        <v>10/04</v>
       </c>
       <c r="B50">
-        <v>274.2857142857143</v>
+        <v>199.5</v>
       </c>
       <c r="C50">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D50">
-        <v>1920</v>
+        <v>399</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>09/28</v>
+        <v>10/05</v>
       </c>
       <c r="B51">
-        <v>266</v>
+        <v>193.5</v>
       </c>
       <c r="C51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D51">
-        <v>266</v>
+        <v>387</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>09/29</v>
+        <v>10/06</v>
       </c>
       <c r="B52">
-        <v>265</v>
+        <v>0</v>
       </c>
       <c r="C52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D52">
-        <v>265</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>09/30</v>
+        <v>10/07</v>
       </c>
       <c r="B53">
-        <v>266</v>
+        <v>249</v>
       </c>
       <c r="C53">
         <v>1</v>
       </c>
       <c r="D53">
-        <v>266</v>
+        <v>249</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>10/01</v>
+        <v>10/08</v>
       </c>
       <c r="B54">
-        <v>194</v>
+        <v>245.10500000000002</v>
       </c>
       <c r="C54">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D54">
-        <v>194</v>
+        <v>490.21000000000004</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>10/02</v>
+        <v>10/09</v>
       </c>
       <c r="B55">
-        <v>322.15999999999997</v>
+        <v>387.14625</v>
       </c>
       <c r="C55">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D55">
-        <v>3221.6</v>
+        <v>3097.17</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>10/03</v>
+        <v>10/10</v>
       </c>
       <c r="B56">
-        <v>314.40000000000003</v>
+        <v>376.1642857142857</v>
       </c>
       <c r="C56">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D56">
-        <v>3458.4</v>
+        <v>2633.15</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>10/04</v>
+        <v>10/11</v>
       </c>
       <c r="B57">
-        <v>199.5</v>
+        <v>336</v>
       </c>
       <c r="C57">
         <v>2</v>
       </c>
       <c r="D57">
-        <v>399</v>
+        <v>672</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>10/05</v>
+        <v>10/12</v>
       </c>
       <c r="B58">
-        <v>193.5</v>
+        <v>192</v>
       </c>
       <c r="C58">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D58">
-        <v>387</v>
+        <v>192</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>10/06</v>
+        <v>10/13</v>
       </c>
       <c r="B59">
-        <v>0</v>
+        <v>184</v>
       </c>
       <c r="C59">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D59">
-        <v>0</v>
+        <v>184</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>10/07</v>
+        <v>10/14</v>
       </c>
       <c r="B60">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="C60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D60">
-        <v>0</v>
+        <v>190</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>10/08</v>
+        <v>10/15</v>
       </c>
       <c r="B61">
-        <v>222.21</v>
+        <v>0</v>
       </c>
       <c r="C61">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D61">
-        <v>222.21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>10/09</v>
+        <v>10/16</v>
       </c>
       <c r="B62">
-        <v>446.45285714285717</v>
+        <v>341.77777777777777</v>
       </c>
       <c r="C62">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D62">
-        <v>3125.17</v>
+        <v>3076</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>10/10</v>
+        <v>10/17</v>
       </c>
       <c r="B63">
-        <v>445.02500000000003</v>
+        <v>337.3333333333333</v>
       </c>
       <c r="C63">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D63">
-        <v>2670.15</v>
+        <v>4048</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>10/11</v>
+        <v>10/18</v>
       </c>
       <c r="B64">
-        <v>336</v>
+        <v>231</v>
       </c>
       <c r="C64">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D64">
-        <v>672</v>
+        <v>924</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>10/12</v>
+        <v>10/19</v>
       </c>
       <c r="B65">
-        <v>192</v>
+        <v>232</v>
       </c>
       <c r="C65">
         <v>1</v>
       </c>
       <c r="D65">
-        <v>192</v>
+        <v>232</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>10/13</v>
+        <v>10/20</v>
       </c>
       <c r="B66">
-        <v>184</v>
+        <v>0</v>
       </c>
       <c r="C66">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D66">
-        <v>184</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>10/14</v>
+        <v>10/21</v>
       </c>
       <c r="B67">
-        <v>190</v>
+        <v>149</v>
       </c>
       <c r="C67">
         <v>1</v>
       </c>
       <c r="D67">
-        <v>190</v>
+        <v>149</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>10/15</v>
+        <v>10/22</v>
       </c>
       <c r="B68">
-        <v>0</v>
+        <v>220.846</v>
       </c>
       <c r="C68">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D68">
-        <v>0</v>
+        <v>1104.23</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>10/16</v>
+        <v>10/23</v>
       </c>
       <c r="B69">
-        <v>352.25</v>
+        <v>294.88499999999993</v>
       </c>
       <c r="C69">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D69">
-        <v>2818</v>
+        <v>4128.389999999999</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>10/17</v>
+        <v>10/24</v>
       </c>
       <c r="B70">
-        <v>344.45454545454544</v>
+        <v>295.25307692307695</v>
       </c>
       <c r="C70">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D70">
-        <v>3789</v>
+        <v>3838.29</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>10/18</v>
+        <v>10/25</v>
       </c>
       <c r="B71">
-        <v>250.5</v>
+        <v>217</v>
       </c>
       <c r="C71">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D71">
-        <v>1002</v>
+        <v>651</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>10/19</v>
+        <v>10/26</v>
       </c>
       <c r="B72">
-        <v>230.5</v>
+        <v>220</v>
       </c>
       <c r="C72">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D72">
-        <v>461</v>
+        <v>660</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>10/20</v>
+        <v>10/27</v>
       </c>
       <c r="B73">
         <v>0</v>
@@ -1423,91 +1423,91 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>10/21</v>
+        <v>10/28</v>
       </c>
       <c r="B74">
-        <v>149</v>
+        <v>135.15</v>
       </c>
       <c r="C74">
         <v>1</v>
       </c>
       <c r="D74">
-        <v>149</v>
+        <v>135.15</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>10/22</v>
+        <v>10/29</v>
       </c>
       <c r="B75">
-        <v>220.846</v>
+        <v>164.25</v>
       </c>
       <c r="C75">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D75">
-        <v>1104.23</v>
+        <v>328.5</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>10/23</v>
+        <v>10/30</v>
       </c>
       <c r="B76">
-        <v>296.46153846153845</v>
+        <v>264.8</v>
       </c>
       <c r="C76">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D76">
-        <v>3854</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>10/24</v>
+        <v>10/31</v>
       </c>
       <c r="B77">
-        <v>296.75</v>
+        <v>276.5</v>
       </c>
       <c r="C77">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D77">
-        <v>3561</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>10/25</v>
+        <v>11/01</v>
       </c>
       <c r="B78">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="C78">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D78">
-        <v>651</v>
+        <v>448</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>10/26</v>
+        <v>11/02</v>
       </c>
       <c r="B79">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="C79">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D79">
-        <v>660</v>
+        <v>229</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>10/27</v>
+        <v>11/03</v>
       </c>
       <c r="B80">
         <v>0</v>
@@ -1521,91 +1521,91 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>10/28</v>
+        <v>11/04</v>
       </c>
       <c r="B81">
-        <v>135.15</v>
+        <v>0</v>
       </c>
       <c r="C81">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D81">
-        <v>135.15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>10/29</v>
+        <v>11/05</v>
       </c>
       <c r="B82">
-        <v>164.25</v>
+        <v>0</v>
       </c>
       <c r="C82">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D82">
-        <v>328.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>10/30</v>
+        <v>11/06</v>
       </c>
       <c r="B83">
-        <v>273.5</v>
+        <v>284.5833333333333</v>
       </c>
       <c r="C83">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D83">
-        <v>1094</v>
+        <v>853.75</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>10/31</v>
+        <v>11/07</v>
       </c>
       <c r="B84">
-        <v>291</v>
+        <v>284.28333333333336</v>
       </c>
       <c r="C84">
         <v>3</v>
       </c>
       <c r="D84">
-        <v>873</v>
+        <v>852.85</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>11/01</v>
+        <v>11/08</v>
       </c>
       <c r="B85">
-        <v>224</v>
+        <v>0</v>
       </c>
       <c r="C85">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D85">
-        <v>448</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>11/02</v>
+        <v>11/09</v>
       </c>
       <c r="B86">
-        <v>229</v>
+        <v>0</v>
       </c>
       <c r="C86">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D86">
-        <v>229</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>11/03</v>
+        <v>11/10</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -1619,7 +1619,7 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>11/04</v>
+        <v>11/11</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -1633,7 +1633,7 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>11/05</v>
+        <v>11/12</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -1647,35 +1647,35 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>11/06</v>
+        <v>11/13</v>
       </c>
       <c r="B90">
-        <v>278.375</v>
+        <v>0</v>
       </c>
       <c r="C90">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D90">
-        <v>556.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>11/07</v>
+        <v>11/14</v>
       </c>
       <c r="B91">
-        <v>280.925</v>
+        <v>0</v>
       </c>
       <c r="C91">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D91">
-        <v>561.85</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>11/08</v>
+        <v>11/15</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -1689,7 +1689,7 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>11/09</v>
+        <v>11/16</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -1703,7 +1703,7 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>11/10</v>
+        <v>11/17</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -1717,7 +1717,7 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>11/11</v>
+        <v>11/18</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -1731,7 +1731,7 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>11/12</v>
+        <v>11/19</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -1745,7 +1745,7 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>11/13</v>
+        <v>11/20</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -1759,7 +1759,7 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>11/14</v>
+        <v>11/21</v>
       </c>
       <c r="B98">
         <v>0</v>
@@ -1773,7 +1773,7 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>11/15</v>
+        <v>11/22</v>
       </c>
       <c r="B99">
         <v>0</v>
@@ -1787,7 +1787,7 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>11/16</v>
+        <v>11/23</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>11/17</v>
+        <v>11/24</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -1815,7 +1815,7 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>11/18</v>
+        <v>11/25</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -1829,7 +1829,7 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>11/19</v>
+        <v>11/26</v>
       </c>
       <c r="B103">
         <v>0</v>
@@ -1843,7 +1843,7 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>11/20</v>
+        <v>11/27</v>
       </c>
       <c r="B104">
         <v>0</v>
@@ -1857,7 +1857,7 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>11/21</v>
+        <v>11/28</v>
       </c>
       <c r="B105">
         <v>0</v>
@@ -1871,7 +1871,7 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>11/22</v>
+        <v>11/29</v>
       </c>
       <c r="B106">
         <v>0</v>
@@ -1885,7 +1885,7 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>11/23</v>
+        <v>11/30</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -1899,7 +1899,7 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>11/24</v>
+        <v>12/01</v>
       </c>
       <c r="B108">
         <v>0</v>
@@ -1913,7 +1913,7 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>11/25</v>
+        <v>12/02</v>
       </c>
       <c r="B109">
         <v>0</v>
@@ -1927,7 +1927,7 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>11/26</v>
+        <v>12/03</v>
       </c>
       <c r="B110">
         <v>0</v>
@@ -1941,7 +1941,7 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>11/27</v>
+        <v>12/04</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -1955,7 +1955,7 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>11/28</v>
+        <v>12/05</v>
       </c>
       <c r="B112">
         <v>0</v>
@@ -1969,7 +1969,7 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>11/29</v>
+        <v>12/06</v>
       </c>
       <c r="B113">
         <v>0</v>
@@ -1983,7 +1983,7 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>11/30</v>
+        <v>12/07</v>
       </c>
       <c r="B114">
         <v>0</v>
@@ -1997,7 +1997,7 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>12/01</v>
+        <v>12/08</v>
       </c>
       <c r="B115">
         <v>0</v>
@@ -2011,7 +2011,7 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>12/02</v>
+        <v>12/09</v>
       </c>
       <c r="B116">
         <v>0</v>
@@ -2025,7 +2025,7 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>12/03</v>
+        <v>12/10</v>
       </c>
       <c r="B117">
         <v>0</v>
@@ -2039,7 +2039,7 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>12/04</v>
+        <v>12/11</v>
       </c>
       <c r="B118">
         <v>0</v>
@@ -2053,7 +2053,7 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>12/05</v>
+        <v>12/12</v>
       </c>
       <c r="B119">
         <v>0</v>
@@ -2067,7 +2067,7 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>12/06</v>
+        <v>12/13</v>
       </c>
       <c r="B120">
         <v>0</v>
@@ -2081,7 +2081,7 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>12/07</v>
+        <v>12/14</v>
       </c>
       <c r="B121">
         <v>0</v>
@@ -2095,7 +2095,7 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>12/08</v>
+        <v>12/15</v>
       </c>
       <c r="B122">
         <v>0</v>
@@ -2109,7 +2109,7 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>12/09</v>
+        <v>12/16</v>
       </c>
       <c r="B123">
         <v>0</v>
@@ -2123,7 +2123,7 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>12/10</v>
+        <v>12/17</v>
       </c>
       <c r="B124">
         <v>0</v>
@@ -2132,12 +2132,208 @@
         <v>0</v>
       </c>
       <c r="D124">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>12/18</v>
+      </c>
+      <c r="B125">
+        <v>0</v>
+      </c>
+      <c r="C125">
+        <v>0</v>
+      </c>
+      <c r="D125">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>12/19</v>
+      </c>
+      <c r="B126">
+        <v>0</v>
+      </c>
+      <c r="C126">
+        <v>0</v>
+      </c>
+      <c r="D126">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>12/20</v>
+      </c>
+      <c r="B127">
+        <v>0</v>
+      </c>
+      <c r="C127">
+        <v>0</v>
+      </c>
+      <c r="D127">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>12/21</v>
+      </c>
+      <c r="B128">
+        <v>0</v>
+      </c>
+      <c r="C128">
+        <v>0</v>
+      </c>
+      <c r="D128">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>12/22</v>
+      </c>
+      <c r="B129">
+        <v>0</v>
+      </c>
+      <c r="C129">
+        <v>0</v>
+      </c>
+      <c r="D129">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="str">
+        <v>12/23</v>
+      </c>
+      <c r="B130">
+        <v>0</v>
+      </c>
+      <c r="C130">
+        <v>0</v>
+      </c>
+      <c r="D130">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="str">
+        <v>12/24</v>
+      </c>
+      <c r="B131">
+        <v>0</v>
+      </c>
+      <c r="C131">
+        <v>0</v>
+      </c>
+      <c r="D131">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="str">
+        <v>12/25</v>
+      </c>
+      <c r="B132">
+        <v>0</v>
+      </c>
+      <c r="C132">
+        <v>0</v>
+      </c>
+      <c r="D132">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="str">
+        <v>12/26</v>
+      </c>
+      <c r="B133">
+        <v>0</v>
+      </c>
+      <c r="C133">
+        <v>0</v>
+      </c>
+      <c r="D133">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="str">
+        <v>12/27</v>
+      </c>
+      <c r="B134">
+        <v>0</v>
+      </c>
+      <c r="C134">
+        <v>0</v>
+      </c>
+      <c r="D134">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="str">
+        <v>12/28</v>
+      </c>
+      <c r="B135">
+        <v>0</v>
+      </c>
+      <c r="C135">
+        <v>0</v>
+      </c>
+      <c r="D135">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="str">
+        <v>12/29</v>
+      </c>
+      <c r="B136">
+        <v>0</v>
+      </c>
+      <c r="C136">
+        <v>0</v>
+      </c>
+      <c r="D136">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="str">
+        <v>12/30</v>
+      </c>
+      <c r="B137">
+        <v>0</v>
+      </c>
+      <c r="C137">
+        <v>0</v>
+      </c>
+      <c r="D137">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="str">
+        <v>12/31</v>
+      </c>
+      <c r="B138">
+        <v>0</v>
+      </c>
+      <c r="C138">
+        <v>0</v>
+      </c>
+      <c r="D138">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D124"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D138"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/PA-PL_occupancy_pace_150day.xlsx
+++ b/PA-PL_occupancy_pace_150day.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D138"/>
+  <dimension ref="A1:D131"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -415,903 +415,903 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>08/17</v>
+        <v>08/24</v>
       </c>
       <c r="B2">
-        <v>273.8828571428572</v>
+        <v>242.41799999999998</v>
       </c>
       <c r="C2">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D2">
-        <v>3834.36</v>
+        <v>4848.36</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>08/18</v>
+        <v>08/25</v>
       </c>
       <c r="B3">
-        <v>265.61249999999995</v>
+        <v>234.25842105263158</v>
       </c>
       <c r="C3">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D3">
-        <v>4249.799999999999</v>
+        <v>4450.91</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>08/19</v>
+        <v>08/26</v>
       </c>
       <c r="B4">
-        <v>240.57142857142858</v>
+        <v>237.16533333333334</v>
       </c>
       <c r="C4">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D4">
-        <v>3368</v>
+        <v>3557.48</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>08/20</v>
+        <v>08/27</v>
       </c>
       <c r="B5">
-        <v>247.20999999999998</v>
+        <v>254.9125</v>
       </c>
       <c r="C5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D5">
-        <v>2472.1</v>
+        <v>2039.3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>08/21</v>
+        <v>08/28</v>
       </c>
       <c r="B6">
-        <v>307.502</v>
+        <v>316.4173333333334</v>
       </c>
       <c r="C6">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D6">
-        <v>6150.04</v>
+        <v>4746.26</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>08/22</v>
+        <v>08/29</v>
       </c>
       <c r="B7">
-        <v>289.71695652173906</v>
+        <v>311.678125</v>
       </c>
       <c r="C7">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="D7">
-        <v>6663.489999999998</v>
+        <v>4986.85</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>08/23</v>
+        <v>08/30</v>
       </c>
       <c r="B8">
-        <v>275.8961538461539</v>
+        <v>275.3333333333333</v>
       </c>
       <c r="C8">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D8">
-        <v>3586.65</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>08/24</v>
+        <v>08/31</v>
       </c>
       <c r="B9">
-        <v>254.6475</v>
+        <v>254.908</v>
       </c>
       <c r="C9">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="D9">
-        <v>4074.36</v>
+        <v>1274.54</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>08/25</v>
+        <v>09/01</v>
       </c>
       <c r="B10">
-        <v>247.37624999999997</v>
+        <v>256</v>
       </c>
       <c r="C10">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="D10">
-        <v>3958.0199999999995</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>08/26</v>
+        <v>09/02</v>
       </c>
       <c r="B11">
-        <v>235.92153846153843</v>
+        <v>231.5</v>
       </c>
       <c r="C11">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D11">
-        <v>3066.9799999999996</v>
+        <v>1852</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>08/27</v>
+        <v>09/03</v>
       </c>
       <c r="B12">
-        <v>254.9125</v>
+        <v>248.675</v>
       </c>
       <c r="C12">
         <v>8</v>
       </c>
       <c r="D12">
-        <v>2039.3</v>
+        <v>1989.4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>08/28</v>
+        <v>09/04</v>
       </c>
       <c r="B13">
-        <v>336.33666666666664</v>
+        <v>404.6769230769231</v>
       </c>
       <c r="C13">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D13">
-        <v>4036.04</v>
+        <v>5260.8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>08/29</v>
+        <v>09/05</v>
       </c>
       <c r="B14">
-        <v>333.31000000000006</v>
+        <v>402.1855</v>
       </c>
       <c r="C14">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D14">
-        <v>4333.030000000001</v>
+        <v>8043.71</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>08/30</v>
+        <v>09/06</v>
       </c>
       <c r="B15">
-        <v>275.3333333333333</v>
+        <v>364.35181818181815</v>
       </c>
       <c r="C15">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D15">
-        <v>1652</v>
+        <v>4007.87</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>08/31</v>
+        <v>09/07</v>
       </c>
       <c r="B16">
-        <v>254.908</v>
+        <v>229.61666666666667</v>
       </c>
       <c r="C16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D16">
-        <v>1274.54</v>
+        <v>1377.7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>09/01</v>
+        <v>09/08</v>
       </c>
       <c r="B17">
-        <v>268.25</v>
+        <v>213.42222222222222</v>
       </c>
       <c r="C17">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D17">
-        <v>1073</v>
+        <v>1920.8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>09/02</v>
+        <v>09/09</v>
       </c>
       <c r="B18">
-        <v>225</v>
+        <v>220.65</v>
       </c>
       <c r="C18">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D18">
-        <v>1125</v>
+        <v>882.6</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>09/03</v>
+        <v>09/10</v>
       </c>
       <c r="B19">
-        <v>240.62857142857143</v>
+        <v>226.57</v>
       </c>
       <c r="C19">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D19">
-        <v>1684.4</v>
+        <v>453.14</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>09/04</v>
+        <v>09/11</v>
       </c>
       <c r="B20">
-        <v>413.06666666666666</v>
+        <v>279.9430769230769</v>
       </c>
       <c r="C20">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D20">
-        <v>4956.8</v>
+        <v>3639.2599999999998</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>09/05</v>
+        <v>09/12</v>
       </c>
       <c r="B21">
-        <v>404.3394444444445</v>
+        <v>283.8566666666667</v>
       </c>
       <c r="C21">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D21">
-        <v>7278.110000000001</v>
+        <v>4257.85</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>09/06</v>
+        <v>09/13</v>
       </c>
       <c r="B22">
-        <v>367.75307692307695</v>
+        <v>208.6</v>
       </c>
       <c r="C22">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D22">
-        <v>4780.79</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>09/07</v>
+        <v>09/14</v>
       </c>
       <c r="B23">
-        <v>220.08333333333334</v>
+        <v>190.5</v>
       </c>
       <c r="C23">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D23">
-        <v>1320.5</v>
+        <v>381</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>09/08</v>
+        <v>09/15</v>
       </c>
       <c r="B24">
-        <v>218.14285714285714</v>
+        <v>236.5</v>
       </c>
       <c r="C24">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D24">
-        <v>1527</v>
+        <v>473</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>09/09</v>
+        <v>09/16</v>
       </c>
       <c r="B25">
-        <v>234</v>
+        <v>252.66666666666666</v>
       </c>
       <c r="C25">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D25">
-        <v>468</v>
+        <v>758</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>09/10</v>
+        <v>09/17</v>
       </c>
       <c r="B26">
-        <v>226.57</v>
+        <v>260.354</v>
       </c>
       <c r="C26">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D26">
-        <v>453.14</v>
+        <v>1301.77</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>09/11</v>
+        <v>09/18</v>
       </c>
       <c r="B27">
-        <v>275.64214285714286</v>
+        <v>314.0555</v>
       </c>
       <c r="C27">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D27">
-        <v>3858.99</v>
+        <v>6281.11</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>09/12</v>
+        <v>09/19</v>
       </c>
       <c r="B28">
-        <v>280.41999999999996</v>
+        <v>307.12416666666667</v>
       </c>
       <c r="C28">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D28">
-        <v>4486.719999999999</v>
+        <v>7370.98</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>09/13</v>
+        <v>09/20</v>
       </c>
       <c r="B29">
-        <v>209.75</v>
+        <v>237.3990909090909</v>
       </c>
       <c r="C29">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D29">
-        <v>839</v>
+        <v>2611.39</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>09/14</v>
+        <v>09/21</v>
       </c>
       <c r="B30">
-        <v>188</v>
+        <v>214.5</v>
       </c>
       <c r="C30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D30">
-        <v>188</v>
+        <v>429</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>09/15</v>
+        <v>09/22</v>
       </c>
       <c r="B31">
-        <v>267</v>
+        <v>206.33333333333334</v>
       </c>
       <c r="C31">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D31">
-        <v>267</v>
+        <v>619</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>09/16</v>
+        <v>09/23</v>
       </c>
       <c r="B32">
-        <v>252.66666666666666</v>
+        <v>206.5</v>
       </c>
       <c r="C32">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D32">
-        <v>758</v>
+        <v>413</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>09/17</v>
+        <v>09/24</v>
       </c>
       <c r="B33">
-        <v>260.354</v>
+        <v>220.33333333333334</v>
       </c>
       <c r="C33">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D33">
-        <v>1301.77</v>
+        <v>661</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>09/18</v>
+        <v>09/25</v>
       </c>
       <c r="B34">
-        <v>314.05550000000005</v>
+        <v>292.2</v>
       </c>
       <c r="C34">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D34">
-        <v>6281.110000000001</v>
+        <v>4967.4</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>09/19</v>
+        <v>09/26</v>
       </c>
       <c r="B35">
-        <v>308.3904347826087</v>
+        <v>313.4222222222222</v>
       </c>
       <c r="C35">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D35">
-        <v>7092.98</v>
+        <v>5641.6</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>09/20</v>
+        <v>09/27</v>
       </c>
       <c r="B36">
-        <v>225.37375</v>
+        <v>272.72875</v>
       </c>
       <c r="C36">
         <v>8</v>
       </c>
       <c r="D36">
-        <v>1802.99</v>
+        <v>2181.83</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>09/21</v>
+        <v>09/28</v>
       </c>
       <c r="B37">
-        <v>242</v>
+        <v>266</v>
       </c>
       <c r="C37">
         <v>1</v>
       </c>
       <c r="D37">
-        <v>242</v>
+        <v>266</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>09/22</v>
+        <v>09/29</v>
       </c>
       <c r="B38">
-        <v>217.5</v>
+        <v>265</v>
       </c>
       <c r="C38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D38">
-        <v>435</v>
+        <v>265</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>09/23</v>
+        <v>09/30</v>
       </c>
       <c r="B39">
-        <v>184</v>
+        <v>266</v>
       </c>
       <c r="C39">
         <v>1</v>
       </c>
       <c r="D39">
-        <v>184</v>
+        <v>266</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>09/24</v>
+        <v>10/01</v>
       </c>
       <c r="B40">
-        <v>196.5</v>
+        <v>190.5</v>
       </c>
       <c r="C40">
         <v>2</v>
       </c>
       <c r="D40">
-        <v>393</v>
+        <v>381</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>09/25</v>
+        <v>10/02</v>
       </c>
       <c r="B41">
-        <v>305.7857142857143</v>
+        <v>304.0842105263158</v>
       </c>
       <c r="C41">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D41">
-        <v>4281</v>
+        <v>5777.6</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>09/26</v>
+        <v>10/03</v>
       </c>
       <c r="B42">
-        <v>328.5733333333334</v>
+        <v>305.37</v>
       </c>
       <c r="C42">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D42">
-        <v>4928.6</v>
+        <v>6107.4</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>09/27</v>
+        <v>10/04</v>
       </c>
       <c r="B43">
-        <v>272.72875</v>
+        <v>199.5</v>
       </c>
       <c r="C43">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D43">
-        <v>2181.83</v>
+        <v>399</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>09/28</v>
+        <v>10/05</v>
       </c>
       <c r="B44">
-        <v>266</v>
+        <v>193.5</v>
       </c>
       <c r="C44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D44">
-        <v>266</v>
+        <v>387</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>09/29</v>
+        <v>10/06</v>
       </c>
       <c r="B45">
-        <v>265</v>
+        <v>0</v>
       </c>
       <c r="C45">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D45">
-        <v>265</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>09/30</v>
+        <v>10/07</v>
       </c>
       <c r="B46">
-        <v>266</v>
+        <v>249</v>
       </c>
       <c r="C46">
         <v>1</v>
       </c>
       <c r="D46">
-        <v>266</v>
+        <v>249</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>10/01</v>
+        <v>10/08</v>
       </c>
       <c r="B47">
-        <v>190.5</v>
+        <v>268</v>
       </c>
       <c r="C47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D47">
-        <v>381</v>
+        <v>268</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>10/02</v>
+        <v>10/09</v>
       </c>
       <c r="B48">
-        <v>320.3066666666667</v>
+        <v>364.82384615384615</v>
       </c>
       <c r="C48">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D48">
-        <v>4804.6</v>
+        <v>4742.71</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>10/03</v>
+        <v>10/10</v>
       </c>
       <c r="B49">
-        <v>318.3375</v>
+        <v>345.1614285714286</v>
       </c>
       <c r="C49">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D49">
-        <v>5093.4</v>
+        <v>4832.26</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>10/04</v>
+        <v>10/11</v>
       </c>
       <c r="B50">
-        <v>199.5</v>
+        <v>318.69166666666666</v>
       </c>
       <c r="C50">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D50">
-        <v>399</v>
+        <v>1912.15</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>10/05</v>
+        <v>10/12</v>
       </c>
       <c r="B51">
-        <v>193.5</v>
+        <v>169.91</v>
       </c>
       <c r="C51">
         <v>2</v>
       </c>
       <c r="D51">
-        <v>387</v>
+        <v>339.82</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>10/06</v>
+        <v>10/13</v>
       </c>
       <c r="B52">
-        <v>0</v>
+        <v>184</v>
       </c>
       <c r="C52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D52">
-        <v>0</v>
+        <v>184</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>10/07</v>
+        <v>10/14</v>
       </c>
       <c r="B53">
-        <v>249</v>
+        <v>190</v>
       </c>
       <c r="C53">
         <v>1</v>
       </c>
       <c r="D53">
-        <v>249</v>
+        <v>190</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>10/08</v>
+        <v>10/15</v>
       </c>
       <c r="B54">
-        <v>245.10500000000002</v>
+        <v>0</v>
       </c>
       <c r="C54">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D54">
-        <v>490.21000000000004</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>10/09</v>
+        <v>10/16</v>
       </c>
       <c r="B55">
-        <v>387.14625</v>
+        <v>332.5</v>
       </c>
       <c r="C55">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D55">
-        <v>3097.17</v>
+        <v>3325</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>10/10</v>
+        <v>10/17</v>
       </c>
       <c r="B56">
-        <v>376.1642857142857</v>
+        <v>326.5</v>
       </c>
       <c r="C56">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D56">
-        <v>2633.15</v>
+        <v>4571</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>10/11</v>
+        <v>10/18</v>
       </c>
       <c r="B57">
-        <v>336</v>
+        <v>230.6</v>
       </c>
       <c r="C57">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D57">
-        <v>672</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>10/12</v>
+        <v>10/19</v>
       </c>
       <c r="B58">
-        <v>192</v>
+        <v>232</v>
       </c>
       <c r="C58">
         <v>1</v>
       </c>
       <c r="D58">
-        <v>192</v>
+        <v>232</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>10/13</v>
+        <v>10/20</v>
       </c>
       <c r="B59">
-        <v>184</v>
+        <v>0</v>
       </c>
       <c r="C59">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D59">
-        <v>184</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>10/14</v>
+        <v>10/21</v>
       </c>
       <c r="B60">
-        <v>190</v>
+        <v>168.20000000000002</v>
       </c>
       <c r="C60">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D60">
-        <v>190</v>
+        <v>672.8000000000001</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>10/15</v>
+        <v>10/22</v>
       </c>
       <c r="B61">
-        <v>0</v>
+        <v>203.50375</v>
       </c>
       <c r="C61">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D61">
-        <v>0</v>
+        <v>1628.03</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>10/16</v>
+        <v>10/23</v>
       </c>
       <c r="B62">
-        <v>341.77777777777777</v>
+        <v>287.9</v>
       </c>
       <c r="C62">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D62">
-        <v>3076</v>
+        <v>4606.4</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>10/17</v>
+        <v>10/24</v>
       </c>
       <c r="B63">
-        <v>337.3333333333333</v>
+        <v>288.22</v>
       </c>
       <c r="C63">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D63">
-        <v>4048</v>
+        <v>4323.3</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>10/18</v>
+        <v>10/25</v>
       </c>
       <c r="B64">
-        <v>231</v>
+        <v>217</v>
       </c>
       <c r="C64">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D64">
-        <v>924</v>
+        <v>651</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>10/19</v>
+        <v>10/26</v>
       </c>
       <c r="B65">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="C65">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D65">
-        <v>232</v>
+        <v>660</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>10/20</v>
+        <v>10/27</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -1325,91 +1325,91 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>10/21</v>
+        <v>10/28</v>
       </c>
       <c r="B67">
-        <v>149</v>
+        <v>135.15</v>
       </c>
       <c r="C67">
         <v>1</v>
       </c>
       <c r="D67">
-        <v>149</v>
+        <v>135.15</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>10/22</v>
+        <v>10/29</v>
       </c>
       <c r="B68">
-        <v>220.846</v>
+        <v>164.25</v>
       </c>
       <c r="C68">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D68">
-        <v>1104.23</v>
+        <v>328.5</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>10/23</v>
+        <v>10/30</v>
       </c>
       <c r="B69">
-        <v>294.88499999999993</v>
+        <v>269</v>
       </c>
       <c r="C69">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D69">
-        <v>4128.389999999999</v>
+        <v>2421</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>10/24</v>
+        <v>10/31</v>
       </c>
       <c r="B70">
-        <v>295.25307692307695</v>
+        <v>278.875</v>
       </c>
       <c r="C70">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D70">
-        <v>3838.29</v>
+        <v>2231</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>10/25</v>
+        <v>11/01</v>
       </c>
       <c r="B71">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="C71">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D71">
-        <v>651</v>
+        <v>448</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>10/26</v>
+        <v>11/02</v>
       </c>
       <c r="B72">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="C72">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D72">
-        <v>660</v>
+        <v>229</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>10/27</v>
+        <v>11/03</v>
       </c>
       <c r="B73">
         <v>0</v>
@@ -1423,91 +1423,91 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>10/28</v>
+        <v>11/04</v>
       </c>
       <c r="B74">
-        <v>135.15</v>
+        <v>0</v>
       </c>
       <c r="C74">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D74">
-        <v>135.15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>10/29</v>
+        <v>11/05</v>
       </c>
       <c r="B75">
-        <v>164.25</v>
+        <v>0</v>
       </c>
       <c r="C75">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D75">
-        <v>328.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>10/30</v>
+        <v>11/06</v>
       </c>
       <c r="B76">
-        <v>264.8</v>
+        <v>284.5833333333333</v>
       </c>
       <c r="C76">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D76">
-        <v>1324</v>
+        <v>853.75</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>10/31</v>
+        <v>11/07</v>
       </c>
       <c r="B77">
-        <v>276.5</v>
+        <v>284.2833333333333</v>
       </c>
       <c r="C77">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D77">
-        <v>1106</v>
+        <v>852.8499999999999</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>11/01</v>
+        <v>11/08</v>
       </c>
       <c r="B78">
-        <v>224</v>
+        <v>0</v>
       </c>
       <c r="C78">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D78">
-        <v>448</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>11/02</v>
+        <v>11/09</v>
       </c>
       <c r="B79">
-        <v>229</v>
+        <v>0</v>
       </c>
       <c r="C79">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D79">
-        <v>229</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>11/03</v>
+        <v>11/10</v>
       </c>
       <c r="B80">
         <v>0</v>
@@ -1521,7 +1521,7 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>11/04</v>
+        <v>11/11</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -1535,7 +1535,7 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>11/05</v>
+        <v>11/12</v>
       </c>
       <c r="B82">
         <v>0</v>
@@ -1549,35 +1549,35 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>11/06</v>
+        <v>11/13</v>
       </c>
       <c r="B83">
-        <v>284.5833333333333</v>
+        <v>313</v>
       </c>
       <c r="C83">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D83">
-        <v>853.75</v>
+        <v>313</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>11/07</v>
+        <v>11/14</v>
       </c>
       <c r="B84">
-        <v>284.28333333333336</v>
+        <v>323</v>
       </c>
       <c r="C84">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D84">
-        <v>852.85</v>
+        <v>323</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>11/08</v>
+        <v>11/15</v>
       </c>
       <c r="B85">
         <v>0</v>
@@ -1591,7 +1591,7 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>11/09</v>
+        <v>11/16</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -1605,7 +1605,7 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>11/10</v>
+        <v>11/17</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -1619,7 +1619,7 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>11/11</v>
+        <v>11/18</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -1633,7 +1633,7 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>11/12</v>
+        <v>11/19</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -1647,35 +1647,35 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>11/13</v>
+        <v>11/20</v>
       </c>
       <c r="B90">
-        <v>0</v>
+        <v>236.55</v>
       </c>
       <c r="C90">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D90">
-        <v>0</v>
+        <v>473.1</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>11/14</v>
+        <v>11/21</v>
       </c>
       <c r="B91">
-        <v>0</v>
+        <v>240.35</v>
       </c>
       <c r="C91">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D91">
-        <v>0</v>
+        <v>480.7</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>11/15</v>
+        <v>11/22</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -1689,7 +1689,7 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>11/16</v>
+        <v>11/23</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -1703,7 +1703,7 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>11/17</v>
+        <v>11/24</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -1717,7 +1717,7 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>11/18</v>
+        <v>11/25</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -1731,7 +1731,7 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>11/19</v>
+        <v>11/26</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -1745,7 +1745,7 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>11/20</v>
+        <v>11/27</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -1759,7 +1759,7 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>11/21</v>
+        <v>11/28</v>
       </c>
       <c r="B98">
         <v>0</v>
@@ -1773,7 +1773,7 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>11/22</v>
+        <v>11/29</v>
       </c>
       <c r="B99">
         <v>0</v>
@@ -1787,7 +1787,7 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>11/23</v>
+        <v>11/30</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>11/24</v>
+        <v>12/01</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -1815,7 +1815,7 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>11/25</v>
+        <v>12/02</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -1829,7 +1829,7 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>11/26</v>
+        <v>12/03</v>
       </c>
       <c r="B103">
         <v>0</v>
@@ -1843,7 +1843,7 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>11/27</v>
+        <v>12/04</v>
       </c>
       <c r="B104">
         <v>0</v>
@@ -1857,7 +1857,7 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>11/28</v>
+        <v>12/05</v>
       </c>
       <c r="B105">
         <v>0</v>
@@ -1871,7 +1871,7 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>11/29</v>
+        <v>12/06</v>
       </c>
       <c r="B106">
         <v>0</v>
@@ -1885,7 +1885,7 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>11/30</v>
+        <v>12/07</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -1899,7 +1899,7 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>12/01</v>
+        <v>12/08</v>
       </c>
       <c r="B108">
         <v>0</v>
@@ -1913,7 +1913,7 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>12/02</v>
+        <v>12/09</v>
       </c>
       <c r="B109">
         <v>0</v>
@@ -1927,7 +1927,7 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>12/03</v>
+        <v>12/10</v>
       </c>
       <c r="B110">
         <v>0</v>
@@ -1941,7 +1941,7 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>12/04</v>
+        <v>12/11</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -1955,7 +1955,7 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>12/05</v>
+        <v>12/12</v>
       </c>
       <c r="B112">
         <v>0</v>
@@ -1969,7 +1969,7 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>12/06</v>
+        <v>12/13</v>
       </c>
       <c r="B113">
         <v>0</v>
@@ -1983,7 +1983,7 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>12/07</v>
+        <v>12/14</v>
       </c>
       <c r="B114">
         <v>0</v>
@@ -1997,7 +1997,7 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>12/08</v>
+        <v>12/15</v>
       </c>
       <c r="B115">
         <v>0</v>
@@ -2011,7 +2011,7 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>12/09</v>
+        <v>12/16</v>
       </c>
       <c r="B116">
         <v>0</v>
@@ -2025,7 +2025,7 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>12/10</v>
+        <v>12/17</v>
       </c>
       <c r="B117">
         <v>0</v>
@@ -2039,7 +2039,7 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>12/11</v>
+        <v>12/18</v>
       </c>
       <c r="B118">
         <v>0</v>
@@ -2053,7 +2053,7 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>12/12</v>
+        <v>12/19</v>
       </c>
       <c r="B119">
         <v>0</v>
@@ -2067,7 +2067,7 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>12/13</v>
+        <v>12/20</v>
       </c>
       <c r="B120">
         <v>0</v>
@@ -2081,7 +2081,7 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>12/14</v>
+        <v>12/21</v>
       </c>
       <c r="B121">
         <v>0</v>
@@ -2095,7 +2095,7 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>12/15</v>
+        <v>12/22</v>
       </c>
       <c r="B122">
         <v>0</v>
@@ -2109,7 +2109,7 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>12/16</v>
+        <v>12/23</v>
       </c>
       <c r="B123">
         <v>0</v>
@@ -2123,7 +2123,7 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>12/17</v>
+        <v>12/24</v>
       </c>
       <c r="B124">
         <v>0</v>
@@ -2137,7 +2137,7 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>12/18</v>
+        <v>12/25</v>
       </c>
       <c r="B125">
         <v>0</v>
@@ -2151,7 +2151,7 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>12/19</v>
+        <v>12/26</v>
       </c>
       <c r="B126">
         <v>0</v>
@@ -2165,7 +2165,7 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>12/20</v>
+        <v>12/27</v>
       </c>
       <c r="B127">
         <v>0</v>
@@ -2179,7 +2179,7 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>12/21</v>
+        <v>12/28</v>
       </c>
       <c r="B128">
         <v>0</v>
@@ -2193,7 +2193,7 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>12/22</v>
+        <v>12/29</v>
       </c>
       <c r="B129">
         <v>0</v>
@@ -2207,7 +2207,7 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>12/23</v>
+        <v>12/30</v>
       </c>
       <c r="B130">
         <v>0</v>
@@ -2221,7 +2221,7 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>12/24</v>
+        <v>12/31</v>
       </c>
       <c r="B131">
         <v>0</v>
@@ -2230,110 +2230,12 @@
         <v>0</v>
       </c>
       <c r="D131">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="str">
-        <v>12/25</v>
-      </c>
-      <c r="B132">
-        <v>0</v>
-      </c>
-      <c r="C132">
-        <v>0</v>
-      </c>
-      <c r="D132">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="str">
-        <v>12/26</v>
-      </c>
-      <c r="B133">
-        <v>0</v>
-      </c>
-      <c r="C133">
-        <v>0</v>
-      </c>
-      <c r="D133">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="str">
-        <v>12/27</v>
-      </c>
-      <c r="B134">
-        <v>0</v>
-      </c>
-      <c r="C134">
-        <v>0</v>
-      </c>
-      <c r="D134">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="str">
-        <v>12/28</v>
-      </c>
-      <c r="B135">
-        <v>0</v>
-      </c>
-      <c r="C135">
-        <v>0</v>
-      </c>
-      <c r="D135">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="str">
-        <v>12/29</v>
-      </c>
-      <c r="B136">
-        <v>0</v>
-      </c>
-      <c r="C136">
-        <v>0</v>
-      </c>
-      <c r="D136">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="str">
-        <v>12/30</v>
-      </c>
-      <c r="B137">
-        <v>0</v>
-      </c>
-      <c r="C137">
-        <v>0</v>
-      </c>
-      <c r="D137">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="str">
-        <v>12/31</v>
-      </c>
-      <c r="B138">
-        <v>0</v>
-      </c>
-      <c r="C138">
-        <v>0</v>
-      </c>
-      <c r="D138">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D138"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D131"/>
   </ignoredErrors>
 </worksheet>
 </file>